--- a/tame_output/ON/bt/strategyON_20240618.xlsx
+++ b/tame_output/ON/bt/strategyON_20240618.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>60.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>51.3%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.4%</t>
+          <t>-76.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.6%</t>
+          <t>109.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.4%</t>
+          <t>123.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-52.2%</t>
+          <t>-51.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.2%</t>
+          <t>-72.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>90.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.8%</t>
+          <t>454.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-584.9%</t>
+          <t>-585.0%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.7%</t>
+          <t>-40.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-11.0%</t>
+          <t>1415.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>220.6%</t>
+          <t>84.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-22.5%</t>
+          <t>-20.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.6%</t>
+          <t>-32.0%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-14.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>-40.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-170.4%</t>
+          <t>-2138.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-222.1%</t>
+          <t>-211.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.0%</t>
+          <t>95.7%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.1%</t>
+          <t>-27.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>49.1%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-122.5%</t>
+          <t>-116.1%</t>
         </is>
       </c>
     </row>
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.915492735990862</v>
+        <v>-5.814271147034907</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7508709422129893</v>
+        <v>0.7913595777953715</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.8432755328774175</v>
+        <v>-0.7370650909849382</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.611459141196631</v>
+        <v>2.675185406332119</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.280620118629608</v>
+        <v>-6.179398529673653</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.604074504163322</v>
+        <v>0.6445631397457041</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.13958631717643</v>
+        <v>-1.033375875283951</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.432927185623055</v>
+        <v>2.496653450758542</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.689208895810287</v>
+        <v>-6.587987306854332</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4394005373058096</v>
+        <v>0.4798891728881913</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.548175094357108</v>
+        <v>-1.441964652464629</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.186535463329407</v>
+        <v>2.250261728464894</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.96578499612612</v>
+        <v>-6.864563407170165</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3239555296509371</v>
+        <v>0.3644441652333192</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.548175094357108</v>
+        <v>-1.441964652464629</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.181720895800868</v>
+        <v>2.245447160936355</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.382176870413117</v>
+        <v>-7.280955281457162</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1553928305450154</v>
+        <v>0.1958814661273975</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.548175094357108</v>
+        <v>-1.441964652464629</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.179714946409745</v>
+        <v>2.243441211545232</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.652942959505762</v>
+        <v>-7.551721370549807</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.0573450855766362</v>
+        <v>0.09783372115901834</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.548175094357108</v>
+        <v>-1.441964652464629</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.189973637078424</v>
+        <v>2.253699902213911</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.998817781490571</v>
+        <v>-7.897596192534616</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.08490527807159198</v>
+        <v>-0.04441664248920985</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.548175094357108</v>
+        <v>-1.441964652464629</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.186073202224119</v>
+        <v>2.249799467359606</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.162397659674955</v>
+        <v>-8.061176070719</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1519323092903444</v>
+        <v>-0.1114436737079627</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.548175094357108</v>
+        <v>-1.441964652464629</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.18447812227912</v>
+        <v>2.248204387414607</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.459059001485153</v>
+        <v>-8.357837412529198</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2668178700852155</v>
+        <v>-0.2263292345028338</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.616918230090987</v>
+        <v>-1.510707788198508</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.147011216768001</v>
+        <v>2.210737481903489</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.645778709794456</v>
+        <v>-8.544557120838501</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3455320579433399</v>
+        <v>-0.3050434223609582</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.616918230090987</v>
+        <v>-1.510707788198508</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.142984912233598</v>
+        <v>2.206711177369086</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.028780098537087</v>
+        <v>-8.927558509581132</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4988347147619763</v>
+        <v>-0.4583460791795946</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.616918230090987</v>
+        <v>-1.510707788198508</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.142882810912014</v>
+        <v>2.206609076047501</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.210649889522122</v>
+        <v>-9.109428300566167</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5690111151845603</v>
+        <v>-0.5285224796021781</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.798788021076022</v>
+        <v>-1.692577579183543</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.036332452292423</v>
+        <v>2.100058717427911</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.570180212026123</v>
+        <v>-9.468958623070169</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.7074729408881106</v>
+        <v>-0.6669843053057285</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.798788021076022</v>
+        <v>-1.692577579183543</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.041682755590473</v>
+        <v>2.10540902072596</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.620529275480346</v>
+        <v>-9.519307686524391</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.7196965463126221</v>
+        <v>-0.67920791073024</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.849137084530244</v>
+        <v>-1.742926642637765</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.019389337475118</v>
+        <v>2.083115602610605</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.718148552901742</v>
+        <v>-9.616926963945787</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7557025066594116</v>
+        <v>-0.7152138710770295</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.946756361951641</v>
+        <v>-1.840545920059162</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.963859521644048</v>
+        <v>2.027585786779536</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.865674640907384</v>
+        <v>-9.764453051951429</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8118193855400966</v>
+        <v>-0.7713307499577144</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.094282449957284</v>
+        <v>-1.988072008064805</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.878237425162234</v>
+        <v>1.941963690297722</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.06993281623725</v>
+        <v>-9.968711227281293</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.8880094585534</v>
+        <v>-0.8475208229710178</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.221921394571273</v>
+        <v>-2.115710952678794</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.807167255512484</v>
+        <v>1.870893520647971</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.14426579249741</v>
+        <v>-10.04304420354146</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.9132600945730291</v>
+        <v>-0.872771458990647</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.366620918505946</v>
+        <v>-2.260410476613467</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.724830095636116</v>
+        <v>1.788556360771603</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.07079596082996</v>
+        <v>-9.969574371874009</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.868500460412629</v>
+        <v>-0.8280118248302468</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.293151086838497</v>
+        <v>-2.186940644946018</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.784283696130006</v>
+        <v>1.848009961265493</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.24592037821651</v>
+        <v>-10.14469878926055</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9239950066197293</v>
+        <v>-0.8835063710373472</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.468275504225041</v>
+        <v>-2.362065062332562</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.693764266445597</v>
+        <v>1.757490531581084</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.480372472231</v>
+        <v>-10.37915088327504</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.024995009127121</v>
+        <v>-0.9845063735447392</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.468275504225041</v>
+        <v>-2.362065062332562</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.686545101544001</v>
+        <v>1.750271366679488</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.58474720325744</v>
+        <v>-10.48352561430149</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.073417092311676</v>
+        <v>-1.032928456729294</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.572650235251487</v>
+        <v>-2.466439793359008</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.617248072154157</v>
+        <v>1.680974337289644</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.63753335885777</v>
+        <v>-10.53631176990181</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.09341576471325</v>
+        <v>-1.052927129130868</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.668325721833884</v>
+        <v>-2.562115279941405</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.560958570043275</v>
+        <v>1.624684835178763</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.76357015222606</v>
+        <v>-10.6623485632701</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.141136753431451</v>
+        <v>-1.100648117849069</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.643074099024141</v>
+        <v>-2.536863657131662</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.578803272358235</v>
+        <v>1.642529537493723</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.71155463825725</v>
+        <v>-10.61033304930129</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.116340212157525</v>
+        <v>-1.075851576575143</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.643074099024141</v>
+        <v>-2.536863657131662</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.582793608044636</v>
+        <v>1.646519873180124</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.85322647998137</v>
+        <v>-10.75200489102541</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.174484175745915</v>
+        <v>-1.133995540163533</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.643074099024141</v>
+        <v>-2.536863657131662</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.581318381145894</v>
+        <v>1.645044646281382</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.80363563555653</v>
+        <v>-10.70241404660058</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.139594427811109</v>
+        <v>-1.099105792228727</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.593483254599307</v>
+        <v>-2.487272812706828</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.626126297965667</v>
+        <v>1.689852563101155</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.79082824255176</v>
+        <v>-10.6896066535958</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.147522604255883</v>
+        <v>-1.1070339686735</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.642339029608209</v>
+        <v>-2.53612858771573</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.583761699313643</v>
+        <v>1.647487964449131</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.56498308983235</v>
+        <v>-10.46376150087639</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.047605470131909</v>
+        <v>-1.007116834549527</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.600412354021045</v>
+        <v>-2.494201912128566</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.61849677770215</v>
+        <v>1.682223042837638</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.44040443349475</v>
+        <v>-10.3391828445388</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9966348630408128</v>
+        <v>-0.9561462274584316</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.600412354021045</v>
+        <v>-2.494201912128566</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.619635922258209</v>
+        <v>1.683362187393697</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.49329972153904</v>
+        <v>-10.39207813258309</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.01515920409642</v>
+        <v>-0.9746705685140382</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.595457007932599</v>
+        <v>-2.48924656604012</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.625242904073384</v>
+        <v>1.688969169208872</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.42116654625116</v>
+        <v>-10.3199449572952</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9805722297426316</v>
+        <v>-0.9400835941602494</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.595457007932599</v>
+        <v>-2.48924656604012</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.630976608312021</v>
+        <v>1.694702873447508</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.34980015364151</v>
+        <v>-10.24857856468556</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9617629350926373</v>
+        <v>-0.9212742995102552</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.524090615322951</v>
+        <v>-2.417880173430472</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.664059181483945</v>
+        <v>1.727785446619432</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.25634111965629</v>
+        <v>-10.15511953070033</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.9342628028114555</v>
+        <v>-0.8937741672290733</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.524090615322951</v>
+        <v>-2.417880173430472</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.654175700171037</v>
+        <v>1.717901965306524</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.98909931878789</v>
+        <v>-9.887877729831935</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.8292006429634697</v>
+        <v>-0.788712007381088</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.524090615322951</v>
+        <v>-2.417880173430472</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.652341139671663</v>
+        <v>1.716067404807151</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.891192280111399</v>
+        <v>-9.789970691155444</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7903381424663345</v>
+        <v>-0.7498495068839524</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.456104865462394</v>
+        <v>-2.349894423569915</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.692832274614536</v>
+        <v>1.756558539750024</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.867238739135441</v>
+        <v>-9.766017150179486</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7800882199304575</v>
+        <v>-0.7395995843480758</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.432151324486437</v>
+        <v>-2.325940882593958</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.707872905345605</v>
+        <v>1.771599170481092</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.603178800812644</v>
+        <v>-9.50195721185669</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6877245607630913</v>
+        <v>-0.6472359251807092</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.168091386163641</v>
+        <v>-2.061880944271162</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.85304855217753</v>
+        <v>1.916774817313017</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.896099177307807</v>
+        <v>-8.794877588351852</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.4076797450214569</v>
+        <v>-0.3671911094390752</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.168091386163641</v>
+        <v>-2.061880944271162</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.850261518517229</v>
+        <v>1.913987783652717</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.855914878941617</v>
+        <v>-8.754693289985662</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3912624017871393</v>
+        <v>-0.3507737662047576</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.12790708779745</v>
+        <v>-2.021696645904971</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.874715721424785</v>
+        <v>1.938441986560273</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.692515008002253</v>
+        <v>-8.591293419046298</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.3265356321906374</v>
+        <v>-0.2860469966082553</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.964507216858087</v>
+        <v>-1.858296774965608</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.972122465209159</v>
+        <v>2.035848730344647</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.459033785772654</v>
+        <v>-8.357812196816699</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.225218714460945</v>
+        <v>-0.1847300788785633</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.731025994628489</v>
+        <v>-1.62481555273601</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.120135627384771</v>
+        <v>2.183861892520258</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.30936739476514</v>
+        <v>-8.208145805809185</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1682443683708987</v>
+        <v>-0.1277557327885166</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.638122503385953</v>
+        <v>-1.531912061493474</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.172985511817333</v>
+        <v>2.236711776952821</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.177091921134252</v>
+        <v>-8.075870332178297</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.1199666921715168</v>
+        <v>-0.07947805658913465</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.505847029755066</v>
+        <v>-1.399636587862587</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.247718282742892</v>
+        <v>2.31144454787838</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.9864922464611</v>
+        <v>-7.885270657505145</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.04091176161461885</v>
+        <v>-0.0004231260322367092</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.315247355081913</v>
+        <v>-1.209036913189434</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.364893148234421</v>
+        <v>2.428619413369908</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.737492447777519</v>
+        <v>-7.636270858821564</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.0715944990824724</v>
+        <v>0.1120831346648541</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.315247355081913</v>
+        <v>-1.209036913189434</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.377799489458079</v>
+        <v>2.441525754593567</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.843082437550623</v>
+        <v>-7.741860848594668</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.09861742642598825</v>
+        <v>-0.05812879084360612</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.420837344855018</v>
+        <v>-1.314626902962539</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.186469565994998</v>
+        <v>2.250195831130485</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.86181733966922</v>
+        <v>-7.760595750713265</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.05756704539634061</v>
+        <v>-0.01707840981395847</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.426433354515149</v>
+        <v>-1.32022291262267</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.231656302076006</v>
+        <v>2.295382567211493</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.713877298261621</v>
+        <v>-7.612655709305666</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1182699515214685</v>
+        <v>-0.07778131593908633</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.406112438606591</v>
+        <v>-1.299901996714112</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.123969928932973</v>
+        <v>2.18769619406846</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.660907776007632</v>
+        <v>-7.559686187051677</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.1057961288733513</v>
+        <v>-0.06530749329096919</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.353142916352602</v>
+        <v>-1.246932474460123</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.147037656031888</v>
+        <v>2.210763921167375</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.617359369236942</v>
+        <v>-7.516137780280987</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.0953373782601683</v>
+        <v>-0.05484874267778617</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.353142916352602</v>
+        <v>-1.246932474460123</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.140077043936795</v>
+        <v>2.203803309072282</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.375210975783084</v>
+        <v>-7.273989386827129</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.01598433350251804</v>
+        <v>0.05647296908490018</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.353142916352602</v>
+        <v>-1.246932474460123</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.154539398317938</v>
+        <v>2.218265663453425</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.266951838660562</v>
+        <v>-7.165730249704607</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.05382010881072175</v>
+        <v>0.09430874439310388</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.353142916352602</v>
+        <v>-1.246932474460123</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.149071518777133</v>
+        <v>2.21279778391262</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.143660703843431</v>
+        <v>-7.042439114887476</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1006346567481509</v>
+        <v>0.141123292330533</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.229851781535472</v>
+        <v>-1.123641339642993</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.220544293677988</v>
+        <v>2.284270558813475</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.122511504939988</v>
+        <v>-7.021289915984033</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1167953145468537</v>
+        <v>0.1572839501292354</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.208702582632029</v>
+        <v>-1.10249214073955</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.240934791257379</v>
+        <v>2.304661056392867</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.878746062956544</v>
+        <v>-6.777524474000589</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2100821996872821</v>
+        <v>0.2505708352696638</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.208702582632029</v>
+        <v>-1.10249214073955</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.23671549960443</v>
+        <v>2.300441764739917</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.776983242679249</v>
+        <v>-6.675761653723294</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.252911641718216</v>
+        <v>0.2934002773005977</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.1954835142396</v>
+        <v>-1.089273072347121</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.246771254559903</v>
+        <v>2.310497519695391</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.527132848730174</v>
+        <v>-6.425911259774219</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3455938742815481</v>
+        <v>0.3860825098639298</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.1954835142396</v>
+        <v>-1.089273072347121</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.239513329543605</v>
+        <v>2.303239594679093</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.351240756262742</v>
+        <v>-6.250019167306787</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4195498347891693</v>
+        <v>0.4600384703715514</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.1954835142396</v>
+        <v>-1.089273072347121</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.243112453064254</v>
+        <v>2.306838718199741</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.179794293240279</v>
+        <v>-6.078572704284324</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5014559260527087</v>
+        <v>0.5419445616350904</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.024037051217137</v>
+        <v>-0.9178266093246578</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.359307836932286</v>
+        <v>2.423034102067773</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.105504727501939</v>
+        <v>-6.004283138545984</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5301922299643413</v>
+        <v>0.570680865546723</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.9497474854787973</v>
+        <v>-0.8435370435863185</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.402902053991586</v>
+        <v>2.466628319127073</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.041868985268005</v>
+        <v>-5.94064739631205</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5603413279122322</v>
+        <v>0.6008299634946144</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.8861117432448627</v>
+        <v>-0.779901301352384</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.445778300386264</v>
+        <v>2.509504565521751</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.930442225942085</v>
+        <v>-5.82922063698613</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5861062904263958</v>
+        <v>0.626594926008778</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.8861117432448627</v>
+        <v>-0.779901301352384</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.42697255917006</v>
+        <v>2.490698824305547</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.690011729137225</v>
+        <v>-5.58879014018127</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6840215657732176</v>
+        <v>0.7245102013555993</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.6456812464400025</v>
+        <v>-0.5394708045475237</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.572973933877853</v>
+        <v>2.636700199013341</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.61776916096603</v>
+        <v>-5.516547572010075</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7168479068765157</v>
+        <v>0.7573365424588974</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.6456812464400025</v>
+        <v>-0.5394708045475237</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.576903247712674</v>
+        <v>2.640629512848161</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.564770838684642</v>
+        <v>-5.463549249728687</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7387258197064108</v>
+        <v>0.7792144552887925</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.5903449874380636</v>
+        <v>-0.4841345455455849</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.610783587031177</v>
+        <v>2.674509852166664</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.455965953204915</v>
+        <v>-5.35474436424896</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7792458451182949</v>
+        <v>0.819734480700677</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.5903449874380636</v>
+        <v>-0.4841345455455849</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.607781658251171</v>
+        <v>2.671507923386658</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.235945155167904</v>
+        <v>-5.134723566211949</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8688332013437132</v>
+        <v>0.9093218369260954</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4491251423700834</v>
+        <v>-0.3429147004776046</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.694092602302573</v>
+        <v>2.75781886743806</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.103077466104627</v>
+        <v>-5.001855877148672</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9378744597708479</v>
+        <v>0.9783630953532296</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4491251423700834</v>
+        <v>-0.3429147004776046</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.709986785104396</v>
+        <v>2.773713050239883</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.982904382740128</v>
+        <v>-4.881682793784173</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9870895375569491</v>
+        <v>1.027578173139331</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.3289520590055844</v>
+        <v>-0.2227416171131057</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.783236479563397</v>
+        <v>2.846962744698884</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.838232237640391</v>
+        <v>-4.737010648684436</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.055046498158284</v>
+        <v>1.095535133740666</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.184279913905847</v>
+        <v>-0.07806947201336828</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.88012786918468</v>
+        <v>2.943854134320167</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.898107064998083</v>
+        <v>-4.796885476042128</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.017134058616633</v>
+        <v>1.057622694199015</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.2441547412635391</v>
+        <v>-0.1379442993710604</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.83024046417149</v>
+        <v>2.893966729306977</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.811307567219075</v>
+        <v>-4.71008597826312</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.074254351050802</v>
+        <v>1.114742986633184</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.2441547412635391</v>
+        <v>-0.1379442993710604</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.852640957494056</v>
+        <v>2.916367222629543</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.813777273680881</v>
+        <v>-4.712555684724926</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.073338869839492</v>
+        <v>1.113827505421874</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.2466244477253453</v>
+        <v>-0.1404140058328666</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.851231534990385</v>
+        <v>2.914957800125872</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.882147460004891</v>
+        <v>-4.780925871048936</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.05699771778459</v>
+        <v>1.097486353366972</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.2373487486891304</v>
+        <v>-0.1311383067966516</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.867803876886815</v>
+        <v>2.931530142022303</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.990685640921025</v>
+        <v>-4.88946405196507</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.004019154050028</v>
+        <v>1.04450778963241</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.2373487486891304</v>
+        <v>-0.1311383067966516</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.858240585518707</v>
+        <v>2.921966850654194</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.02167880024973</v>
+        <v>-4.920457211293775</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8163314553589323</v>
+        <v>0.8568200909413144</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.2373487486891304</v>
+        <v>-0.1311383067966516</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.682950150559094</v>
+        <v>2.746676415694581</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.846204540457261</v>
+        <v>-4.744982951501306</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.8910883912677077</v>
+        <v>0.9315770268500896</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.2373487486891304</v>
+        <v>-0.1311383067966516</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.687517382550881</v>
+        <v>2.751243647686369</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.95714079309851</v>
+        <v>-4.855919204142555</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8224559189724152</v>
+        <v>0.8629445545547971</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.2373487486891304</v>
+        <v>-0.1311383067966516</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.663259411312088</v>
+        <v>2.726985676447576</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.965422867243569</v>
+        <v>-4.864201278287614</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8222744745342974</v>
+        <v>0.8627631101166793</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.2456308228341887</v>
+        <v>-0.13942038094171</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.661421552044959</v>
+        <v>2.725147817180446</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.905570248039846</v>
+        <v>-4.804348659083891</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8563879086479189</v>
+        <v>0.8968765442303008</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.2456308228341887</v>
+        <v>-0.13942038094171</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.671593938477091</v>
+        <v>2.735320203612579</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.819326785013468</v>
+        <v>-4.718105196057513</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8858315644323302</v>
+        <v>0.9263202000147124</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.2456308228341887</v>
+        <v>-0.13942038094171</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.666540209050952</v>
+        <v>2.730266474186439</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.864633604412448</v>
+        <v>-4.763412015456493</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8594846121172639</v>
+        <v>0.8999732476996458</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.2864409858434195</v>
+        <v>-0.1802305439509408</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.633829886689939</v>
+        <v>2.697556151825426</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.893666709114749</v>
+        <v>-4.792445120158794</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.848423243269445</v>
+        <v>0.8889118788518271</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.2864409858434195</v>
+        <v>-0.1802305439509408</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.63438175972304</v>
+        <v>2.698108024858528</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.800856227663889</v>
+        <v>-4.699634638707934</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8148201277411546</v>
+        <v>0.8553087633235366</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.1936305043925602</v>
+        <v>-0.08742006250008144</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.619340740484922</v>
+        <v>2.683067005620409</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.845245696993317</v>
+        <v>-4.744024108037362</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.7989378159339844</v>
+        <v>0.8394264515163663</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.2380199737219879</v>
+        <v>-0.1318095318295091</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.594580534811866</v>
+        <v>2.658306799947353</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.732574478757066</v>
+        <v>-4.631352889801112</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8390820117402074</v>
+        <v>0.8795706473225895</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.1253487554857377</v>
+        <v>-0.0191383135932589</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.657258974265339</v>
+        <v>2.720985239400826</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.620197477574393</v>
+        <v>-4.518975888618439</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.8895241080439438</v>
+        <v>0.9300127436263259</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.1253487554857377</v>
+        <v>-0.0191383135932589</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.662750270096006</v>
+        <v>2.726476535231493</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.647977875475746</v>
+        <v>-4.546756286519791</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8899091506519419</v>
+        <v>0.9303977862343238</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1531291533870907</v>
+        <v>-0.04691871149461196</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.657579233123733</v>
+        <v>2.721305498259221</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.730979156501025</v>
+        <v>-4.62975756754507</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6950643582424836</v>
+        <v>0.7355529938248655</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.1717000379142645</v>
+        <v>-0.06548959602178572</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.484792422408082</v>
+        <v>2.54851868754357</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.839593234944356</v>
+        <v>-4.738371645988401</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7717683875843568</v>
+        <v>0.8122570231667388</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.1717000379142645</v>
+        <v>-0.06548959602178572</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.604942083127288</v>
+        <v>2.668668348262775</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.926191817925459</v>
+        <v>-4.824970228969504</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7516419804942385</v>
+        <v>0.7921306160766206</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.1717000379142645</v>
+        <v>-0.06548959602178572</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.619455109229611</v>
+        <v>2.683181374365098</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.887808155367308</v>
+        <v>-4.786586566411353</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.7644148868598677</v>
+        <v>0.8049035224422496</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.1333163753561133</v>
+        <v>-0.02710593346363455</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.63990474810687</v>
+        <v>2.703631013242358</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.710691825332142</v>
+        <v>-4.609470236376187</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8319904477192361</v>
+        <v>0.8724790833016181</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.1333163753561133</v>
+        <v>-0.02710593346363455</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.636633776952173</v>
+        <v>2.700360042087659</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.755784070165688</v>
+        <v>-4.654562481209733</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8146369415477308</v>
+        <v>0.8551255771301127</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.1952124185255031</v>
+        <v>-0.08900197663302434</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.600179542812452</v>
+        <v>2.663905807947939</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.57640864892692</v>
+        <v>-4.475187059970965</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.8801740853496522</v>
+        <v>0.9206627209320342</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.03843566035478441</v>
+        <v>0.06777478153769434</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.688032573021297</v>
+        <v>2.751758838156785</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.621422862447526</v>
+        <v>-4.520201273491571</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8429758552729998</v>
+        <v>0.8834644908553817</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.06878455566938901</v>
+        <v>0.03742588622308973</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.650630691164124</v>
+        <v>2.714356956299611</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.888427372719961</v>
+        <v>-4.787205783764006</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.7418656135029715</v>
+        <v>0.7823542490853534</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2631475937123376</v>
+        <v>-0.1569371518198588</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.539704430677301</v>
+        <v>2.603430695812788</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.989625154157133</v>
+        <v>-4.888403565201179</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7005904228246038</v>
+        <v>0.7410790584069857</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.3315564072576568</v>
+        <v>-0.225345965365178</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.497863064446611</v>
+        <v>2.561589329582098</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.957149567986361</v>
+        <v>-4.855927979030406</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7111806188472294</v>
+        <v>0.7516692544296113</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.3315564072576568</v>
+        <v>-0.225345965365178</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.495463026000928</v>
+        <v>2.559189291136414</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.938111440279064</v>
+        <v>-4.836889851323109</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7153205891383934</v>
+        <v>0.7558092247207753</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3897400185888513</v>
+        <v>-0.2835295766963726</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.457077578410455</v>
+        <v>2.520803843545943</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.969238071429682</v>
+        <v>-4.868016482473728</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.8804518056168265</v>
+        <v>0.9209404411992084</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3897400185888513</v>
+        <v>-0.2835295766963726</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.634659447349136</v>
+        <v>2.698385712484623</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.9831048327636</v>
+        <v>-4.881883243807645</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.8757384300693929</v>
+        <v>0.9162270656517748</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4275979353226743</v>
+        <v>-0.3213874934301955</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.612778026294976</v>
+        <v>2.676504291430463</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.003362131292558</v>
+        <v>-4.902140542336603</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.8736440410547357</v>
+        <v>0.9141326766371176</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.4275979353226743</v>
+        <v>-0.3213874934301955</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.618786556691902</v>
+        <v>2.682512821827389</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.855619161057556</v>
+        <v>-4.754397572101601</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.011893876940759</v>
+        <v>1.052382512523141</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2597905780877911</v>
+        <v>-0.1535801361953124</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.798623618824854</v>
+        <v>2.862349883960341</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.957633843588777</v>
+        <v>-4.856412254632822</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9738816254597511</v>
+        <v>1.014370261042133</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.2597905780877911</v>
+        <v>-0.1535801361953124</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.801417240356335</v>
+        <v>2.865143505491822</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.951481137535993</v>
+        <v>-4.850259548580038</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9770050562725232</v>
+        <v>1.017493691854905</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.2536378720350068</v>
+        <v>-0.1474274301425281</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.805771212379664</v>
+        <v>2.869497477515151</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.968290435686495</v>
+        <v>-4.86706884673054</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9693618137524327</v>
+        <v>1.009850449334815</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.2704471701855085</v>
+        <v>-0.1642367282930297</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.794766110229473</v>
+        <v>2.85849237536496</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.905992436910372</v>
+        <v>-4.804770847954417</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.060616567059702</v>
+        <v>1.101105202642084</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.2704471701855085</v>
+        <v>-0.1642367282930297</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.861101664026294</v>
+        <v>2.924827929161781</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.704202239245214</v>
+        <v>-4.602980650289259</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8499135185151636</v>
+        <v>0.8904021540975455</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.07242897801635406</v>
+        <v>0.03378146387612468</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.688493451717184</v>
+        <v>2.752219716852672</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.644311557602621</v>
+        <v>-4.543089968646666</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9441600234943761</v>
+        <v>0.984648659076758</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.01253829637376058</v>
+        <v>0.09367214551871816</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.794718093024916</v>
+        <v>2.858444358160403</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.742052102227595</v>
+        <v>-4.640830513271641</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9196915417604301</v>
+        <v>0.960180177342812</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.02842757450674077</v>
+        <v>0.07778286738573797</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.799812262261171</v>
+        <v>2.863538527396658</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.918389862350525</v>
+        <v>-4.81716827339457</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.84769241853593</v>
+        <v>0.8881810541183119</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.2047653346296702</v>
+        <v>-0.09855489273719142</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.692545587012085</v>
+        <v>2.756271852147572</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.846843539573648</v>
+        <v>-4.745621950617693</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8748025656866094</v>
+        <v>0.9152912012689913</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.2047653346296702</v>
+        <v>-0.09855489273719142</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.691037205052014</v>
+        <v>2.754763470187501</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.802470407935079</v>
+        <v>-4.701248818979124</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8924146857774731</v>
+        <v>0.932903321359855</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.1603922029911016</v>
+        <v>-0.05418176109862283</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.717523951470591</v>
+        <v>2.781250216606078</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.794516437640307</v>
+        <v>-4.693294848684352</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.8955962738953818</v>
+        <v>0.9360849094777639</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.1603922029911016</v>
+        <v>-0.05418176109862283</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.717523951470591</v>
+        <v>2.781250216606078</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.746860707079251</v>
+        <v>-4.645639118123296</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9210403231476088</v>
+        <v>0.9615289587299909</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.1127364724300459</v>
+        <v>-0.006526030537567173</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.752499146835029</v>
+        <v>2.816225411970517</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.619176397284955</v>
+        <v>-4.517954808329</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.9770064204400521</v>
+        <v>1.017495056022434</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.01494783736425054</v>
+        <v>0.1211582792567293</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.834002106086332</v>
+        <v>2.897728371221819</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.679842987687344</v>
+        <v>-4.578621398731389</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.9394944567549686</v>
+        <v>0.9799830923373505</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.06675047935428313</v>
+        <v>0.03945996253819561</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.771737788531084</v>
+        <v>2.835464053666571</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.635004586078946</v>
+        <v>-4.533782997122991</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.9615275200089566</v>
+        <v>1.002016155591338</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.06220704640941366</v>
+        <v>0.04400339548306509</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.778561550908634</v>
+        <v>2.842287816044121</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.735763221835944</v>
+        <v>-4.634541632879989</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.9253850053372354</v>
+        <v>0.9658736409196174</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.1510326151364191</v>
+        <v>-0.04482217324394033</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.729427149303509</v>
+        <v>2.793153414438996</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.691560384750043</v>
+        <v>-4.590338795794088</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.9489457426994328</v>
+        <v>0.9894343782818147</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.1068297780505186</v>
+        <v>-0.0006193361580398848</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.761828454082886</v>
+        <v>2.825554719218374</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.728539412413486</v>
+        <v>-4.627317823457531</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.9325641321033031</v>
+        <v>0.973052767685685</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.0698558762591881</v>
+        <v>0.03635456563329065</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.782422795626932</v>
+        <v>2.84614906076242</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.748597491278327</v>
+        <v>-4.647375902322372</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.9757886657404065</v>
+        <v>1.016277301322789</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.0698558762591881</v>
+        <v>0.03635456563329065</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.833670560809972</v>
+        <v>2.897396825945459</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.708666818100436</v>
+        <v>-4.607445229144481</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.9902016396058158</v>
+        <v>1.030690275188198</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.02992520308129776</v>
+        <v>0.07628523881118099</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.856069669310959</v>
+        <v>2.919795934446447</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.657634725377909</v>
+        <v>-4.556413136421954</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.005562704933097</v>
+        <v>1.046051340515479</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.0211068896412302</v>
+        <v>0.1273173315337089</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.881637153182746</v>
+        <v>2.945363418318233</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.592410544250703</v>
+        <v>-4.491188955294748</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.048839781476684</v>
+        <v>1.089328417059066</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.08633107076843582</v>
+        <v>0.1925415126609146</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.937959065951774</v>
+        <v>3.001685331087262</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.642904834607759</v>
+        <v>-4.541683245651805</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.024603037633142</v>
+        <v>1.065091673215524</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.04131033364236159</v>
+        <v>0.1475207755348403</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.90690759597541</v>
+        <v>2.970633861110898</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.663016490642468</v>
+        <v>-4.561794901686513</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.017815167550499</v>
+        <v>1.058303803132881</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.05233767863978078</v>
+        <v>0.1585481205322595</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.914780795305102</v>
+        <v>2.978507060440589</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.760697069915114</v>
+        <v>-4.659475480959159</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.139300706862651</v>
+        <v>1.179789342445033</v>
       </c>
       <c r="F1991" t="n">
-        <v>-0.05836551670040802</v>
+        <v>0.04784492519207073</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.008916649122199</v>
+        <v>3.072642914257687</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.736905501308971</v>
+        <v>-4.635683912353016</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.268930243522925</v>
+        <v>1.309418879105307</v>
       </c>
       <c r="F1992" t="n">
-        <v>-0.03457394809426573</v>
+        <v>0.07163649379821302</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.143304499503702</v>
+        <v>3.207030764639189</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.773659919870694</v>
+        <v>-4.672438330914739</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.245936452112095</v>
+        <v>1.286425087694477</v>
       </c>
       <c r="F1993" t="n">
-        <v>-0.03457394809426573</v>
+        <v>0.07163649379821302</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.135012475517561</v>
+        <v>3.198738740653048</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.769325616813646</v>
+        <v>-4.668104027857691</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.245863368918694</v>
+        <v>1.286352004501076</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.1170761552249382</v>
+        <v>0.2232865971174169</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.224195733092863</v>
+        <v>3.28792199822835</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.760433155420363</v>
+        <v>-4.659211566464408</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.266974759202799</v>
+        <v>1.307463394785181</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.1170761552249382</v>
+        <v>0.2232865971174169</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.241750138819654</v>
+        <v>3.305476403955141</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.92890927239024</v>
+        <v>-4.827687683434285</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.191439359819432</v>
+        <v>1.231927995401814</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.08912831950835742</v>
+        <v>0.1953387614008362</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.21683648479429</v>
+        <v>3.280562749929777</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.233772154546119</v>
       </c>
       <c r="D1997" t="n">
-        <v>-4.231109743528657</v>
+        <v>-4.129888154572702</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.540971832820909</v>
+        <v>1.58146046840329</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.0187802601379467</v>
+        <v>0.1249907020304254</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.245040310628887</v>
+        <v>3.308766575764374</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.760418871733831</v>
+        <v>3.793368797740295</v>
       </c>
       <c r="C1998" t="n">
         <v>3.224436177043023</v>
       </c>
       <c r="D1998" t="n">
-        <v>-4.233495784021034</v>
+        <v>-4.234015631618478</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.530681439120862</v>
+        <v>1.530473500081885</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.0187802601379467</v>
+        <v>0.1249907020304254</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.235704333125792</v>
+        <v>3.299430598261279</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240618.xlsx
+++ b/tame_output/ON/bt/strategyON_20240618.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-12.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,17 +859,17 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-5.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.3%</t>
+          <t>-76.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.2%</t>
+          <t>109.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.6%</t>
+          <t>124.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.2%</t>
+          <t>93.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.8%</t>
+          <t>-52.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.0%</t>
+          <t>-73.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>454.0%</t>
+          <t>449.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-585.0%</t>
+          <t>-599.2%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>49.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.4%</t>
+          <t>-40.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>1415.9%</t>
+          <t>-23.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>84.1%</t>
+          <t>-33.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-223.2%</t>
+          <t>-228.9%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-22.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.0%</t>
+          <t>-32.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-14.0%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-40.3%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-2138.2%</t>
+          <t>-170.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-211.5%</t>
+          <t>-222.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>95.7%</t>
+          <t>96.0%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-27.5%</t>
+          <t>-28.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-116.1%</t>
+          <t>-122.5%</t>
         </is>
       </c>
     </row>
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.814271147034907</v>
+        <v>-5.915492735990862</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7913595777953715</v>
+        <v>0.7508709422129893</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.7370650909849382</v>
+        <v>-0.8432755328774175</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.675185406332119</v>
+        <v>2.611459141196631</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970903</v>
+        <v>3.304715716970902</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.179398529673653</v>
+        <v>-6.280620118629608</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6445631397457041</v>
+        <v>0.604074504163322</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.033375875283951</v>
+        <v>-1.13958631717643</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.496653450758542</v>
+        <v>2.432927185623055</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330521</v>
+        <v>3.30081581833052</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.587987306854332</v>
+        <v>-6.689208895810287</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4798891728881913</v>
+        <v>0.4394005373058096</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.441964652464629</v>
+        <v>-1.548175094357108</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.250261728464894</v>
+        <v>2.186535463329407</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.864563407170165</v>
+        <v>-6.96578499612612</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3644441652333192</v>
+        <v>0.3239555296509371</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.441964652464629</v>
+        <v>-1.548175094357108</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.245447160936355</v>
+        <v>2.181720895800868</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108638</v>
+        <v>3.305023265108637</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.280955281457162</v>
+        <v>-7.382176870413117</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1958814661273975</v>
+        <v>0.1553928305450154</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.441964652464629</v>
+        <v>-1.548175094357108</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.243441211545232</v>
+        <v>2.179714946409745</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.34137872309782</v>
+        <v>3.341378723097819</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.551721370549807</v>
+        <v>-7.652942959505762</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.09783372115901834</v>
+        <v>0.0573450855766362</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.441964652464629</v>
+        <v>-1.548175094357108</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.253699902213911</v>
+        <v>2.189973637078424</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094116</v>
+        <v>3.374439043094115</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.897596192534616</v>
+        <v>-7.998817781490571</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.04441664248920985</v>
+        <v>-0.08490527807159198</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.441964652464629</v>
+        <v>-1.548175094357108</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.249799467359606</v>
+        <v>2.186073202224119</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199285</v>
+        <v>3.405960511199284</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.061176070719</v>
+        <v>-8.162397659674955</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1114436737079627</v>
+        <v>-0.1519323092903444</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.441964652464629</v>
+        <v>-1.548175094357108</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.248204387414607</v>
+        <v>2.18447812227912</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.357837412529198</v>
+        <v>-8.459059001485153</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2263292345028338</v>
+        <v>-0.2668178700852155</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.510707788198508</v>
+        <v>-1.616918230090987</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.210737481903489</v>
+        <v>2.147011216768001</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923086</v>
+        <v>3.419979433923085</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.544557120838501</v>
+        <v>-8.645778709794456</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3050434223609582</v>
+        <v>-0.3455320579433399</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.510707788198508</v>
+        <v>-1.616918230090987</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.206711177369086</v>
+        <v>2.142984912233598</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297748</v>
+        <v>3.458100091297747</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.927558509581132</v>
+        <v>-9.028780098537087</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4583460791795946</v>
+        <v>-0.4988347147619763</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.510707788198508</v>
+        <v>-1.616918230090987</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.206609076047501</v>
+        <v>2.142882810912014</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317615</v>
+        <v>3.447750501317614</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.109428300566167</v>
+        <v>-9.210649889522122</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5285224796021781</v>
+        <v>-0.5690111151845603</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.692577579183543</v>
+        <v>-1.798788021076022</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.100058717427911</v>
+        <v>2.036332452292423</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737168</v>
+        <v>3.503515506737167</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.468958623070169</v>
+        <v>-9.570180212026123</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6669843053057285</v>
+        <v>-0.7074729408881106</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.692577579183543</v>
+        <v>-1.798788021076022</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.10540902072596</v>
+        <v>2.041682755590473</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341311</v>
+        <v>3.50317028234131</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.519307686524391</v>
+        <v>-9.620529275480346</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.67920791073024</v>
+        <v>-0.7196965463126221</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.742926642637765</v>
+        <v>-1.849137084530244</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.083115602610605</v>
+        <v>2.019389337475118</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539461</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.616926963945787</v>
+        <v>-9.718148552901742</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7152138710770295</v>
+        <v>-0.7557025066594116</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.840545920059162</v>
+        <v>-1.946756361951641</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.027585786779536</v>
+        <v>1.963859521644048</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937497</v>
+        <v>3.492448711937496</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.764453051951429</v>
+        <v>-9.865674640907384</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7713307499577144</v>
+        <v>-0.8118193855400966</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.988072008064805</v>
+        <v>-2.094282449957284</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.941963690297722</v>
+        <v>1.878237425162234</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141699</v>
+        <v>3.502790399141698</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.968711227281293</v>
+        <v>-10.06993281623725</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.8475208229710178</v>
+        <v>-0.8880094585534</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.115710952678794</v>
+        <v>-2.221921394571273</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.870893520647971</v>
+        <v>1.807167255512484</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.04304420354146</v>
+        <v>-10.14426579249741</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.872771458990647</v>
+        <v>-0.9132600945730291</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.260410476613467</v>
+        <v>-2.366620918505946</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.788556360771603</v>
+        <v>1.724830095636116</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440632</v>
+        <v>3.499971739440631</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.969574371874009</v>
+        <v>-10.07079596082996</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.8280118248302468</v>
+        <v>-0.868500460412629</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.186940644946018</v>
+        <v>-2.293151086838497</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.848009961265493</v>
+        <v>1.784283696130006</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608599</v>
+        <v>3.490059241608598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.14469878926055</v>
+        <v>-10.24592037821651</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8835063710373472</v>
+        <v>-0.9239950066197293</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.362065062332562</v>
+        <v>-2.468275504225041</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.757490531581084</v>
+        <v>1.693764266445597</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587859441027</v>
+        <v>3.485878594410269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.37915088327504</v>
+        <v>-10.480372472231</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9845063735447392</v>
+        <v>-1.024995009127121</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.362065062332562</v>
+        <v>-2.468275504225041</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.750271366679488</v>
+        <v>1.686545101544001</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764395</v>
+        <v>3.480692492764394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.48352561430149</v>
+        <v>-10.58474720325744</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.032928456729294</v>
+        <v>-1.073417092311676</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.466439793359008</v>
+        <v>-2.572650235251487</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.680974337289644</v>
+        <v>1.617248072154157</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390584</v>
+        <v>3.493716014390583</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.53631176990181</v>
+        <v>-10.63753335885777</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.052927129130868</v>
+        <v>-1.09341576471325</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.562115279941405</v>
+        <v>-2.668325721833884</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.624684835178763</v>
+        <v>1.560958570043275</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.6623485632701</v>
+        <v>-10.76357015222606</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.100648117849069</v>
+        <v>-1.141136753431451</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.536863657131662</v>
+        <v>-2.643074099024141</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.642529537493723</v>
+        <v>1.578803272358235</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.61033304930129</v>
+        <v>-10.71155463825725</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.075851576575143</v>
+        <v>-1.116340212157525</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.536863657131662</v>
+        <v>-2.643074099024141</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.646519873180124</v>
+        <v>1.582793608044636</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.75200489102541</v>
+        <v>-10.85322647998137</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.133995540163533</v>
+        <v>-1.174484175745915</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.536863657131662</v>
+        <v>-2.643074099024141</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.645044646281382</v>
+        <v>1.581318381145894</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940718</v>
+        <v>3.691571733940717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.70241404660058</v>
+        <v>-10.80363563555653</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.099105792228727</v>
+        <v>-1.139594427811109</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.487272812706828</v>
+        <v>-2.593483254599307</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.689852563101155</v>
+        <v>1.626126297965667</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770579</v>
+        <v>3.676841549770578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.6896066535958</v>
+        <v>-10.79082824255176</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.1070339686735</v>
+        <v>-1.147522604255883</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.53612858771573</v>
+        <v>-2.642339029608209</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.647487964449131</v>
+        <v>1.583761699313643</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.46376150087639</v>
+        <v>-10.56498308983235</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.007116834549527</v>
+        <v>-1.047605470131909</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.494201912128566</v>
+        <v>-2.600412354021045</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.682223042837638</v>
+        <v>1.61849677770215</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812101</v>
+        <v>3.6848438238121</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.3391828445388</v>
+        <v>-10.44040443349475</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9561462274584316</v>
+        <v>-0.9966348630408128</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.494201912128566</v>
+        <v>-2.600412354021045</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.683362187393697</v>
+        <v>1.619635922258209</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646215</v>
+        <v>3.710935533646214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.39207813258309</v>
+        <v>-10.49329972153904</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9746705685140382</v>
+        <v>-1.01515920409642</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.48924656604012</v>
+        <v>-2.595457007932599</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.688969169208872</v>
+        <v>1.625242904073384</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611567</v>
+        <v>3.768951674611566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.3199449572952</v>
+        <v>-10.42116654625116</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9400835941602494</v>
+        <v>-0.9805722297426316</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.48924656604012</v>
+        <v>-2.595457007932599</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.694702873447508</v>
+        <v>1.630976608312021</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955327</v>
+        <v>3.728577929955325</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.24857856468556</v>
+        <v>-10.34980015364151</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9212742995102552</v>
+        <v>-0.9617629350926373</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.417880173430472</v>
+        <v>-2.524090615322951</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.727785446619432</v>
+        <v>1.664059181483945</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232411</v>
+        <v>3.74770266023241</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.15511953070033</v>
+        <v>-10.25634111965629</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8937741672290733</v>
+        <v>-0.9342628028114555</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.417880173430472</v>
+        <v>-2.524090615322951</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.717901965306524</v>
+        <v>1.654175700171037</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436227</v>
+        <v>3.766317079436226</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.887877729831935</v>
+        <v>-10.15724787015055</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.788712007381088</v>
+        <v>-0.8964600635085334</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.417880173430472</v>
+        <v>-2.524090615322951</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.716067404807151</v>
+        <v>1.652341139671663</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311948</v>
+        <v>3.784684521311947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.789970691155444</v>
+        <v>-10.05934083147406</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7498495068839524</v>
+        <v>-0.8575975630113981</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.349894423569915</v>
+        <v>-2.456104865462394</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.756558539750024</v>
+        <v>1.692832274614536</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097244</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.766017150179486</v>
+        <v>-10.0353872904981</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7395995843480758</v>
+        <v>-0.8473476404755211</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.325940882593958</v>
+        <v>-2.432151324486437</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.771599170481092</v>
+        <v>1.707872905345605</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017772</v>
+        <v>3.789311112017771</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.50195721185669</v>
+        <v>-9.771327352175303</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6472359251807092</v>
+        <v>-0.7549839813081549</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.061880944271162</v>
+        <v>-2.168091386163641</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.916774817313017</v>
+        <v>1.85304855217753</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839724</v>
+        <v>3.833252747839722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.794877588351852</v>
+        <v>-9.064247728670466</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3671911094390752</v>
+        <v>-0.4749391655665205</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.061880944271162</v>
+        <v>-2.168091386163641</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.913987783652717</v>
+        <v>1.850261518517229</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388727</v>
+        <v>3.839374447388725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.754693289985662</v>
+        <v>-9.024063430304276</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3507737662047576</v>
+        <v>-0.458521822332203</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.021696645904971</v>
+        <v>-2.12790708779745</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.938441986560273</v>
+        <v>1.874715721424785</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626473</v>
+        <v>3.856161751626471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.591293419046298</v>
+        <v>-8.860663559364912</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2860469966082553</v>
+        <v>-0.393795052735701</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.858296774965608</v>
+        <v>-1.964507216858087</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.035848730344647</v>
+        <v>1.972122465209159</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.78733042929181</v>
+        <v>3.787330429291808</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.357812196816699</v>
+        <v>-8.627182337135313</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1847300788785633</v>
+        <v>-0.2924781350060086</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.62481555273601</v>
+        <v>-1.731025994628489</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.183861892520258</v>
+        <v>2.120135627384771</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785786</v>
+        <v>3.801637122785785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.208145805809185</v>
+        <v>-8.477515946127799</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1277557327885166</v>
+        <v>-0.2355037889159624</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.531912061493474</v>
+        <v>-1.638122503385953</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.236711776952821</v>
+        <v>2.172985511817333</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390426</v>
+        <v>3.763182248390424</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.075870332178297</v>
+        <v>-8.345240472496911</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.07947805658913465</v>
+        <v>-0.1872261127165804</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.399636587862587</v>
+        <v>-1.505847029755066</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.31144454787838</v>
+        <v>2.247718282742892</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105951</v>
+        <v>3.784718794105949</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.885270657505145</v>
+        <v>-8.154640797823758</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.0004231260322367092</v>
+        <v>-0.108171182159682</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.209036913189434</v>
+        <v>-1.315247355081913</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.428619413369908</v>
+        <v>2.364893148234421</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960985</v>
+        <v>3.753882571960983</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.636270858821564</v>
+        <v>-7.905640999140177</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1120831346648541</v>
+        <v>0.00433507853740922</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.209036913189434</v>
+        <v>-1.315247355081913</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.441525754593567</v>
+        <v>2.377799489458079</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607642</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.741860848594668</v>
+        <v>-8.011230988913281</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.05812879084360612</v>
+        <v>-0.1658768469710514</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.314626902962539</v>
+        <v>-1.420837344855018</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.250195831130485</v>
+        <v>2.186469565994998</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.7704225839879</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.760595750713265</v>
+        <v>-8.029965891031878</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.01707840981395847</v>
+        <v>-0.1248264659414038</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.32022291262267</v>
+        <v>-1.426433354515149</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.295382567211493</v>
+        <v>2.231656302076006</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.76033368671081</v>
+        <v>3.760333686710808</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.612655709305666</v>
+        <v>-7.882025849624279</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.07778131593908633</v>
+        <v>-0.1855293720665316</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.299901996714112</v>
+        <v>-1.406112438606591</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.18769619406846</v>
+        <v>2.123969928932973</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409202</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.559686187051677</v>
+        <v>-7.82905632737029</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.06530749329096919</v>
+        <v>-0.1730555494184145</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.246932474460123</v>
+        <v>-1.353142916352602</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.210763921167375</v>
+        <v>2.147037656031888</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.729969716098106</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.516137780280987</v>
+        <v>-7.7855079205996</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.05484874267778617</v>
+        <v>-0.1625967988052315</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.246932474460123</v>
+        <v>-1.353142916352602</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.203803309072282</v>
+        <v>2.140077043936795</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493418</v>
+        <v>3.782922533493417</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.273989386827129</v>
+        <v>-7.543359527145742</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.05647296908490018</v>
+        <v>-0.05127508704254513</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.246932474460123</v>
+        <v>-1.353142916352602</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.218265663453425</v>
+        <v>2.154539398317938</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722815</v>
+        <v>3.828551486722813</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.165730249704607</v>
+        <v>-7.43510039002322</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.09430874439310388</v>
+        <v>-0.01343931173434143</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.246932474460123</v>
+        <v>-1.353142916352602</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.21279778391262</v>
+        <v>2.149071518777133</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792045</v>
+        <v>3.828052928792043</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.042439114887476</v>
+        <v>-7.311809255206089</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.141123292330533</v>
+        <v>0.03337523620308769</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.123641339642993</v>
+        <v>-1.229851781535472</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.284270558813475</v>
+        <v>2.220544293677988</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919906</v>
+        <v>3.812453678919904</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.021289915984033</v>
+        <v>-7.290660056302646</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1572839501292354</v>
+        <v>0.04953589400179048</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.10249214073955</v>
+        <v>-1.208702582632029</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.304661056392867</v>
+        <v>2.240934791257379</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318091</v>
+        <v>3.748328408318089</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.777524474000589</v>
+        <v>-7.046894614319202</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2505708352696638</v>
+        <v>0.1428227791422185</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.10249214073955</v>
+        <v>-1.208702582632029</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.300441764739917</v>
+        <v>2.23671549960443</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057524</v>
+        <v>3.824311233057522</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.675761653723294</v>
+        <v>-6.945131794041907</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2934002773005977</v>
+        <v>0.1856522211731528</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.089273072347121</v>
+        <v>-1.1954835142396</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.310497519695391</v>
+        <v>2.246771254559903</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279184</v>
+        <v>3.826354974279182</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.425911259774219</v>
+        <v>-6.695281400092832</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3860825098639298</v>
+        <v>0.2783344537364845</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.089273072347121</v>
+        <v>-1.1954835142396</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.303239594679093</v>
+        <v>2.239513329543605</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011497</v>
+        <v>3.835957987011495</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.250019167306787</v>
+        <v>-6.519389307625399</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4600384703715514</v>
+        <v>0.3522904142441066</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.089273072347121</v>
+        <v>-1.1954835142396</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.306838718199741</v>
+        <v>2.243112453064254</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392985</v>
+        <v>3.780933911392983</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.078572704284324</v>
+        <v>-6.347942844602936</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5419445616350904</v>
+        <v>0.4341965055076455</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.9178266093246578</v>
+        <v>-1.024037051217137</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.423034102067773</v>
+        <v>2.359307836932286</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.77376522263278</v>
+        <v>3.773765222632778</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.004283138545984</v>
+        <v>-6.273653278864597</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.570680865546723</v>
+        <v>0.4629328094192782</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.8435370435863185</v>
+        <v>-0.9497474854787973</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.466628319127073</v>
+        <v>2.402902053991586</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883072</v>
+        <v>3.76461787988307</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.94064739631205</v>
+        <v>-6.210017536630662</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6008299634946144</v>
+        <v>0.4930819073671695</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.779901301352384</v>
+        <v>-0.8861117432448627</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.509504565521751</v>
+        <v>2.445778300386264</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074781</v>
+        <v>3.798814771074779</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.82922063698613</v>
+        <v>-6.098590777304742</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.626594926008778</v>
+        <v>0.5188468698813331</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.779901301352384</v>
+        <v>-0.8861117432448627</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.490698824305547</v>
+        <v>2.42697255917006</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.797694884242291</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.58879014018127</v>
+        <v>-5.858160280499882</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7245102013555993</v>
+        <v>0.6167621452281544</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.5394708045475237</v>
+        <v>-0.6456812464400025</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.636700199013341</v>
+        <v>2.572973933877853</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367684</v>
+        <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.516547572010075</v>
+        <v>-5.785917712328687</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7573365424588974</v>
+        <v>0.6495884863314525</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.5394708045475237</v>
+        <v>-0.6456812464400025</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.640629512848161</v>
+        <v>2.576903247712674</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879966</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.463549249728687</v>
+        <v>-5.732919390047299</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7792144552887925</v>
+        <v>0.6714663991613476</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.4841345455455849</v>
+        <v>-0.5903449874380636</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.674509852166664</v>
+        <v>2.610783587031177</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502338</v>
+        <v>3.848616626502336</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.35474436424896</v>
+        <v>-5.624114504567572</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.819734480700677</v>
+        <v>0.7119864245732321</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.4841345455455849</v>
+        <v>-0.5903449874380636</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.671507923386658</v>
+        <v>2.607781658251171</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675938</v>
+        <v>3.818668951675936</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.134723566211949</v>
+        <v>-5.404093706530562</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9093218369260954</v>
+        <v>0.8015737807986505</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.3429147004776046</v>
+        <v>-0.4491251423700834</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.75781886743806</v>
+        <v>2.694092602302573</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539949</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.001855877148672</v>
+        <v>-5.271226017467284</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9783630953532296</v>
+        <v>0.8706150392257848</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.3429147004776046</v>
+        <v>-0.4491251423700834</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.773713050239883</v>
+        <v>2.709986785104396</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496259</v>
+        <v>3.845047386496257</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.881682793784173</v>
+        <v>-5.151052934102785</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.027578173139331</v>
+        <v>0.9198301170118861</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.2227416171131057</v>
+        <v>-0.3289520590055844</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.846962744698884</v>
+        <v>2.783236479563397</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576996</v>
+        <v>3.791273551576994</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.737010648684436</v>
+        <v>-5.006380789003048</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.095535133740666</v>
+        <v>0.9877870776132212</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.07806947201336828</v>
+        <v>-0.184279913905847</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.943854134320167</v>
+        <v>2.88012786918468</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.7358392229421</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.796885476042128</v>
+        <v>-5.06625561636074</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.057622694199015</v>
+        <v>0.9498746380715701</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.1379442993710604</v>
+        <v>-0.2441547412635391</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.893966729306977</v>
+        <v>2.83024046417149</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674512</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.71008597826312</v>
+        <v>-4.979456118581732</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.114742986633184</v>
+        <v>1.006994930505739</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.1379442993710604</v>
+        <v>-0.2441547412635391</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.916367222629543</v>
+        <v>2.852640957494056</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430693</v>
+        <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.712555684724926</v>
+        <v>-4.981925825043538</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.113827505421874</v>
+        <v>1.006079449294429</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.1404140058328666</v>
+        <v>-0.2466244477253453</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.914957800125872</v>
+        <v>2.851231534990385</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432201960036</v>
+        <v>3.743220196003598</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.780925871048936</v>
+        <v>-5.050296011367548</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.097486353366972</v>
+        <v>0.9897382972395272</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.1311383067966516</v>
+        <v>-0.2373487486891304</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.931530142022303</v>
+        <v>2.867803876886815</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508368</v>
+        <v>3.714179139508366</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.88946405196507</v>
+        <v>-5.158834192283682</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.04450778963241</v>
+        <v>0.9367597335049647</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.1311383067966516</v>
+        <v>-0.2373487486891304</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.921966850654194</v>
+        <v>2.858240585518707</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417703</v>
+        <v>3.710906731417701</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.920457211293775</v>
+        <v>-5.189827351612387</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8568200909413144</v>
+        <v>0.7490720348138695</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.1311383067966516</v>
+        <v>-0.2373487486891304</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.746676415694581</v>
+        <v>2.682950150559094</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205901</v>
+        <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.744982951501306</v>
+        <v>-5.014353091819919</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9315770268500896</v>
+        <v>0.8238289707226447</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.1311383067966516</v>
+        <v>-0.2373487486891304</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.751243647686369</v>
+        <v>2.687517382550881</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225445</v>
+        <v>3.765024323225443</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.855919204142555</v>
+        <v>-5.125289344461168</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8629445545547971</v>
+        <v>0.755196498427352</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.1311383067966516</v>
+        <v>-0.2373487486891304</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.726985676447576</v>
+        <v>2.663259411312088</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111293</v>
+        <v>3.773210297111291</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.864201278287614</v>
+        <v>-5.133571418606226</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8627631101166793</v>
+        <v>0.7550150539892342</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.13942038094171</v>
+        <v>-0.2456308228341887</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.725147817180446</v>
+        <v>2.661421552044959</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264161</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.804348659083891</v>
+        <v>-5.073718799402503</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8968765442303008</v>
+        <v>0.7891284881028562</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.13942038094171</v>
+        <v>-0.2456308228341887</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.735320203612579</v>
+        <v>2.671593938477091</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.786949957742297</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.718105196057513</v>
+        <v>-4.987475336376125</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9263202000147124</v>
+        <v>0.8185721438872675</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.13942038094171</v>
+        <v>-0.2456308228341887</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.730266474186439</v>
+        <v>2.666540209050952</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.763412015456493</v>
+        <v>-5.032782155775105</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8999732476996458</v>
+        <v>0.7922251915722009</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.1802305439509408</v>
+        <v>-0.2864409858434195</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.697556151825426</v>
+        <v>2.633829886689939</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803189</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.792445120158794</v>
+        <v>-5.061815260477406</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8889118788518271</v>
+        <v>0.7811638227243822</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.1802305439509408</v>
+        <v>-0.2864409858434195</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.698108024858528</v>
+        <v>2.63438175972304</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809498</v>
+        <v>3.733390600809496</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.699634638707934</v>
+        <v>-4.969004779026546</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8553087633235366</v>
+        <v>0.7475607071960917</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.08742006250008144</v>
+        <v>-0.1936305043925602</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.683067005620409</v>
+        <v>2.619340740484922</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560424</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.744024108037362</v>
+        <v>-5.013394248355974</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8394264515163663</v>
+        <v>0.7316783953889217</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.1318095318295091</v>
+        <v>-0.2380199737219879</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.658306799947353</v>
+        <v>2.594580534811866</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472738</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.631352889801112</v>
+        <v>-4.900723030119724</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8795706473225895</v>
+        <v>0.7718225911951446</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.0191383135932589</v>
+        <v>-0.1253487554857377</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.720985239400826</v>
+        <v>2.657258974265339</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.518975888618439</v>
+        <v>-4.788346028937051</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9300127436263259</v>
+        <v>0.822264687498881</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.0191383135932589</v>
+        <v>-0.1253487554857377</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.726476535231493</v>
+        <v>2.662750270096006</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.546756286519791</v>
+        <v>-4.816126426838403</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9303977862343238</v>
+        <v>0.8226497301068789</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.04691871149461196</v>
+        <v>-0.1531291533870907</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.721305498259221</v>
+        <v>2.657579233123733</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705325</v>
+        <v>3.643069621705323</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.62975756754507</v>
+        <v>-4.899127707863682</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7355529938248655</v>
+        <v>0.6278049376974206</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.06548959602178572</v>
+        <v>-0.1717000379142645</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.54851868754357</v>
+        <v>2.484792422408082</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.68271631072927</v>
+        <v>3.682716310729268</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.738371645988401</v>
+        <v>-5.007741786307013</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8122570231667388</v>
+        <v>0.7045089670392939</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.06548959602178572</v>
+        <v>-0.1717000379142645</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.668668348262775</v>
+        <v>2.604942083127288</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190769</v>
+        <v>3.733012441190767</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.824970228969504</v>
+        <v>-5.094340369288116</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7921306160766206</v>
+        <v>0.6843825599491757</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.06548959602178572</v>
+        <v>-0.1717000379142645</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.683181374365098</v>
+        <v>2.619455109229611</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913426</v>
+        <v>3.741174069913424</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.786586566411353</v>
+        <v>-5.055956706729965</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8049035224422496</v>
+        <v>0.697155466314805</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.02710593346363455</v>
+        <v>-0.1333163753561133</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.703631013242358</v>
+        <v>2.63990474810687</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532487</v>
+        <v>3.751147197532485</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.609470236376187</v>
+        <v>-4.878840376694799</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8724790833016181</v>
+        <v>0.7647310271741732</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.02710593346363455</v>
+        <v>-0.1333163753561133</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.700360042087659</v>
+        <v>2.636633776952173</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793904</v>
+        <v>3.741328448793903</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.654562481209733</v>
+        <v>-4.923932621528345</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8551255771301127</v>
+        <v>0.7473775210026679</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.08900197663302434</v>
+        <v>-0.1952124185255031</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.663905807947939</v>
+        <v>2.600179542812452</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011238</v>
+        <v>3.750729377011236</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.475187059970965</v>
+        <v>-4.744557200289577</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9206627209320342</v>
+        <v>0.8129146648045893</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.06777478153769434</v>
+        <v>-0.03843566035478441</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.751758838156785</v>
+        <v>2.688032573021297</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982232</v>
+        <v>3.71699171898223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.520201273491571</v>
+        <v>-4.789571413810183</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8834644908553817</v>
+        <v>0.7757164347279368</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.03742588622308973</v>
+        <v>-0.06878455566938901</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.714356956299611</v>
+        <v>2.650630691164124</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509539</v>
+        <v>3.737026608509537</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.787205783764006</v>
+        <v>-5.056575924082618</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.7823542490853534</v>
+        <v>0.6746061929579086</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.1569371518198588</v>
+        <v>-0.2631475937123376</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.603430695812788</v>
+        <v>2.539704430677301</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760811</v>
+        <v>3.702309454760809</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.888403565201179</v>
+        <v>-5.157773705519791</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7410790584069857</v>
+        <v>0.6333310022795411</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.225345965365178</v>
+        <v>-0.3315564072576568</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.561589329582098</v>
+        <v>2.497863064446611</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815456</v>
+        <v>3.705571661815454</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.855927979030406</v>
+        <v>-5.125298119349019</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7516692544296113</v>
+        <v>0.6439211983021664</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.225345965365178</v>
+        <v>-0.3315564072576568</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.559189291136414</v>
+        <v>2.495463026000928</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378101</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.836889851323109</v>
+        <v>-5.106259991641721</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7558092247207753</v>
+        <v>0.6480611685933302</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.2835295766963726</v>
+        <v>-0.3897400185888513</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.520803843545943</v>
+        <v>2.457077578410455</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.868016482473728</v>
+        <v>-5.13738662279234</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9209404411992084</v>
+        <v>0.8131923850717637</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.2835295766963726</v>
+        <v>-0.3897400185888513</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.698385712484623</v>
+        <v>2.634659447349136</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067867</v>
+        <v>3.722447362067865</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.881883243807645</v>
+        <v>-5.151253384126258</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9162270656517748</v>
+        <v>0.8084790095243299</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.3213874934301955</v>
+        <v>-0.4275979353226743</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.676504291430463</v>
+        <v>2.612778026294976</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789124</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.902140542336603</v>
+        <v>-5.171510682655216</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9141326766371176</v>
+        <v>0.8063846205096725</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.3213874934301955</v>
+        <v>-0.4275979353226743</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.682512821827389</v>
+        <v>2.618786556691902</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519911</v>
+        <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.754397572101601</v>
+        <v>-5.023767712420213</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.052382512523141</v>
+        <v>0.9446344563956957</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.1535801361953124</v>
+        <v>-0.2597905780877911</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.862349883960341</v>
+        <v>2.798623618824854</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181174</v>
+        <v>3.802245929181172</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.856412254632822</v>
+        <v>-5.125782394951434</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.014370261042133</v>
+        <v>0.9066222049146879</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.1535801361953124</v>
+        <v>-0.2597905780877911</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.865143505491822</v>
+        <v>2.801417240356335</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394732</v>
+        <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.850259548580038</v>
+        <v>-5.11962968889865</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.017493691854905</v>
+        <v>0.90974563572746</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.1474274301425281</v>
+        <v>-0.2536378720350068</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.869497477515151</v>
+        <v>2.805771212379664</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.86706884673054</v>
+        <v>-5.136438987049152</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.009850449334815</v>
+        <v>0.9021023932073695</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.1642367282930297</v>
+        <v>-0.2704471701855085</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.85849237536496</v>
+        <v>2.794766110229473</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.804770847954417</v>
+        <v>-5.07414098827303</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.101105202642084</v>
+        <v>0.9933571465146396</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.1642367282930297</v>
+        <v>-0.2704471701855085</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.924827929161781</v>
+        <v>2.861101664026294</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992194</v>
+        <v>3.848729139992193</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.602980650289259</v>
+        <v>-4.872350790607872</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8904021540975455</v>
+        <v>0.7826540979701007</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.03378146387612468</v>
+        <v>-0.07242897801635406</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.752219716852672</v>
+        <v>2.688493451717184</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852423</v>
+        <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.543089968646666</v>
+        <v>-4.812460108965278</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.984648659076758</v>
+        <v>0.8769006029493132</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.09367214551871816</v>
+        <v>-0.01253829637376058</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.858444358160403</v>
+        <v>2.794718093024916</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319549</v>
+        <v>3.819063300319547</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.640830513271641</v>
+        <v>-4.910200653590253</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.960180177342812</v>
+        <v>0.8524321212153672</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.07778286738573797</v>
+        <v>-0.02842757450674077</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.863538527396658</v>
+        <v>2.799812262261171</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489386</v>
+        <v>3.831819032489384</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.81716827339457</v>
+        <v>-5.086538413713182</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8881810541183119</v>
+        <v>0.7804329979908671</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.09855489273719142</v>
+        <v>-0.2047653346296702</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.756271852147572</v>
+        <v>2.692545587012085</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397795</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.745621950617693</v>
+        <v>-5.014992090936305</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9152912012689913</v>
+        <v>0.8075431451415462</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.09855489273719142</v>
+        <v>-0.2047653346296702</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.754763470187501</v>
+        <v>2.691037205052014</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024963</v>
+        <v>3.836023391024962</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.701248818979124</v>
+        <v>-4.970618959297736</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.932903321359855</v>
+        <v>0.8251552652324101</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.05418176109862283</v>
+        <v>-0.1603922029911016</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.781250216606078</v>
+        <v>2.717523951470591</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863225</v>
+        <v>3.821591150863223</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.693294848684352</v>
+        <v>-4.962664989002964</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9360849094777639</v>
+        <v>0.828336853350319</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.05418176109862283</v>
+        <v>-0.1603922029911016</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.781250216606078</v>
+        <v>2.717523951470591</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947584</v>
+        <v>3.833040181947582</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.645639118123296</v>
+        <v>-4.915009258441908</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9615289587299909</v>
+        <v>0.853780902602546</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.006526030537567173</v>
+        <v>-0.1127364724300459</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.816225411970517</v>
+        <v>2.752499146835029</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326876</v>
+        <v>3.822707244326875</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.517954808329</v>
+        <v>-4.787324948647612</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.017495056022434</v>
+        <v>0.9097469998949892</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.1211582792567293</v>
+        <v>0.01494783736425054</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.897728371221819</v>
+        <v>2.834002106086332</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314552</v>
+        <v>3.82883791131455</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.578621398731389</v>
+        <v>-4.847991539050001</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.9799830923373505</v>
+        <v>0.8722350362099056</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.03945996253819561</v>
+        <v>-0.06675047935428313</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.835464053666571</v>
+        <v>2.771737788531084</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690028</v>
+        <v>3.816866067690026</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.533782997122991</v>
+        <v>-4.803153137441603</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.002016155591338</v>
+        <v>0.8942680994638936</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.04400339548306509</v>
+        <v>-0.06220704640941366</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.842287816044121</v>
+        <v>2.778561550908634</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674311</v>
+        <v>3.817961388674309</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.634541632879989</v>
+        <v>-4.903911773198601</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.9658736409196174</v>
+        <v>0.8581255847921725</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.04482217324394033</v>
+        <v>-0.1510326151364191</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.793153414438996</v>
+        <v>2.729427149303509</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.82671377916322</v>
+        <v>3.826713779163218</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.590338795794088</v>
+        <v>-4.859708936112701</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.9894343782818147</v>
+        <v>0.8816863221543698</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.0006193361580398848</v>
+        <v>-0.1068297780505186</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.825554719218374</v>
+        <v>2.761828454082886</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022905</v>
+        <v>3.838228663022903</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.627317823457531</v>
+        <v>-4.896687963776143</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.973052767685685</v>
+        <v>0.8653047115582402</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.03635456563329065</v>
+        <v>-0.0698558762591881</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.84614906076242</v>
+        <v>2.782422795626932</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042139</v>
+        <v>3.863924114042137</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.647375902322372</v>
+        <v>-4.916746042640984</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.016277301322789</v>
+        <v>0.9085292451953437</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.03635456563329065</v>
+        <v>-0.0698558762591881</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.897396825945459</v>
+        <v>2.833670560809972</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078282</v>
+        <v>3.86536771507828</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.607445229144481</v>
+        <v>-4.876815369463094</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.030690275188198</v>
+        <v>0.922942219060753</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.07628523881118099</v>
+        <v>-0.02992520308129776</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.919795934446447</v>
+        <v>2.856069669310959</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232399</v>
+        <v>3.864518876232397</v>
       </c>
       <c r="C1987" t="n">
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.556413136421954</v>
+        <v>-4.825783276740566</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.046051340515479</v>
+        <v>0.9383032843880339</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.1273173315337089</v>
+        <v>0.0211068896412302</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.945363418318233</v>
+        <v>2.881637153182746</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162115</v>
+        <v>3.842576394162113</v>
       </c>
       <c r="C1988" t="n">
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.491188955294748</v>
+        <v>-4.760559095613361</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.089328417059066</v>
+        <v>0.9815803609316212</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.1925415126609146</v>
+        <v>0.08633107076843582</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.001685331087262</v>
+        <v>2.937959065951774</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639819</v>
+        <v>3.840090220639818</v>
       </c>
       <c r="C1989" t="n">
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.541683245651805</v>
+        <v>-4.811053385970417</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.065091673215524</v>
+        <v>0.9573436170880789</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.1475207755348403</v>
+        <v>0.04131033364236159</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.970633861110898</v>
+        <v>2.90690759597541</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845198842749921</v>
+        <v>3.84519884274992</v>
       </c>
       <c r="C1990" t="n">
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.561794901686513</v>
+        <v>-4.831165042005125</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.058303803132881</v>
+        <v>0.950555747005436</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.1585481205322595</v>
+        <v>0.05233767863978078</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.978507060440589</v>
+        <v>2.914780795305102</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828690479393547</v>
+        <v>3.828690479393545</v>
       </c>
       <c r="C1991" t="n">
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.659475480959159</v>
+        <v>-4.928845621277771</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.179789342445033</v>
+        <v>1.072041286317588</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.04784492519207073</v>
+        <v>-0.05836551670040802</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.072642914257687</v>
+        <v>3.008916649122199</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714885</v>
+        <v>3.813251854714883</v>
       </c>
       <c r="C1992" t="n">
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.635683912353016</v>
+        <v>-4.905054052671629</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.309418879105307</v>
+        <v>1.201670822977863</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.07163649379821302</v>
+        <v>-0.03457394809426573</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.207030764639189</v>
+        <v>3.143304499503702</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814259761756012</v>
+        <v>3.81425976175601</v>
       </c>
       <c r="C1993" t="n">
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.672438330914739</v>
+        <v>-4.941808471233351</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.286425087694477</v>
+        <v>1.178677031567033</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.07163649379821302</v>
+        <v>-0.03457394809426573</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.198738740653048</v>
+        <v>3.135012475517561</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803426852654186</v>
+        <v>3.803426852654185</v>
       </c>
       <c r="C1994" t="n">
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.668104027857691</v>
+        <v>-4.937474168176303</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.286352004501076</v>
+        <v>1.178603948373631</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.2232865971174169</v>
+        <v>0.1170761552249382</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.28792199822835</v>
+        <v>3.224195733092863</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796293177717117</v>
+        <v>3.796293177717115</v>
       </c>
       <c r="C1995" t="n">
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.659211566464408</v>
+        <v>-4.92858170678302</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.307463394785181</v>
+        <v>1.199715338657736</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.2232865971174169</v>
+        <v>0.1170761552249382</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.305476403955141</v>
+        <v>3.241750138819654</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794453975702625</v>
+        <v>3.794453975702623</v>
       </c>
       <c r="C1996" t="n">
         <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.827687683434285</v>
+        <v>-5.097057823752897</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.231927995401814</v>
+        <v>1.124179939274369</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.1953387614008362</v>
+        <v>0.08912831950835742</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.280562749929777</v>
+        <v>3.21683648479429</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795603100539967</v>
+        <v>3.795603100539966</v>
       </c>
       <c r="C1997" t="n">
         <v>3.233772154546119</v>
       </c>
       <c r="D1997" t="n">
-        <v>-4.129888154572702</v>
+        <v>-4.399258294891315</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.58146046840329</v>
+        <v>1.473712412275846</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.1249907020304254</v>
+        <v>0.0187802601379467</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.308766575764374</v>
+        <v>3.245040310628887</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.793368797740295</v>
+        <v>3.447954131919267</v>
       </c>
       <c r="C1998" t="n">
         <v>3.224436177043023</v>
       </c>
       <c r="D1998" t="n">
-        <v>-4.234015631618478</v>
+        <v>-4.376537191208162</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.530473500081885</v>
+        <v>1.473464876246011</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.1249907020304254</v>
+        <v>0.0187802601379467</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.299430598261279</v>
+        <v>3.235704333125792</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240618.xlsx
+++ b/tame_output/ON/bt/strategyON_20240618.xlsx
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970902</v>
+        <v>3.304715716970903</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330521</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108637</v>
+        <v>3.305023265108638</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097819</v>
+        <v>3.34137872309782</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094115</v>
+        <v>3.374439043094116</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199284</v>
+        <v>3.405960511199285</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923085</v>
+        <v>3.419979433923086</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297747</v>
+        <v>3.458100091297748</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317614</v>
+        <v>3.447750501317615</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737167</v>
+        <v>3.503515506737168</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.50317028234131</v>
+        <v>3.503170282341311</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539461</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937496</v>
+        <v>3.492448711937497</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141698</v>
+        <v>3.502790399141699</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729889</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440631</v>
+        <v>3.499971739440632</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608598</v>
+        <v>3.490059241608599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410269</v>
+        <v>3.48587859441027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764394</v>
+        <v>3.480692492764395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390583</v>
+        <v>3.493716014390584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297396</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322541</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158919</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940717</v>
+        <v>3.691571733940718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770578</v>
+        <v>3.676841549770579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615281</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848438238121</v>
+        <v>3.684843823812101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646214</v>
+        <v>3.710935533646215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611566</v>
+        <v>3.768951674611567</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955325</v>
+        <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.74770266023241</v>
+        <v>3.747702660232412</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436226</v>
+        <v>3.766317079436228</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311947</v>
+        <v>3.784684521311949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.800829354097244</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017771</v>
+        <v>3.789311112017772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839722</v>
+        <v>3.833252747839724</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388725</v>
+        <v>3.839374447388727</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.856161751626473</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291808</v>
+        <v>3.78733042929181</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785785</v>
+        <v>3.801637122785786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390424</v>
+        <v>3.763182248390426</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105949</v>
+        <v>3.784718794105951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960983</v>
+        <v>3.753882571960985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607642</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.7704225839879</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710808</v>
+        <v>3.76033368671081</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409202</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098106</v>
+        <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493417</v>
+        <v>3.782922533493418</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722813</v>
+        <v>3.828551486722815</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792043</v>
+        <v>3.828052928792045</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919904</v>
+        <v>3.812453678919906</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318089</v>
+        <v>3.748328408318091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057522</v>
+        <v>3.824311233057524</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279182</v>
+        <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011495</v>
+        <v>3.835957987011497</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392983</v>
+        <v>3.780933911392985</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632778</v>
+        <v>3.77376522263278</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.76461787988307</v>
+        <v>3.764617879883072</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074779</v>
+        <v>3.798814771074781</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242291</v>
+        <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367682</v>
+        <v>3.821593509367684</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879964</v>
+        <v>3.822326997879966</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502336</v>
+        <v>3.848616626502338</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675936</v>
+        <v>3.818668951675938</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496257</v>
+        <v>3.845047386496259</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576994</v>
+        <v>3.791273551576996</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.7358392229421</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674512</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430691</v>
+        <v>3.729146398430693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003598</v>
+        <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508366</v>
+        <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417701</v>
+        <v>3.710906731417703</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
@@ -46142,7 +46142,7 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205899</v>
+        <v>3.746042526205901</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225443</v>
+        <v>3.765024323225445</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111291</v>
+        <v>3.773210297111293</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264161</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742297</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803189</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809496</v>
+        <v>3.733390600809498</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560424</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472736</v>
+        <v>3.721077195472738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705323</v>
+        <v>3.643069621705325</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729268</v>
+        <v>3.68271631072927</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
@@ -46464,7 +46464,7 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190767</v>
+        <v>3.733012441190769</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
@@ -46487,7 +46487,7 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913424</v>
+        <v>3.741174069913426</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
@@ -46510,7 +46510,7 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532485</v>
+        <v>3.751147197532487</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
@@ -46533,7 +46533,7 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793903</v>
+        <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
@@ -46556,7 +46556,7 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011236</v>
+        <v>3.750729377011238</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71699171898223</v>
+        <v>3.716991718982232</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
@@ -46602,7 +46602,7 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509537</v>
+        <v>3.737026608509539</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
@@ -46625,7 +46625,7 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760809</v>
+        <v>3.702309454760811</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
@@ -46648,7 +46648,7 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815454</v>
+        <v>3.705571661815456</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
@@ -46671,7 +46671,7 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.709510443378101</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
@@ -46694,7 +46694,7 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106447313125</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
@@ -46717,7 +46717,7 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067865</v>
+        <v>3.722447362067867</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
@@ -46740,7 +46740,7 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789124</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
@@ -46763,7 +46763,7 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519909</v>
+        <v>3.781501250519911</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
@@ -46786,7 +46786,7 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181172</v>
+        <v>3.802245929181174</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
@@ -46809,7 +46809,7 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394731</v>
+        <v>3.805608985394732</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
@@ -46832,7 +46832,7 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890611</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
@@ -46855,7 +46855,7 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
@@ -46878,7 +46878,7 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992193</v>
+        <v>3.848729139992194</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
@@ -46901,7 +46901,7 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852421</v>
+        <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
@@ -46924,7 +46924,7 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319547</v>
+        <v>3.819063300319549</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
@@ -46947,7 +46947,7 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489384</v>
+        <v>3.831819032489386</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
@@ -46970,7 +46970,7 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397795</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
@@ -46993,7 +46993,7 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024962</v>
+        <v>3.836023391024963</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
@@ -47016,7 +47016,7 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863223</v>
+        <v>3.821591150863225</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
@@ -47039,7 +47039,7 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947582</v>
+        <v>3.833040181947584</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
@@ -47062,7 +47062,7 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326875</v>
+        <v>3.822707244326876</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
@@ -47085,7 +47085,7 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.82883791131455</v>
+        <v>3.828837911314552</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
@@ -47108,7 +47108,7 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690026</v>
+        <v>3.816866067690028</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
@@ -47131,7 +47131,7 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674309</v>
+        <v>3.817961388674311</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
@@ -47154,7 +47154,7 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163218</v>
+        <v>3.82671377916322</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
@@ -47177,7 +47177,7 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022903</v>
+        <v>3.838228663022905</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
@@ -47200,7 +47200,7 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042137</v>
+        <v>3.863924114042139</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
@@ -47223,7 +47223,7 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86536771507828</v>
+        <v>3.865367715078282</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
@@ -47246,7 +47246,7 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232397</v>
+        <v>3.864518876232399</v>
       </c>
       <c r="C1987" t="n">
         <v>2.868973019398008</v>
@@ -47269,7 +47269,7 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162113</v>
+        <v>3.842576394162115</v>
       </c>
       <c r="C1988" t="n">
         <v>2.886160423490713</v>
@@ -47292,7 +47292,7 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639818</v>
+        <v>3.840090220639819</v>
       </c>
       <c r="C1989" t="n">
         <v>2.882121395789993</v>
@@ -47315,7 +47315,7 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.84519884274992</v>
+        <v>3.845198842749921</v>
       </c>
       <c r="C1990" t="n">
         <v>2.883378188121233</v>
@@ -47338,7 +47338,7 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828690479393545</v>
+        <v>3.828690479393547</v>
       </c>
       <c r="C1991" t="n">
         <v>3.043935959142444</v>
@@ -47361,7 +47361,7 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714883</v>
+        <v>3.813251854714885</v>
       </c>
       <c r="C1992" t="n">
         <v>3.164048868360261</v>
@@ -47384,7 +47384,7 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.81425976175601</v>
+        <v>3.814259761756012</v>
       </c>
       <c r="C1993" t="n">
         <v>3.15575684437412</v>
@@ -47407,7 +47407,7 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803426852654185</v>
+        <v>3.803426852654186</v>
       </c>
       <c r="C1994" t="n">
         <v>3.1539500399579</v>
@@ -47430,7 +47430,7 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796293177717115</v>
+        <v>3.796293177717117</v>
       </c>
       <c r="C1995" t="n">
         <v>3.171504445684691</v>
@@ -47453,7 +47453,7 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794453975702623</v>
+        <v>3.794453975702625</v>
       </c>
       <c r="C1996" t="n">
         <v>3.163359493089275</v>
@@ -47476,7 +47476,7 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795603100539966</v>
+        <v>3.795603100539967</v>
       </c>
       <c r="C1997" t="n">
         <v>3.233772154546119</v>
@@ -47499,7 +47499,7 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.447954131919267</v>
+        <v>3.447954131919269</v>
       </c>
       <c r="C1998" t="n">
         <v>3.224436177043023</v>

--- a/tame_output/ON/bt/strategyON_20240618.xlsx
+++ b/tame_output/ON/bt/strategyON_20240618.xlsx
@@ -605,7 +605,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>16.3%</t>
         </is>
       </c>
     </row>
@@ -758,26 +758,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>61.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,32 +844,32 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.5%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>-9.1%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.9%</t>
+          <t>-76.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.1%</t>
+          <t>108.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.5%</t>
+          <t>123.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.0%</t>
+          <t>93.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-52.2%</t>
+          <t>-51.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.3%</t>
+          <t>-72.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>90.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>449.7%</t>
+          <t>449.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-599.2%</t>
+          <t>-587.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>49.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.7%</t>
+          <t>-40.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-23.4%</t>
+          <t>-17.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-33.6%</t>
+          <t>-646.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-228.9%</t>
+          <t>-224.2%</t>
         </is>
       </c>
     </row>
@@ -1232,26 +1232,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-22.5%</t>
+          <t>-20.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.6%</t>
+          <t>-32.0%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-15.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>-39.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-170.4%</t>
+          <t>-2138.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-222.1%</t>
+          <t>-211.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-06-17</t>
+          <t>2024-06-18</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>96.0%</t>
+          <t>95.7%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-28.1%</t>
+          <t>-27.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-15.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-122.5%</t>
+          <t>-144.2%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1998"/>
+  <dimension ref="A1:G1999"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.915492735990862</v>
+        <v>-5.814271147034907</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7508709422129893</v>
+        <v>0.7913595777953715</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.8432755328774175</v>
+        <v>-0.7370650909849382</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.611459141196631</v>
+        <v>2.675185406332119</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.280620118629608</v>
+        <v>-6.179398529673653</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.604074504163322</v>
+        <v>0.6445631397457041</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.13958631717643</v>
+        <v>-1.033375875283951</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.432927185623055</v>
+        <v>2.496653450758542</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.689208895810287</v>
+        <v>-6.587987306854332</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4394005373058096</v>
+        <v>0.4798891728881913</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.548175094357108</v>
+        <v>-1.441964652464629</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.186535463329407</v>
+        <v>2.250261728464894</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.96578499612612</v>
+        <v>-6.864563407170165</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3239555296509371</v>
+        <v>0.3644441652333192</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.548175094357108</v>
+        <v>-1.441964652464629</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.181720895800868</v>
+        <v>2.245447160936355</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.382176870413117</v>
+        <v>-7.280955281457162</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1553928305450154</v>
+        <v>0.1958814661273975</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.548175094357108</v>
+        <v>-1.441964652464629</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.179714946409745</v>
+        <v>2.243441211545232</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.652942959505762</v>
+        <v>-7.551721370549807</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.0573450855766362</v>
+        <v>0.09783372115901834</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.548175094357108</v>
+        <v>-1.441964652464629</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.189973637078424</v>
+        <v>2.253699902213911</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.998817781490571</v>
+        <v>-7.897596192534616</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.08490527807159198</v>
+        <v>-0.04441664248920985</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.548175094357108</v>
+        <v>-1.441964652464629</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.186073202224119</v>
+        <v>2.249799467359606</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.162397659674955</v>
+        <v>-8.061176070719</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1519323092903444</v>
+        <v>-0.1114436737079627</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.548175094357108</v>
+        <v>-1.441964652464629</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.18447812227912</v>
+        <v>2.248204387414607</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.459059001485153</v>
+        <v>-8.357837412529198</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2668178700852155</v>
+        <v>-0.2263292345028338</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.616918230090987</v>
+        <v>-1.510707788198508</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.147011216768001</v>
+        <v>2.210737481903489</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.645778709794456</v>
+        <v>-8.544557120838501</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3455320579433399</v>
+        <v>-0.3050434223609582</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.616918230090987</v>
+        <v>-1.510707788198508</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.142984912233598</v>
+        <v>2.206711177369086</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.028780098537087</v>
+        <v>-8.927558509581132</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4988347147619763</v>
+        <v>-0.4583460791795946</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.616918230090987</v>
+        <v>-1.510707788198508</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.142882810912014</v>
+        <v>2.206609076047501</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.210649889522122</v>
+        <v>-9.109428300566167</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5690111151845603</v>
+        <v>-0.5285224796021781</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.798788021076022</v>
+        <v>-1.692577579183543</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.036332452292423</v>
+        <v>2.100058717427911</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.570180212026123</v>
+        <v>-9.468958623070169</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.7074729408881106</v>
+        <v>-0.6669843053057285</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.798788021076022</v>
+        <v>-1.692577579183543</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.041682755590473</v>
+        <v>2.10540902072596</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.620529275480346</v>
+        <v>-9.519307686524391</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.7196965463126221</v>
+        <v>-0.67920791073024</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.849137084530244</v>
+        <v>-1.742926642637765</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.019389337475118</v>
+        <v>2.083115602610605</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.718148552901742</v>
+        <v>-9.616926963945787</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7557025066594116</v>
+        <v>-0.7152138710770295</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.946756361951641</v>
+        <v>-1.840545920059162</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.963859521644048</v>
+        <v>2.027585786779536</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.865674640907384</v>
+        <v>-9.764453051951429</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8118193855400966</v>
+        <v>-0.7713307499577144</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.094282449957284</v>
+        <v>-1.988072008064805</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.878237425162234</v>
+        <v>1.941963690297722</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.06993281623725</v>
+        <v>-9.968711227281293</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.8880094585534</v>
+        <v>-0.8475208229710178</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.221921394571273</v>
+        <v>-2.115710952678794</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.807167255512484</v>
+        <v>1.870893520647971</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.14426579249741</v>
+        <v>-10.04304420354146</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.9132600945730291</v>
+        <v>-0.872771458990647</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.366620918505946</v>
+        <v>-2.260410476613467</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.724830095636116</v>
+        <v>1.788556360771603</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.07079596082996</v>
+        <v>-9.969574371874009</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.868500460412629</v>
+        <v>-0.8280118248302468</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.293151086838497</v>
+        <v>-2.186940644946018</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.784283696130006</v>
+        <v>1.848009961265493</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.24592037821651</v>
+        <v>-10.14469878926055</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9239950066197293</v>
+        <v>-0.8835063710373472</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.468275504225041</v>
+        <v>-2.362065062332562</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.693764266445597</v>
+        <v>1.757490531581084</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.480372472231</v>
+        <v>-10.37915088327504</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.024995009127121</v>
+        <v>-0.9845063735447392</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.468275504225041</v>
+        <v>-2.362065062332562</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.686545101544001</v>
+        <v>1.750271366679488</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.58474720325744</v>
+        <v>-10.48352561430149</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.073417092311676</v>
+        <v>-1.032928456729294</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.572650235251487</v>
+        <v>-2.466439793359008</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.617248072154157</v>
+        <v>1.680974337289644</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.63753335885777</v>
+        <v>-10.53631176990181</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.09341576471325</v>
+        <v>-1.052927129130868</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.668325721833884</v>
+        <v>-2.562115279941405</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.560958570043275</v>
+        <v>1.624684835178763</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.76357015222606</v>
+        <v>-10.6623485632701</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.141136753431451</v>
+        <v>-1.100648117849069</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.643074099024141</v>
+        <v>-2.536863657131662</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.578803272358235</v>
+        <v>1.642529537493723</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.71155463825725</v>
+        <v>-10.61033304930129</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.116340212157525</v>
+        <v>-1.075851576575143</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.643074099024141</v>
+        <v>-2.536863657131662</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.582793608044636</v>
+        <v>1.646519873180124</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.85322647998137</v>
+        <v>-10.75200489102541</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.174484175745915</v>
+        <v>-1.133995540163533</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.643074099024141</v>
+        <v>-2.536863657131662</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.581318381145894</v>
+        <v>1.645044646281382</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.80363563555653</v>
+        <v>-10.70241404660058</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.139594427811109</v>
+        <v>-1.099105792228727</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.593483254599307</v>
+        <v>-2.487272812706828</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.626126297965667</v>
+        <v>1.689852563101155</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.79082824255176</v>
+        <v>-10.6896066535958</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.147522604255883</v>
+        <v>-1.1070339686735</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.642339029608209</v>
+        <v>-2.53612858771573</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.583761699313643</v>
+        <v>1.647487964449131</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.56498308983235</v>
+        <v>-10.46376150087639</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.047605470131909</v>
+        <v>-1.007116834549527</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.600412354021045</v>
+        <v>-2.494201912128566</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.61849677770215</v>
+        <v>1.682223042837638</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.44040443349475</v>
+        <v>-10.3391828445388</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9966348630408128</v>
+        <v>-0.9561462274584316</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.600412354021045</v>
+        <v>-2.494201912128566</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.619635922258209</v>
+        <v>1.683362187393697</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.49329972153904</v>
+        <v>-10.39207813258309</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.01515920409642</v>
+        <v>-0.9746705685140382</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.595457007932599</v>
+        <v>-2.48924656604012</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.625242904073384</v>
+        <v>1.688969169208872</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.42116654625116</v>
+        <v>-10.3199449572952</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9805722297426316</v>
+        <v>-0.9400835941602494</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.595457007932599</v>
+        <v>-2.48924656604012</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.630976608312021</v>
+        <v>1.694702873447508</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.34980015364151</v>
+        <v>-10.24857856468556</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9617629350926373</v>
+        <v>-0.9212742995102552</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.524090615322951</v>
+        <v>-2.417880173430472</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.664059181483945</v>
+        <v>1.727785446619432</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232412</v>
+        <v>3.747702660232411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.25634111965629</v>
+        <v>-10.15511953070033</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.9342628028114555</v>
+        <v>-0.8937741672290733</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.524090615322951</v>
+        <v>-2.417880173430472</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.654175700171037</v>
+        <v>1.717901965306524</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436228</v>
+        <v>3.766317079436227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.15724787015055</v>
+        <v>-10.04053749437869</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.8964600635085334</v>
+        <v>-0.8497759131997902</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.524090615322951</v>
+        <v>-2.417880173430472</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.652341139671663</v>
+        <v>1.716067404807151</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311949</v>
+        <v>3.784684521311948</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.05934083147406</v>
+        <v>-9.942630455702199</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8575975630113981</v>
+        <v>-0.8109134127026545</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.456104865462394</v>
+        <v>-2.349894423569915</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.692832274614536</v>
+        <v>1.756558539750024</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.0353872904981</v>
+        <v>-9.918676914726241</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8473476404755211</v>
+        <v>-0.8006634901667775</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.432151324486437</v>
+        <v>-2.325940882593958</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.707872905345605</v>
+        <v>1.771599170481092</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.771327352175303</v>
+        <v>-9.654616976403444</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.7549839813081549</v>
+        <v>-0.7082998309994109</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.168091386163641</v>
+        <v>-2.061880944271162</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.85304855217753</v>
+        <v>1.916774817313017</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.064247728670466</v>
+        <v>-8.947537352898607</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.4749391655665205</v>
+        <v>-0.4282550152577769</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.168091386163641</v>
+        <v>-2.061880944271162</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.850261518517229</v>
+        <v>1.913987783652717</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.024063430304276</v>
+        <v>-8.907353054532416</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.458521822332203</v>
+        <v>-0.4118376720234593</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.12790708779745</v>
+        <v>-2.021696645904971</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.874715721424785</v>
+        <v>1.938441986560273</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.860663559364912</v>
+        <v>-8.743953183593053</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.393795052735701</v>
+        <v>-0.347110902426957</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.964507216858087</v>
+        <v>-1.858296774965608</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.972122465209159</v>
+        <v>2.035848730344647</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.627182337135313</v>
+        <v>-8.510471961363454</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.2924781350060086</v>
+        <v>-0.245793984697265</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.731025994628489</v>
+        <v>-1.62481555273601</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.120135627384771</v>
+        <v>2.183861892520258</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.477515946127799</v>
+        <v>-8.360805570355939</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.2355037889159624</v>
+        <v>-0.1888196386072183</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.638122503385953</v>
+        <v>-1.531912061493474</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.172985511817333</v>
+        <v>2.236711776952821</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.345240472496911</v>
+        <v>-8.228530096725052</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.1872261127165804</v>
+        <v>-0.1405419624078363</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.505847029755066</v>
+        <v>-1.399636587862587</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.247718282742892</v>
+        <v>2.31144454787838</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.154640797823758</v>
+        <v>-8.037930422051899</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.108171182159682</v>
+        <v>-0.0614870318509384</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.315247355081913</v>
+        <v>-1.209036913189434</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.364893148234421</v>
+        <v>2.428619413369908</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.905640999140177</v>
+        <v>-7.788930623368318</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.00433507853740922</v>
+        <v>0.05101922884615284</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.315247355081913</v>
+        <v>-1.209036913189434</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.377799489458079</v>
+        <v>2.441525754593567</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.011230988913281</v>
+        <v>-7.894520613141422</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.1658768469710514</v>
+        <v>-0.1191926966623078</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.420837344855018</v>
+        <v>-1.314626902962539</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.186469565994998</v>
+        <v>2.250195831130485</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.029965891031878</v>
+        <v>-7.913255515260019</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.1248264659414038</v>
+        <v>-0.07814231563266016</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.426433354515149</v>
+        <v>-1.32022291262267</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.231656302076006</v>
+        <v>2.295382567211493</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.882025849624279</v>
+        <v>-7.76531547385242</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1855293720665316</v>
+        <v>-0.138845221757788</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.406112438606591</v>
+        <v>-1.299901996714112</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.123969928932973</v>
+        <v>2.18769619406846</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.82905632737029</v>
+        <v>-7.712345951598431</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.1730555494184145</v>
+        <v>-0.1263713991096709</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.353142916352602</v>
+        <v>-1.246932474460123</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.147037656031888</v>
+        <v>2.210763921167375</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.7855079205996</v>
+        <v>-7.668797544827741</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.1625967988052315</v>
+        <v>-0.1159126484964879</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.353142916352602</v>
+        <v>-1.246932474460123</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.140077043936795</v>
+        <v>2.203803309072282</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.543359527145742</v>
+        <v>-7.426649151373883</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.05127508704254513</v>
+        <v>-0.004590936733801509</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.353142916352602</v>
+        <v>-1.246932474460123</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.154539398317938</v>
+        <v>2.218265663453425</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.43510039002322</v>
+        <v>-7.318390014251361</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.01343931173434143</v>
+        <v>0.03324483857440219</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.353142916352602</v>
+        <v>-1.246932474460123</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.149071518777133</v>
+        <v>2.21279778391262</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.311809255206089</v>
+        <v>-7.19509887943423</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.03337523620308769</v>
+        <v>0.08005938651183131</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.229851781535472</v>
+        <v>-1.123641339642993</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.220544293677988</v>
+        <v>2.284270558813475</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.290660056302646</v>
+        <v>-7.173949680530787</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.04953589400179048</v>
+        <v>0.0962200443105341</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.208702582632029</v>
+        <v>-1.10249214073955</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.240934791257379</v>
+        <v>2.304661056392867</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.046894614319202</v>
+        <v>-6.930184238547342</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.1428227791422185</v>
+        <v>0.1895069294509626</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.208702582632029</v>
+        <v>-1.10249214073955</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.23671549960443</v>
+        <v>2.300441764739917</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.945131794041907</v>
+        <v>-6.828421418270048</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1856522211731528</v>
+        <v>0.2323363714818965</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.1954835142396</v>
+        <v>-1.089273072347121</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.246771254559903</v>
+        <v>2.310497519695391</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.695281400092832</v>
+        <v>-6.578571024320973</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.2783344537364845</v>
+        <v>0.3250186040452285</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.1954835142396</v>
+        <v>-1.089273072347121</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.239513329543605</v>
+        <v>2.303239594679093</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.519389307625399</v>
+        <v>-6.40267893185354</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3522904142441066</v>
+        <v>0.3989745645528502</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.1954835142396</v>
+        <v>-1.089273072347121</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.243112453064254</v>
+        <v>2.306838718199741</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.347942844602936</v>
+        <v>-6.231232468831077</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4341965055076455</v>
+        <v>0.4808806558163892</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.024037051217137</v>
+        <v>-0.9178266093246578</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.359307836932286</v>
+        <v>2.423034102067773</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.273653278864597</v>
+        <v>-6.156942903092737</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.4629328094192782</v>
+        <v>0.5096169597280218</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.9497474854787973</v>
+        <v>-0.8435370435863185</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.402902053991586</v>
+        <v>2.466628319127073</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.210017536630662</v>
+        <v>-6.093307160858803</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.4930819073671695</v>
+        <v>0.5397660576759131</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.8861117432448627</v>
+        <v>-0.779901301352384</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.445778300386264</v>
+        <v>2.509504565521751</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.098590777304742</v>
+        <v>-5.981880401532883</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5188468698813331</v>
+        <v>0.5655310201900767</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.8861117432448627</v>
+        <v>-0.779901301352384</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.42697255917006</v>
+        <v>2.490698824305547</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.858160280499882</v>
+        <v>-5.741449904728023</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6167621452281544</v>
+        <v>0.6634462955368985</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.6456812464400025</v>
+        <v>-0.5394708045475237</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.572973933877853</v>
+        <v>2.636700199013341</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.785917712328687</v>
+        <v>-5.669207336556828</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6495884863314525</v>
+        <v>0.6962726366401966</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.6456812464400025</v>
+        <v>-0.5394708045475237</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.576903247712674</v>
+        <v>2.640629512848161</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.732919390047299</v>
+        <v>-5.61620901427544</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6714663991613476</v>
+        <v>0.7181505494700917</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.5903449874380636</v>
+        <v>-0.4841345455455849</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.610783587031177</v>
+        <v>2.674509852166664</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.624114504567572</v>
+        <v>-5.507404128795713</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7119864245732321</v>
+        <v>0.7586705748819758</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.5903449874380636</v>
+        <v>-0.4841345455455849</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.607781658251171</v>
+        <v>2.671507923386658</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.404093706530562</v>
+        <v>-5.287383330758702</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8015737807986505</v>
+        <v>0.8482579311073941</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4491251423700834</v>
+        <v>-0.3429147004776046</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.694092602302573</v>
+        <v>2.75781886743806</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.271226017467284</v>
+        <v>-5.154515641695425</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.8706150392257848</v>
+        <v>0.9172991895345284</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4491251423700834</v>
+        <v>-0.3429147004776046</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.709986785104396</v>
+        <v>2.773713050239883</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.151052934102785</v>
+        <v>-5.034342558330926</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9198301170118861</v>
+        <v>0.9665142673206297</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.3289520590055844</v>
+        <v>-0.2227416171131057</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.783236479563397</v>
+        <v>2.846962744698884</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-5.006380789003048</v>
+        <v>-4.889670413231189</v>
       </c>
       <c r="E1932" t="n">
-        <v>0.9877870776132212</v>
+        <v>1.034471227921965</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.184279913905847</v>
+        <v>-0.07806947201336828</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.88012786918468</v>
+        <v>2.943854134320167</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-5.06625561636074</v>
+        <v>-4.949545240588881</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.9498746380715701</v>
+        <v>0.9965587883803138</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.2441547412635391</v>
+        <v>-0.1379442993710604</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.83024046417149</v>
+        <v>2.893966729306977</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.979456118581732</v>
+        <v>-4.862745742809873</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.006994930505739</v>
+        <v>1.053679080814483</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.2441547412635391</v>
+        <v>-0.1379442993710604</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.852640957494056</v>
+        <v>2.916367222629543</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.981925825043538</v>
+        <v>-4.865215449271679</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.006079449294429</v>
+        <v>1.052763599603173</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.2466244477253453</v>
+        <v>-0.1404140058328666</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.851231534990385</v>
+        <v>2.914957800125872</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-5.050296011367548</v>
+        <v>-4.933585635595689</v>
       </c>
       <c r="E1936" t="n">
-        <v>0.9897382972395272</v>
+        <v>1.036422447548271</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.2373487486891304</v>
+        <v>-0.1311383067966516</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.867803876886815</v>
+        <v>2.931530142022303</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-5.158834192283682</v>
+        <v>-5.042123816511823</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.9367597335049647</v>
+        <v>0.9834438838137083</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.2373487486891304</v>
+        <v>-0.1311383067966516</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.858240585518707</v>
+        <v>2.921966850654194</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.189827351612387</v>
+        <v>-5.073116975840528</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.7490720348138695</v>
+        <v>0.7957561851226131</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.2373487486891304</v>
+        <v>-0.1311383067966516</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.682950150559094</v>
+        <v>2.746676415694581</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-5.014353091819919</v>
+        <v>-4.897642716048059</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.8238289707226447</v>
+        <v>0.8705131210313883</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.2373487486891304</v>
+        <v>-0.1311383067966516</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.687517382550881</v>
+        <v>2.751243647686369</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-5.125289344461168</v>
+        <v>-5.008578968689308</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.755196498427352</v>
+        <v>0.8018806487360959</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.2373487486891304</v>
+        <v>-0.1311383067966516</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.663259411312088</v>
+        <v>2.726985676447576</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.133571418606226</v>
+        <v>-5.016861042834367</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.7550150539892342</v>
+        <v>0.8016992042979783</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.2456308228341887</v>
+        <v>-0.13942038094171</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.661421552044959</v>
+        <v>2.725147817180446</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-5.073718799402503</v>
+        <v>-4.957008423630644</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.7891284881028562</v>
+        <v>0.8358126384115998</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.2456308228341887</v>
+        <v>-0.13942038094171</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.671593938477091</v>
+        <v>2.735320203612579</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.987475336376125</v>
+        <v>-4.870764960604266</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8185721438872675</v>
+        <v>0.8652562941960111</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.2456308228341887</v>
+        <v>-0.13942038094171</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.666540209050952</v>
+        <v>2.730266474186439</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-5.032782155775105</v>
+        <v>-4.916071780003246</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.7922251915722009</v>
+        <v>0.8389093418809448</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.2864409858434195</v>
+        <v>-0.1802305439509408</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.633829886689939</v>
+        <v>2.697556151825426</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-5.061815260477406</v>
+        <v>-4.945104884705547</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.7811638227243822</v>
+        <v>0.8278479730331259</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.2864409858434195</v>
+        <v>-0.1802305439509408</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.63438175972304</v>
+        <v>2.698108024858528</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.969004779026546</v>
+        <v>-4.852294403254687</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.7475607071960917</v>
+        <v>0.7942448575048353</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.1936305043925602</v>
+        <v>-0.08742006250008144</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.619340740484922</v>
+        <v>2.683067005620409</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-5.013394248355974</v>
+        <v>-4.896683872584115</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.7316783953889217</v>
+        <v>0.7783625456976653</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.2380199737219879</v>
+        <v>-0.1318095318295091</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.594580534811866</v>
+        <v>2.658306799947353</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.900723030119724</v>
+        <v>-4.784012654347864</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.7718225911951446</v>
+        <v>0.8185067415038882</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.1253487554857377</v>
+        <v>-0.0191383135932589</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.657258974265339</v>
+        <v>2.720985239400826</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.788346028937051</v>
+        <v>-4.671635653165191</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.822264687498881</v>
+        <v>0.8689488378076247</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.1253487554857377</v>
+        <v>-0.0191383135932589</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.662750270096006</v>
+        <v>2.726476535231493</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.816126426838403</v>
+        <v>-4.699416051066544</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8226497301068789</v>
+        <v>0.8693338804156228</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1531291533870907</v>
+        <v>-0.04691871149461196</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.657579233123733</v>
+        <v>2.721305498259221</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.899127707863682</v>
+        <v>-4.782417332091823</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6278049376974206</v>
+        <v>0.6744890880061645</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.1717000379142645</v>
+        <v>-0.06548959602178572</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.484792422408082</v>
+        <v>2.54851868754357</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-5.007741786307013</v>
+        <v>-4.891031410535154</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7045089670392939</v>
+        <v>0.7511931173480375</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.1717000379142645</v>
+        <v>-0.06548959602178572</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.604942083127288</v>
+        <v>2.668668348262775</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.094340369288116</v>
+        <v>-4.977629993516257</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.6843825599491757</v>
+        <v>0.7310667102579194</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.1717000379142645</v>
+        <v>-0.06548959602178572</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.619455109229611</v>
+        <v>2.683181374365098</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.055956706729965</v>
+        <v>-4.939246330958106</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.697155466314805</v>
+        <v>0.7438396166235486</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.1333163753561133</v>
+        <v>-0.02710593346363455</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.63990474810687</v>
+        <v>2.703631013242358</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.878840376694799</v>
+        <v>-4.76213000092294</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.7647310271741732</v>
+        <v>0.8114151774829168</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.1333163753561133</v>
+        <v>-0.02710593346363455</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.636633776952173</v>
+        <v>2.700360042087659</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.923932621528345</v>
+        <v>-4.807222245756486</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.7473775210026679</v>
+        <v>0.7940616713114117</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.1952124185255031</v>
+        <v>-0.08900197663302434</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.600179542812452</v>
+        <v>2.663905807947939</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.744557200289577</v>
+        <v>-4.627846824517718</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.8129146648045893</v>
+        <v>0.8595988151133331</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.03843566035478441</v>
+        <v>0.06777478153769434</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.688032573021297</v>
+        <v>2.751758838156785</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.789571413810183</v>
+        <v>-4.672861038038324</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.7757164347279368</v>
+        <v>0.8224005850366805</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.06878455566938901</v>
+        <v>0.03742588622308973</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.650630691164124</v>
+        <v>2.714356956299611</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.056575924082618</v>
+        <v>-4.939865548310759</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.6746061929579086</v>
+        <v>0.7212903432666522</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2631475937123376</v>
+        <v>-0.1569371518198588</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.539704430677301</v>
+        <v>2.603430695812788</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.157773705519791</v>
+        <v>-5.041063329747931</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.6333310022795411</v>
+        <v>0.6800151525882847</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.3315564072576568</v>
+        <v>-0.225345965365178</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.497863064446611</v>
+        <v>2.561589329582098</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.125298119349019</v>
+        <v>-5.008587743577159</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.6439211983021664</v>
+        <v>0.6906053486109103</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.3315564072576568</v>
+        <v>-0.225345965365178</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.495463026000928</v>
+        <v>2.559189291136414</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.106259991641721</v>
+        <v>-4.989549615869862</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.6480611685933302</v>
+        <v>0.694745318902074</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3897400185888513</v>
+        <v>-0.2835295766963726</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.457077578410455</v>
+        <v>2.520803843545943</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.13738662279234</v>
+        <v>-5.02067624702048</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.8131923850717637</v>
+        <v>0.8598765353805073</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3897400185888513</v>
+        <v>-0.2835295766963726</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.634659447349136</v>
+        <v>2.698385712484623</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.151253384126258</v>
+        <v>-5.034543008354398</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.8084790095243299</v>
+        <v>0.8551631598330736</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4275979353226743</v>
+        <v>-0.3213874934301955</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.612778026294976</v>
+        <v>2.676504291430463</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.171510682655216</v>
+        <v>-5.054800306883356</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.8063846205096725</v>
+        <v>0.8530687708184166</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.4275979353226743</v>
+        <v>-0.3213874934301955</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.618786556691902</v>
+        <v>2.682512821827389</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.023767712420213</v>
+        <v>-4.907057336648354</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9446344563956957</v>
+        <v>0.9913186067044393</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2597905780877911</v>
+        <v>-0.1535801361953124</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.798623618824854</v>
+        <v>2.862349883960341</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.125782394951434</v>
+        <v>-5.009072019179575</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9066222049146879</v>
+        <v>0.953306355223432</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.2597905780877911</v>
+        <v>-0.1535801361953124</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.801417240356335</v>
+        <v>2.865143505491822</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.11962968889865</v>
+        <v>-5.002919313126791</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.90974563572746</v>
+        <v>0.9564297860362039</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.2536378720350068</v>
+        <v>-0.1474274301425281</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.805771212379664</v>
+        <v>2.869497477515151</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.136438987049152</v>
+        <v>-5.019728611277293</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9021023932073695</v>
+        <v>0.9487865435161136</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.2704471701855085</v>
+        <v>-0.1642367282930297</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.794766110229473</v>
+        <v>2.85849237536496</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.07414098827303</v>
+        <v>-4.95743061250117</v>
       </c>
       <c r="E1970" t="n">
-        <v>0.9933571465146396</v>
+        <v>1.040041296823383</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.2704471701855085</v>
+        <v>-0.1642367282930297</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.861101664026294</v>
+        <v>2.924827929161781</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.872350790607872</v>
+        <v>-4.755640414836012</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.7826540979701007</v>
+        <v>0.8293382482788445</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.07242897801635406</v>
+        <v>0.03378146387612468</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.688493451717184</v>
+        <v>2.752219716852672</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.812460108965278</v>
+        <v>-4.695749733193419</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.8769006029493132</v>
+        <v>0.923584753258057</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.01253829637376058</v>
+        <v>0.09367214551871816</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.794718093024916</v>
+        <v>2.858444358160403</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.910200653590253</v>
+        <v>-4.793490277818393</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.8524321212153672</v>
+        <v>0.8991162715241108</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.02842757450674077</v>
+        <v>0.07778286738573797</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.799812262261171</v>
+        <v>2.863538527396658</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.086538413713182</v>
+        <v>-4.969828037941323</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.7804329979908671</v>
+        <v>0.8271171482996107</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.2047653346296702</v>
+        <v>-0.09855489273719142</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.692545587012085</v>
+        <v>2.756271852147572</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.014992090936305</v>
+        <v>-4.898281715164446</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8075431451415462</v>
+        <v>0.8542272954502901</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.2047653346296702</v>
+        <v>-0.09855489273719142</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.691037205052014</v>
+        <v>2.754763470187501</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.970618959297736</v>
+        <v>-4.853908583525877</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8251552652324101</v>
+        <v>0.8718394155411537</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.1603922029911016</v>
+        <v>-0.05418176109862283</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.717523951470591</v>
+        <v>2.781250216606078</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.962664989002964</v>
+        <v>-4.845954613231105</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.828336853350319</v>
+        <v>0.8750210036590627</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.1603922029911016</v>
+        <v>-0.05418176109862283</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.717523951470591</v>
+        <v>2.781250216606078</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.915009258441908</v>
+        <v>-4.798298882670049</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.853780902602546</v>
+        <v>0.9004650529112896</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.1127364724300459</v>
+        <v>-0.006526030537567173</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.752499146835029</v>
+        <v>2.816225411970517</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.787324948647612</v>
+        <v>-4.670614572875753</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.9097469998949892</v>
+        <v>0.956431150203733</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.01494783736425054</v>
+        <v>0.1211582792567293</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.834002106086332</v>
+        <v>2.897728371221819</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.847991539050001</v>
+        <v>-4.731281163278142</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.8722350362099056</v>
+        <v>0.9189191865186495</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.06675047935428313</v>
+        <v>0.03945996253819561</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.771737788531084</v>
+        <v>2.835464053666571</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.803153137441603</v>
+        <v>-4.686442761669744</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.8942680994638936</v>
+        <v>0.9409522497726375</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.06220704640941366</v>
+        <v>0.04400339548306509</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.778561550908634</v>
+        <v>2.842287816044121</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.903911773198601</v>
+        <v>-4.787201397426742</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.8581255847921725</v>
+        <v>0.9048097351009161</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.1510326151364191</v>
+        <v>-0.04482217324394033</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.729427149303509</v>
+        <v>2.793153414438996</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.859708936112701</v>
+        <v>-4.742998560340841</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.8816863221543698</v>
+        <v>0.9283704724631134</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.1068297780505186</v>
+        <v>-0.0006193361580398848</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.761828454082886</v>
+        <v>2.825554719218374</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.896687963776143</v>
+        <v>-4.779977588004284</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.8653047115582402</v>
+        <v>0.911988861866984</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.0698558762591881</v>
+        <v>0.03635456563329065</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.782422795626932</v>
+        <v>2.84614906076242</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.916746042640984</v>
+        <v>-4.800035666869125</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.9085292451953437</v>
+        <v>0.9552133955040873</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.0698558762591881</v>
+        <v>0.03635456563329065</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.833670560809972</v>
+        <v>2.897396825945459</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.876815369463094</v>
+        <v>-4.760104993691234</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.922942219060753</v>
+        <v>0.9696263693694966</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.02992520308129776</v>
+        <v>0.07628523881118099</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.856069669310959</v>
+        <v>2.919795934446447</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.825783276740566</v>
+        <v>-4.709072900968707</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.9383032843880339</v>
+        <v>0.9849874346967777</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.0211068896412302</v>
+        <v>0.1273173315337089</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.881637153182746</v>
+        <v>2.945363418318233</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.760559095613361</v>
+        <v>-4.643848719841501</v>
       </c>
       <c r="E1988" t="n">
-        <v>0.9815803609316212</v>
+        <v>1.028264511240365</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.08633107076843582</v>
+        <v>0.1925415126609146</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.937959065951774</v>
+        <v>3.001685331087262</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.811053385970417</v>
+        <v>-4.694343010198557</v>
       </c>
       <c r="E1989" t="n">
-        <v>0.9573436170880789</v>
+        <v>1.004027767396823</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.04131033364236159</v>
+        <v>0.1475207755348403</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.90690759597541</v>
+        <v>2.970633861110898</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.831165042005125</v>
+        <v>-4.714454666233266</v>
       </c>
       <c r="E1990" t="n">
-        <v>0.950555747005436</v>
+        <v>0.9972398973141796</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.05233767863978078</v>
+        <v>0.1585481205322595</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.914780795305102</v>
+        <v>2.978507060440589</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.928845621277771</v>
+        <v>-4.812135245505912</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.072041286317588</v>
+        <v>1.118725436626332</v>
       </c>
       <c r="F1991" t="n">
-        <v>-0.05836551670040802</v>
+        <v>0.04784492519207073</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.008916649122199</v>
+        <v>3.072642914257687</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.905054052671629</v>
+        <v>-4.788343676899769</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.201670822977863</v>
+        <v>1.248354973286606</v>
       </c>
       <c r="F1992" t="n">
-        <v>-0.03457394809426573</v>
+        <v>0.07163649379821302</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.143304499503702</v>
+        <v>3.207030764639189</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.941808471233351</v>
+        <v>-4.825098095461492</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.178677031567033</v>
+        <v>1.225361181875776</v>
       </c>
       <c r="F1993" t="n">
-        <v>-0.03457394809426573</v>
+        <v>0.07163649379821302</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.135012475517561</v>
+        <v>3.198738740653048</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.937474168176303</v>
+        <v>-4.820763792404444</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.178603948373631</v>
+        <v>1.225288098682375</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.1170761552249382</v>
+        <v>0.2232865971174169</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.224195733092863</v>
+        <v>3.28792199822835</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.92858170678302</v>
+        <v>-4.811871331011161</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.199715338657736</v>
+        <v>1.24639948896648</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.1170761552249382</v>
+        <v>0.2232865971174169</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.241750138819654</v>
+        <v>3.305476403955141</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-5.097057823752897</v>
+        <v>-4.980347447981038</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.124179939274369</v>
+        <v>1.170864089583112</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.08912831950835742</v>
+        <v>0.1953387614008362</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.21683648479429</v>
+        <v>3.280562749929777</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>3.233772154546119</v>
       </c>
       <c r="D1997" t="n">
-        <v>-4.399258294891315</v>
+        <v>-4.282547919119455</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.473712412275846</v>
+        <v>1.520396562584589</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.0187802601379467</v>
+        <v>0.1249907020304254</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.245040310628887</v>
+        <v>3.308766575764374</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,45 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.447954131919269</v>
+        <v>3.784700379389898</v>
       </c>
       <c r="C1998" t="n">
         <v>3.224436177043023</v>
       </c>
       <c r="D1998" t="n">
-        <v>-4.376537191208162</v>
+        <v>-4.259826815436303</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.473464876246011</v>
+        <v>1.520149026554755</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.0187802601379467</v>
+        <v>0.1249907020304254</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.235704333125792</v>
+        <v>3.299430598261279</v>
+      </c>
+    </row>
+    <row r="1999">
+      <c r="A1999" s="2" t="n">
+        <v>45461</v>
+      </c>
+      <c r="B1999" t="n">
+        <v>3.444242211450967</v>
+      </c>
+      <c r="C1999" t="n">
+        <v>3.025162371844598</v>
+      </c>
+      <c r="D1999" t="n">
+        <v>-4.259826815436303</v>
+      </c>
+      <c r="E1999" t="n">
+        <v>1.520149026554755</v>
+      </c>
+      <c r="F1999" t="n">
+        <v>0.1249907020304254</v>
+      </c>
+      <c r="G1999" t="n">
+        <v>3.018226168830966</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240618.xlsx
+++ b/tame_output/ON/bt/strategyON_20240618.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>61.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>55.0%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61.7%</t>
+          <t>71.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>42.4%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>33.2%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,22 +844,22 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-9.1%</t>
+          <t>19.6%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.2%</t>
+          <t>-76.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.6%</t>
+          <t>108.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.4%</t>
+          <t>123.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.1%</t>
+          <t>93.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.8%</t>
+          <t>-51.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.5%</t>
+          <t>-71.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.1%</t>
+          <t>89.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>449.8%</t>
+          <t>454.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-587.6%</t>
+          <t>-583.9%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>49.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.4%</t>
+          <t>-40.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-13.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-646.8%</t>
+          <t>343.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-224.2%</t>
+          <t>-222.8%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-21.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.0%</t>
+          <t>-32.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-15.0%</t>
+          <t>-14.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-39.9%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-2138.2%</t>
+          <t>-179.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-211.5%</t>
+          <t>-217.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>95.7%</t>
+          <t>95.9%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-27.5%</t>
+          <t>-27.9%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>50.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.6%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-144.2%</t>
+          <t>-115.5%</t>
         </is>
       </c>
     </row>
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.814271147034907</v>
+        <v>-5.915492735990862</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7913595777953715</v>
+        <v>0.7508709422129893</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.7370650909849382</v>
+        <v>-0.8432755328774175</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.675185406332119</v>
+        <v>2.611459141196631</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.179398529673653</v>
+        <v>-6.127581802042781</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6445631397457041</v>
+        <v>0.665289830798053</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.033375875283951</v>
+        <v>-1.094535488072073</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.496653450758542</v>
+        <v>2.459957683085669</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.587987306854332</v>
+        <v>-6.536170579223459</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4798891728881913</v>
+        <v>0.5006158639405407</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.441964652464629</v>
+        <v>-1.503124265252752</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.250261728464894</v>
+        <v>2.213565960792021</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.864563407170165</v>
+        <v>-6.812746679539291</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3644441652333192</v>
+        <v>0.3851708562856686</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.441964652464629</v>
+        <v>-1.503124265252752</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.245447160936355</v>
+        <v>2.208751393263482</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.280955281457162</v>
+        <v>-7.229138553826289</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1958814661273975</v>
+        <v>0.2166081571797469</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.441964652464629</v>
+        <v>-1.503124265252752</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.243441211545232</v>
+        <v>2.206745443872359</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.551721370549807</v>
+        <v>-7.499904642918934</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.09783372115901834</v>
+        <v>0.1185604122113677</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.441964652464629</v>
+        <v>-1.503124265252752</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.253699902213911</v>
+        <v>2.217004134541038</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.897596192534616</v>
+        <v>-7.845779464903742</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.04441664248920985</v>
+        <v>-0.02368995143686048</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.441964652464629</v>
+        <v>-1.503124265252752</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.249799467359606</v>
+        <v>2.213103699686733</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.061176070719</v>
+        <v>-8.009359343088127</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1114436737079627</v>
+        <v>-0.09071698265561334</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.441964652464629</v>
+        <v>-1.503124265252752</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.248204387414607</v>
+        <v>2.211508619741734</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.357837412529198</v>
+        <v>-8.306020684898325</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2263292345028338</v>
+        <v>-0.2056025434504845</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.510707788198508</v>
+        <v>-1.57186740098663</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.210737481903489</v>
+        <v>2.174041714230615</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923086</v>
+        <v>3.419979433923085</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.544557120838501</v>
+        <v>-8.492740393207628</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3050434223609582</v>
+        <v>-0.2843167313086088</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.510707788198508</v>
+        <v>-1.57186740098663</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.206711177369086</v>
+        <v>2.170015409696212</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.927558509581132</v>
+        <v>-8.875741781950259</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4583460791795946</v>
+        <v>-0.4376193881272452</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.510707788198508</v>
+        <v>-1.57186740098663</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.206609076047501</v>
+        <v>2.169913308374628</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.109428300566167</v>
+        <v>-9.057611572935294</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5285224796021781</v>
+        <v>-0.5077957885498288</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.692577579183543</v>
+        <v>-1.753737191971666</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.100058717427911</v>
+        <v>2.063362949755037</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.468958623070169</v>
+        <v>-9.417141895439295</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6669843053057285</v>
+        <v>-0.6462576142533791</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.692577579183543</v>
+        <v>-1.753737191971666</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.10540902072596</v>
+        <v>2.068713253053087</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.519307686524391</v>
+        <v>-9.467490958893517</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.67920791073024</v>
+        <v>-0.6584812196778906</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.742926642637765</v>
+        <v>-1.804086255425888</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.083115602610605</v>
+        <v>2.046419834937732</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.616926963945787</v>
+        <v>-9.565110236314913</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7152138710770295</v>
+        <v>-0.6944871800246801</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.840545920059162</v>
+        <v>-1.901705532847284</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.027585786779536</v>
+        <v>1.990890019106662</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.764453051951429</v>
+        <v>-9.712636324320556</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7713307499577144</v>
+        <v>-0.7506040589053651</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.988072008064805</v>
+        <v>-2.049231620852928</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.941963690297722</v>
+        <v>1.905267922624848</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.968711227281293</v>
+        <v>-9.91689449965042</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.8475208229710178</v>
+        <v>-0.8267941319186685</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.115710952678794</v>
+        <v>-2.176870565466916</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.870893520647971</v>
+        <v>1.834197752975097</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.04304420354146</v>
+        <v>-9.991227475910584</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.872771458990647</v>
+        <v>-0.8520447679382981</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.260410476613467</v>
+        <v>-2.321570089401589</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.788556360771603</v>
+        <v>1.75186059309873</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.969574371874009</v>
+        <v>-9.917757644243135</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.8280118248302468</v>
+        <v>-0.8072851337778975</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.186940644946018</v>
+        <v>-2.248100257734141</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.848009961265493</v>
+        <v>1.81131419359262</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.14469878926055</v>
+        <v>-10.09288206162968</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8835063710373472</v>
+        <v>-0.8627796799849978</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.362065062332562</v>
+        <v>-2.423224675120685</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.757490531581084</v>
+        <v>1.720794763908211</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.37915088327504</v>
+        <v>-10.32733415564417</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9845063735447392</v>
+        <v>-0.9637796824923899</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.362065062332562</v>
+        <v>-2.423224675120685</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.750271366679488</v>
+        <v>1.713575599006615</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.48352561430149</v>
+        <v>-10.43170888667061</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.032928456729294</v>
+        <v>-1.012201765676945</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.466439793359008</v>
+        <v>-2.52759940614713</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.680974337289644</v>
+        <v>1.644278569616771</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.53631176990181</v>
+        <v>-10.48449504227094</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.052927129130868</v>
+        <v>-1.032200438078519</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.562115279941405</v>
+        <v>-2.623274892729527</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.624684835178763</v>
+        <v>1.587989067505889</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.6623485632701</v>
+        <v>-10.61053183563923</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.100648117849069</v>
+        <v>-1.07992142679672</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.536863657131662</v>
+        <v>-2.598023269919785</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.642529537493723</v>
+        <v>1.605833769820849</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.61033304930129</v>
+        <v>-10.55851632167042</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.075851576575143</v>
+        <v>-1.055124885522794</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.536863657131662</v>
+        <v>-2.598023269919785</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.646519873180124</v>
+        <v>1.60982410550725</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.75200489102541</v>
+        <v>-10.70018816339454</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.133995540163533</v>
+        <v>-1.113268849111184</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.536863657131662</v>
+        <v>-2.598023269919785</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.645044646281382</v>
+        <v>1.608348878608508</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.70241404660058</v>
+        <v>-10.6505973189697</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.099105792228727</v>
+        <v>-1.078379101176378</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.487272812706828</v>
+        <v>-2.548432425494951</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.689852563101155</v>
+        <v>1.653156795428281</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.6896066535958</v>
+        <v>-10.63778992596493</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.1070339686735</v>
+        <v>-1.086307277621151</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.53612858771573</v>
+        <v>-2.597288200503852</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.647487964449131</v>
+        <v>1.610792196776257</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.46376150087639</v>
+        <v>-10.41194477324552</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.007116834549527</v>
+        <v>-0.9863901434971782</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.494201912128566</v>
+        <v>-2.555361524916688</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.682223042837638</v>
+        <v>1.645527275164764</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.3391828445388</v>
+        <v>-10.28736611690793</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9561462274584316</v>
+        <v>-0.9354195364060822</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.494201912128566</v>
+        <v>-2.555361524916688</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.683362187393697</v>
+        <v>1.646666419720823</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.39207813258309</v>
+        <v>-10.34026140495221</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9746705685140382</v>
+        <v>-0.9539438774616897</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.48924656604012</v>
+        <v>-2.550406178828242</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.688969169208872</v>
+        <v>1.652273401535998</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.3199449572952</v>
+        <v>-10.26812822966433</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9400835941602494</v>
+        <v>-0.919356903107901</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.48924656604012</v>
+        <v>-2.550406178828242</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.694702873447508</v>
+        <v>1.658007105774635</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.24857856468556</v>
+        <v>-10.19676183705469</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9212742995102552</v>
+        <v>-0.9005476084579067</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.417880173430472</v>
+        <v>-2.479039786218594</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.727785446619432</v>
+        <v>1.691089678946559</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232411</v>
+        <v>3.747702660232412</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.15511953070033</v>
+        <v>-10.10330280306946</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8937741672290733</v>
+        <v>-0.8730474761767248</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.417880173430472</v>
+        <v>-2.479039786218594</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.717901965306524</v>
+        <v>1.681206197633651</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436227</v>
+        <v>3.766317079436228</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.04053749437869</v>
+        <v>-10.00420955356372</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.8497759131997902</v>
+        <v>-0.8352447368738027</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.417880173430472</v>
+        <v>-2.479039786218594</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.716067404807151</v>
+        <v>1.679371637134277</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311948</v>
+        <v>3.784684521311949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.942630455702199</v>
+        <v>-9.906302514887232</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.8109134127026545</v>
+        <v>-0.7963822363766675</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.349894423569915</v>
+        <v>-2.411054036358038</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.756558539750024</v>
+        <v>1.71986277207715</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.918676914726241</v>
+        <v>-9.882348973911274</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.8006634901667775</v>
+        <v>-0.7861323138407905</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.325940882593958</v>
+        <v>-2.38710049538208</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.771599170481092</v>
+        <v>1.734903402808218</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.654616976403444</v>
+        <v>-9.618289035588477</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.7082998309994109</v>
+        <v>-0.6937686546734243</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.061880944271162</v>
+        <v>-2.123040557059284</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.916774817313017</v>
+        <v>1.880079049640144</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.947537352898607</v>
+        <v>-8.91120941208364</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.4282550152577769</v>
+        <v>-0.4137238389317899</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.061880944271162</v>
+        <v>-2.123040557059284</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.913987783652717</v>
+        <v>1.877292015979843</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388727</v>
+        <v>3.839374447388726</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.907353054532416</v>
+        <v>-8.871025113717449</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.4118376720234593</v>
+        <v>-0.3973064956974723</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.021696645904971</v>
+        <v>-2.082856258693093</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.938441986560273</v>
+        <v>1.901746218887399</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626473</v>
+        <v>3.856161751626472</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.743953183593053</v>
+        <v>-8.707625242778086</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.347110902426957</v>
+        <v>-0.3325797261009704</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.858296774965608</v>
+        <v>-1.919456387753731</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.035848730344647</v>
+        <v>1.999152962671773</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.78733042929181</v>
+        <v>3.787330429291809</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.510471961363454</v>
+        <v>-8.474144020548486</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.245793984697265</v>
+        <v>-0.231262808371278</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.62481555273601</v>
+        <v>-1.685975165524132</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.183861892520258</v>
+        <v>2.147166124847385</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.360805570355939</v>
+        <v>-8.324477629540972</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1888196386072183</v>
+        <v>-0.1742884622812317</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.531912061493474</v>
+        <v>-1.593071674281596</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.236711776952821</v>
+        <v>2.200016009279947</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.228530096725052</v>
+        <v>-8.192202155910085</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.1405419624078363</v>
+        <v>-0.1260107860818498</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.399636587862587</v>
+        <v>-1.46079620065071</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.31144454787838</v>
+        <v>2.274748780205506</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.037930422051899</v>
+        <v>-8.001602481236933</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.0614870318509384</v>
+        <v>-0.04695585552495185</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.209036913189434</v>
+        <v>-1.270196525977557</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.428619413369908</v>
+        <v>2.391923645697035</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.788930623368318</v>
+        <v>-7.752602682553352</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.05101922884615284</v>
+        <v>0.06555040517213939</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.209036913189434</v>
+        <v>-1.270196525977557</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.441525754593567</v>
+        <v>2.404829986920693</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.894520613141422</v>
+        <v>-7.858192672326457</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.1191926966623078</v>
+        <v>-0.1046615203363213</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.314626902962539</v>
+        <v>-1.375786515750661</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.250195831130485</v>
+        <v>2.213500063457612</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.913255515260019</v>
+        <v>-7.876927574445054</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.07814231563266016</v>
+        <v>-0.06361113930667361</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.32022291262267</v>
+        <v>-1.381382525410792</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.295382567211493</v>
+        <v>2.25868679953862</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.76531547385242</v>
+        <v>-7.728987533037454</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.138845221757788</v>
+        <v>-0.1243140454318015</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.299901996714112</v>
+        <v>-1.361061609502235</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.18769619406846</v>
+        <v>2.151000426395587</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.712345951598431</v>
+        <v>-7.676018010783466</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.1263713991096709</v>
+        <v>-0.1118402227836843</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.246932474460123</v>
+        <v>-1.308092087248246</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.210763921167375</v>
+        <v>2.174068153494502</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.668797544827741</v>
+        <v>-7.632469604012775</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.1159126484964879</v>
+        <v>-0.1013814721705013</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.246932474460123</v>
+        <v>-1.308092087248246</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.203803309072282</v>
+        <v>2.167107541399409</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.426649151373883</v>
+        <v>-7.390321210558917</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.004590936733801509</v>
+        <v>0.009940239592185041</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.246932474460123</v>
+        <v>-1.308092087248246</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.218265663453425</v>
+        <v>2.181569895780552</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.318390014251361</v>
+        <v>-7.282062073436395</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.03324483857440219</v>
+        <v>0.04777601490038874</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.246932474460123</v>
+        <v>-1.308092087248246</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.21279778391262</v>
+        <v>2.176102016239747</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.19509887943423</v>
+        <v>-7.158770938619265</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.08005938651183131</v>
+        <v>0.09459056283781786</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.123641339642993</v>
+        <v>-1.184800952431115</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.284270558813475</v>
+        <v>2.247574791140602</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.173949680530787</v>
+        <v>-7.137621739715821</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.0962200443105341</v>
+        <v>0.1107512206365207</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.10249214073955</v>
+        <v>-1.163651753527672</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.304661056392867</v>
+        <v>2.267965288719993</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.930184238547342</v>
+        <v>-6.893856297732377</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.1895069294509626</v>
+        <v>0.2040381057769491</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.10249214073955</v>
+        <v>-1.163651753527672</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.300441764739917</v>
+        <v>2.263745997067044</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.828421418270048</v>
+        <v>-6.792093477455082</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2323363714818965</v>
+        <v>0.246867547807883</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.089273072347121</v>
+        <v>-1.150432685135243</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.310497519695391</v>
+        <v>2.273801752022517</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.578571024320973</v>
+        <v>-6.542243083506007</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3250186040452285</v>
+        <v>0.3395497803712151</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.089273072347121</v>
+        <v>-1.150432685135243</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.303239594679093</v>
+        <v>2.266543827006219</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.40267893185354</v>
+        <v>-6.366350991038575</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3989745645528502</v>
+        <v>0.4135057408788363</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.089273072347121</v>
+        <v>-1.150432685135243</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.306838718199741</v>
+        <v>2.270142950526868</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.231232468831077</v>
+        <v>-6.194904528016112</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4808806558163892</v>
+        <v>0.4954118321423757</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.9178266093246578</v>
+        <v>-0.9789862221127802</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.423034102067773</v>
+        <v>2.3863383343949</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.156942903092737</v>
+        <v>-6.120614962277773</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5096169597280218</v>
+        <v>0.5241481360540083</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.8435370435863185</v>
+        <v>-0.904696656374441</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.466628319127073</v>
+        <v>2.4299325514542</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.093307160858803</v>
+        <v>-6.056979220043838</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5397660576759131</v>
+        <v>0.5542972340018992</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.779901301352384</v>
+        <v>-0.8410609141405064</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.509504565521751</v>
+        <v>2.472808797848878</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074781</v>
+        <v>3.798814771074782</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.981880401532883</v>
+        <v>-5.945552460717918</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5655310201900767</v>
+        <v>0.5800621965160628</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.779901301352384</v>
+        <v>-0.8410609141405064</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.490698824305547</v>
+        <v>2.454003056632674</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.797694884242294</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.741449904728023</v>
+        <v>-5.705121963913058</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6634462955368985</v>
+        <v>0.6779774718628846</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.5394708045475237</v>
+        <v>-0.6006304173356461</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.636700199013341</v>
+        <v>2.600004431340467</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367684</v>
+        <v>3.821593509367685</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.669207336556828</v>
+        <v>-5.632879395741863</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6962726366401966</v>
+        <v>0.7108038129661827</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.5394708045475237</v>
+        <v>-0.6006304173356461</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.640629512848161</v>
+        <v>2.603933745175287</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.61620901427544</v>
+        <v>-5.579881073460475</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7181505494700917</v>
+        <v>0.7326817257960778</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.4841345455455849</v>
+        <v>-0.5452941583337073</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.674509852166664</v>
+        <v>2.637814084493791</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.507404128795713</v>
+        <v>-5.471076187980748</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7586705748819758</v>
+        <v>0.7732017512079619</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.4841345455455849</v>
+        <v>-0.5452941583337073</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.671507923386658</v>
+        <v>2.634812155713784</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675938</v>
+        <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.287383330758702</v>
+        <v>-5.251055389943738</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8482579311073941</v>
+        <v>0.8627891074333802</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.3429147004776046</v>
+        <v>-0.4040743132657271</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.75781886743806</v>
+        <v>2.721123099765186</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539949</v>
+        <v>3.843274527539948</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.154515641695425</v>
+        <v>-5.11818770088046</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9172991895345284</v>
+        <v>0.9318303658605149</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.3429147004776046</v>
+        <v>-0.4040743132657271</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.773713050239883</v>
+        <v>2.73701728256701</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496259</v>
+        <v>3.845047386496258</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.034342558330926</v>
+        <v>-4.998014617515961</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9665142673206297</v>
+        <v>0.9810454436466161</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.2227416171131057</v>
+        <v>-0.2839012299012281</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.846962744698884</v>
+        <v>2.810266977026011</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576996</v>
+        <v>3.791273551576994</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.889670413231189</v>
+        <v>-4.853342472416224</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.034471227921965</v>
+        <v>1.049002404247951</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.07806947201336828</v>
+        <v>-0.1392290848014907</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.943854134320167</v>
+        <v>2.907158366647293</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.7358392229421</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.949545240588881</v>
+        <v>-4.913217299773916</v>
       </c>
       <c r="E1933" t="n">
-        <v>0.9965587883803138</v>
+        <v>1.0110899647063</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.1379442993710604</v>
+        <v>-0.1991039121591828</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.893966729306977</v>
+        <v>2.857270961634104</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674512</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.862745742809873</v>
+        <v>-4.826417801994908</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.053679080814483</v>
+        <v>1.068210257140469</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.1379442993710604</v>
+        <v>-0.1991039121591828</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.916367222629543</v>
+        <v>2.87967145495667</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430693</v>
+        <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.865215449271679</v>
+        <v>-4.828887508456714</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.052763599603173</v>
+        <v>1.067294775929159</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.1404140058328666</v>
+        <v>-0.201573618620989</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.914957800125872</v>
+        <v>2.878262032452998</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432201960036</v>
+        <v>3.743220196003598</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.933585635595689</v>
+        <v>-4.897257694780724</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.036422447548271</v>
+        <v>1.050953623874257</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.1311383067966516</v>
+        <v>-0.192297919584774</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.931530142022303</v>
+        <v>2.89483437434943</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508368</v>
+        <v>3.714179139508366</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-5.042123816511823</v>
+        <v>-5.005795875696858</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.9834438838137083</v>
+        <v>0.9979750601396946</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.1311383067966516</v>
+        <v>-0.192297919584774</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.921966850654194</v>
+        <v>2.885271082981321</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417703</v>
+        <v>3.710906731417701</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.073116975840528</v>
+        <v>-5.036789035025564</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.7957561851226131</v>
+        <v>0.8102873614485993</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.1311383067966516</v>
+        <v>-0.192297919584774</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.746676415694581</v>
+        <v>2.709980648021708</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205901</v>
+        <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.897642716048059</v>
+        <v>-4.861314775233095</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.8705131210313883</v>
+        <v>0.8850442973573747</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.1311383067966516</v>
+        <v>-0.192297919584774</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.751243647686369</v>
+        <v>2.714547880013495</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225445</v>
+        <v>3.765024323225443</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-5.008578968689308</v>
+        <v>-4.972251027874344</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8018806487360959</v>
+        <v>0.8164118250620822</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.1311383067966516</v>
+        <v>-0.192297919584774</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.726985676447576</v>
+        <v>2.690289908774703</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111293</v>
+        <v>3.773210297111291</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.016861042834367</v>
+        <v>-4.980533102019402</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8016992042979783</v>
+        <v>0.8162303806239644</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.13942038094171</v>
+        <v>-0.2005799937298324</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.725147817180446</v>
+        <v>2.688452049507573</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264161</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.957008423630644</v>
+        <v>-4.920680482815679</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8358126384115998</v>
+        <v>0.8503438147375859</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.13942038094171</v>
+        <v>-0.2005799937298324</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.735320203612579</v>
+        <v>2.698624435939705</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.786949957742297</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.870764960604266</v>
+        <v>-4.834437019789301</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8652562941960111</v>
+        <v>0.8797874705219972</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.13942038094171</v>
+        <v>-0.2005799937298324</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.730266474186439</v>
+        <v>2.693570706513566</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.916071780003246</v>
+        <v>-4.879743839188281</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8389093418809448</v>
+        <v>0.8534405182069309</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.1802305439509408</v>
+        <v>-0.2413901567390632</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.697556151825426</v>
+        <v>2.660860384152552</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803189</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.945104884705547</v>
+        <v>-4.908776943890582</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8278479730331259</v>
+        <v>0.842379149359112</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.1802305439509408</v>
+        <v>-0.2413901567390632</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.698108024858528</v>
+        <v>2.661412257185654</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809498</v>
+        <v>3.733390600809496</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.852294403254687</v>
+        <v>-4.815966462439722</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.7942448575048353</v>
+        <v>0.8087760338308216</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.08742006250008144</v>
+        <v>-0.1485796752882039</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.683067005620409</v>
+        <v>2.646371237947535</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560424</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.896683872584115</v>
+        <v>-4.86035593176915</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.7783625456976653</v>
+        <v>0.7928937220236514</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.1318095318295091</v>
+        <v>-0.1929691446176315</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.658306799947353</v>
+        <v>2.62161103227448</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472738</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.784012654347864</v>
+        <v>-4.7476847135329</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8185067415038882</v>
+        <v>0.8330379178298744</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.0191383135932589</v>
+        <v>-0.08029792638138133</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.720985239400826</v>
+        <v>2.684289471727953</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.671635653165191</v>
+        <v>-4.635307712350227</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.8689488378076247</v>
+        <v>0.8834800141336108</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.0191383135932589</v>
+        <v>-0.08029792638138133</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.726476535231493</v>
+        <v>2.68978076755862</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.699416051066544</v>
+        <v>-4.66308811025158</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8693338804156228</v>
+        <v>0.8838650567416089</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.04691871149461196</v>
+        <v>-0.1080783242827344</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.721305498259221</v>
+        <v>2.684609730586347</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705325</v>
+        <v>3.643069621705323</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.782417332091823</v>
+        <v>-4.746089391276858</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6744890880061645</v>
+        <v>0.6890202643321506</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.06548959602178572</v>
+        <v>-0.1266492088099082</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.54851868754357</v>
+        <v>2.511822919870696</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.68271631072927</v>
+        <v>3.682716310729268</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.891031410535154</v>
+        <v>-4.85470346972019</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7511931173480375</v>
+        <v>0.7657242936740238</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.06548959602178572</v>
+        <v>-0.1266492088099082</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.668668348262775</v>
+        <v>2.631972580589902</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190769</v>
+        <v>3.733012441190767</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.977629993516257</v>
+        <v>-4.941302052701293</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7310667102579194</v>
+        <v>0.7455978865839055</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.06548959602178572</v>
+        <v>-0.1266492088099082</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.683181374365098</v>
+        <v>2.646485606692225</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913426</v>
+        <v>3.741174069913424</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.939246330958106</v>
+        <v>-4.902918390143141</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.7438396166235486</v>
+        <v>0.7583707929495347</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.02710593346363455</v>
+        <v>-0.08826554625175698</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.703631013242358</v>
+        <v>2.666935245569484</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532487</v>
+        <v>3.751147197532485</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.76213000092294</v>
+        <v>-4.725802060107975</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8114151774829168</v>
+        <v>0.8259463538089031</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.02710593346363455</v>
+        <v>-0.08826554625175698</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.700360042087659</v>
+        <v>2.663664274414786</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793904</v>
+        <v>3.741328448793903</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.807222245756486</v>
+        <v>-4.770894304941521</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.7940616713114117</v>
+        <v>0.8085928476373978</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.08900197663302434</v>
+        <v>-0.1501615894211468</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.663905807947939</v>
+        <v>2.627210040275065</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011238</v>
+        <v>3.750729377011236</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.627846824517718</v>
+        <v>-4.591518883702753</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.8595988151133331</v>
+        <v>0.8741299914393192</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.06777478153769434</v>
+        <v>0.006615168749571909</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.751758838156785</v>
+        <v>2.715063070483911</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982232</v>
+        <v>3.71699171898223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.672861038038324</v>
+        <v>-4.636533097223359</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8224005850366805</v>
+        <v>0.8369317613626668</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.03742588622308973</v>
+        <v>-0.0237337265650327</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.714356956299611</v>
+        <v>2.677661188626738</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509539</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.939865548310759</v>
+        <v>-4.903537607495794</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.7212903432666522</v>
+        <v>0.7358215195926385</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.1569371518198588</v>
+        <v>-0.2180967646079813</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.603430695812788</v>
+        <v>2.566734928139915</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760811</v>
+        <v>3.702309454760808</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.041063329747931</v>
+        <v>-5.004735388932967</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.6800151525882847</v>
+        <v>0.6945463289142708</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.225345965365178</v>
+        <v>-0.2865055781533005</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.561589329582098</v>
+        <v>2.524893561909225</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815456</v>
+        <v>3.705571661815453</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.008587743577159</v>
+        <v>-4.972259802762195</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.6906053486109103</v>
+        <v>0.7051365249368964</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.225345965365178</v>
+        <v>-0.2865055781533005</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.559189291136414</v>
+        <v>2.522493523463541</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378101</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.989549615869862</v>
+        <v>-4.953221675054897</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.694745318902074</v>
+        <v>0.7092764952280604</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.2835295766963726</v>
+        <v>-0.344689189484495</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.520803843545943</v>
+        <v>2.48410807587307</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.731064473131249</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.02067624702048</v>
+        <v>-4.984348306205516</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.8598765353805073</v>
+        <v>0.8744077117064935</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.2835295766963726</v>
+        <v>-0.344689189484495</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.698385712484623</v>
+        <v>2.66168994481175</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067867</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.034543008354398</v>
+        <v>-4.998215067539434</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.8551631598330736</v>
+        <v>0.8696943361590599</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.3213874934301955</v>
+        <v>-0.3825471062183179</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.676504291430463</v>
+        <v>2.63980852375759</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789124</v>
+        <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.054800306883356</v>
+        <v>-5.018472366068392</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.8530687708184166</v>
+        <v>0.8675999471444027</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.3213874934301955</v>
+        <v>-0.3825471062183179</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.682512821827389</v>
+        <v>2.645817054154516</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519911</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.907057336648354</v>
+        <v>-4.870729395833389</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9913186067044393</v>
+        <v>1.005849783030426</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.1535801361953124</v>
+        <v>-0.2147397489834348</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.862349883960341</v>
+        <v>2.825654116287467</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181174</v>
+        <v>3.80224592918117</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.009072019179575</v>
+        <v>-4.97274407836461</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.953306355223432</v>
+        <v>0.9678375315494181</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.1535801361953124</v>
+        <v>-0.2147397489834348</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.865143505491822</v>
+        <v>2.828447737818948</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394732</v>
+        <v>3.805608985394729</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.002919313126791</v>
+        <v>-4.966591372311826</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9564297860362039</v>
+        <v>0.9709609623621902</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.1474274301425281</v>
+        <v>-0.2085870429306505</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.869497477515151</v>
+        <v>2.832801709842277</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.798239794890609</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.019728611277293</v>
+        <v>-4.983400670462328</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9487865435161136</v>
+        <v>0.9633177198420997</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.1642367282930297</v>
+        <v>-0.2253963410811521</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.85849237536496</v>
+        <v>2.821796607692087</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.95743061250117</v>
+        <v>-4.921102671686206</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.040041296823383</v>
+        <v>1.054572473149369</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.1642367282930297</v>
+        <v>-0.2253963410811521</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.924827929161781</v>
+        <v>2.888132161488908</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992194</v>
+        <v>3.848729139992192</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.755640414836012</v>
+        <v>-4.719312474021048</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8293382482788445</v>
+        <v>0.8438694246048306</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.03378146387612468</v>
+        <v>-0.02737814891199775</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.752219716852672</v>
+        <v>2.715523949179798</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852423</v>
+        <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.695749733193419</v>
+        <v>-4.659421792378454</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.923584753258057</v>
+        <v>0.9381159295840431</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.09367214551871816</v>
+        <v>0.03251253273059573</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.858444358160403</v>
+        <v>2.821748590487529</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319549</v>
+        <v>3.819063300319546</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.793490277818393</v>
+        <v>-4.757162337003429</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.8991162715241108</v>
+        <v>0.9136474478500971</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.07778286738573797</v>
+        <v>0.01662325459761554</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.863538527396658</v>
+        <v>2.826842759723785</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489386</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.969828037941323</v>
+        <v>-4.933500097126358</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8271171482996107</v>
+        <v>0.841648324625597</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.09855489273719142</v>
+        <v>-0.1597145055253139</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.756271852147572</v>
+        <v>2.719576084474699</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397795</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.898281715164446</v>
+        <v>-4.861953774349481</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8542272954502901</v>
+        <v>0.8687584717762764</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.09855489273719142</v>
+        <v>-0.1597145055253139</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.754763470187501</v>
+        <v>2.718067702514628</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024963</v>
+        <v>3.836023391024961</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.853908583525877</v>
+        <v>-4.817580642710912</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8718394155411537</v>
+        <v>0.8863705918671401</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.05418176109862283</v>
+        <v>-0.1153413738867453</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.781250216606078</v>
+        <v>2.744554448933205</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863225</v>
+        <v>3.821591150863222</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.845954613231105</v>
+        <v>-4.80962667241614</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.8750210036590627</v>
+        <v>0.8895521799850488</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.05418176109862283</v>
+        <v>-0.1153413738867453</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.781250216606078</v>
+        <v>2.744554448933205</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947584</v>
+        <v>3.833040181947581</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.798298882670049</v>
+        <v>-4.761970941855084</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9004650529112896</v>
+        <v>0.9149962292372757</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.006526030537567173</v>
+        <v>-0.0676856433256896</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.816225411970517</v>
+        <v>2.779529644297643</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326876</v>
+        <v>3.822707244326874</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.670614572875753</v>
+        <v>-4.634286632060788</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.956431150203733</v>
+        <v>0.9709623265297191</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.1211582792567293</v>
+        <v>0.05999866646860685</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.897728371221819</v>
+        <v>2.861032603548946</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314552</v>
+        <v>3.828837911314549</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.731281163278142</v>
+        <v>-4.694953222463178</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.9189191865186495</v>
+        <v>0.9334503628446356</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.03945996253819561</v>
+        <v>-0.02169965024992682</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.835464053666571</v>
+        <v>2.798768285993698</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690028</v>
+        <v>3.816866067690025</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.686442761669744</v>
+        <v>-4.650114820854779</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.9409522497726375</v>
+        <v>0.9554834260986236</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.04400339548306509</v>
+        <v>-0.01715621730505734</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.842287816044121</v>
+        <v>2.805592048371248</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674311</v>
+        <v>3.817961388674309</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.787201397426742</v>
+        <v>-4.750873456611777</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.9048097351009161</v>
+        <v>0.9193409114269024</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.04482217324394033</v>
+        <v>-0.1059817860320628</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.793153414438996</v>
+        <v>2.756457646766123</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.82671377916322</v>
+        <v>3.826713779163218</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.742998560340841</v>
+        <v>-4.706670619525877</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.9283704724631134</v>
+        <v>0.9429016487890998</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.0006193361580398848</v>
+        <v>-0.06177894894616232</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.825554719218374</v>
+        <v>2.7888589515455</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022905</v>
+        <v>3.838228663022903</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.779977588004284</v>
+        <v>-4.743649647189319</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.911988861866984</v>
+        <v>0.9265200381929701</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.03635456563329065</v>
+        <v>-0.02480504715483178</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.84614906076242</v>
+        <v>2.809453293089546</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042139</v>
+        <v>3.863924114042137</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.800035666869125</v>
+        <v>-4.76370772605416</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.9552133955040873</v>
+        <v>0.9697445718300735</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.03635456563329065</v>
+        <v>-0.02480504715483178</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.897396825945459</v>
+        <v>2.860701058272586</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078282</v>
+        <v>3.86536771507828</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.760104993691234</v>
+        <v>-4.72377705287627</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.9696263693694966</v>
+        <v>0.9841575456954827</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.07628523881118099</v>
+        <v>0.01512562602305856</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.919795934446447</v>
+        <v>2.883100166773573</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232399</v>
+        <v>3.864518876232397</v>
       </c>
       <c r="C1987" t="n">
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.709072900968707</v>
+        <v>-4.672744960153742</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.9849874346967777</v>
+        <v>0.9995186110227638</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.1273173315337089</v>
+        <v>0.06615771874558651</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.945363418318233</v>
+        <v>2.90866765064536</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162115</v>
+        <v>3.842576394162113</v>
       </c>
       <c r="C1988" t="n">
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.643848719841501</v>
+        <v>-4.607520779026537</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.028264511240365</v>
+        <v>1.042795687566351</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.1925415126609146</v>
+        <v>0.1313818998727921</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.001685331087262</v>
+        <v>2.964989563414388</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639819</v>
+        <v>3.840090220639818</v>
       </c>
       <c r="C1989" t="n">
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.694343010198557</v>
+        <v>-4.658015069383593</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.004027767396823</v>
+        <v>1.018558943722809</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.1475207755348403</v>
+        <v>0.0863611627467179</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.970633861110898</v>
+        <v>2.933938093438024</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845198842749921</v>
+        <v>3.84519884274992</v>
       </c>
       <c r="C1990" t="n">
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.714454666233266</v>
+        <v>-4.678126725418301</v>
       </c>
       <c r="E1990" t="n">
-        <v>0.9972398973141796</v>
+        <v>1.011771073640166</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.1585481205322595</v>
+        <v>0.0973885077441371</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.978507060440589</v>
+        <v>2.941811292767716</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828690479393547</v>
+        <v>3.828690479393545</v>
       </c>
       <c r="C1991" t="n">
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.812135245505912</v>
+        <v>-4.775807304690947</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.118725436626332</v>
+        <v>1.133256612952318</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.04784492519207073</v>
+        <v>-0.0133146875960517</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.072642914257687</v>
+        <v>3.035947146584813</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714885</v>
+        <v>3.813251854714883</v>
       </c>
       <c r="C1992" t="n">
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.788343676899769</v>
+        <v>-4.752015736084805</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.248354973286606</v>
+        <v>1.262886149612592</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.07163649379821302</v>
+        <v>0.01047688101009059</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.207030764639189</v>
+        <v>3.170334996966316</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814259761756012</v>
+        <v>3.81425976175601</v>
       </c>
       <c r="C1993" t="n">
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.825098095461492</v>
+        <v>-4.788770154646527</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.225361181875776</v>
+        <v>1.239892358201762</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.07163649379821302</v>
+        <v>0.01047688101009059</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.198738740653048</v>
+        <v>3.162042972980175</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803426852654186</v>
+        <v>3.803426852654185</v>
       </c>
       <c r="C1994" t="n">
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.820763792404444</v>
+        <v>-4.784435851589479</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.225288098682375</v>
+        <v>1.239819275008361</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.2232865971174169</v>
+        <v>0.1621269843292945</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.28792199822835</v>
+        <v>3.251226230555477</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796293177717117</v>
+        <v>3.796293177717115</v>
       </c>
       <c r="C1995" t="n">
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.811871331011161</v>
+        <v>-4.775543390196196</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.24639948896648</v>
+        <v>1.260930665292466</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.2232865971174169</v>
+        <v>0.1621269843292945</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.305476403955141</v>
+        <v>3.268780636282268</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794453975702625</v>
+        <v>3.794453975702623</v>
       </c>
       <c r="C1996" t="n">
         <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.980347447981038</v>
+        <v>-4.944019507166074</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.170864089583112</v>
+        <v>1.185395265909099</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.1953387614008362</v>
+        <v>0.1341791486127137</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.280562749929777</v>
+        <v>3.243866982256904</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795603100539967</v>
+        <v>3.795603100539966</v>
       </c>
       <c r="C1997" t="n">
         <v>3.233772154546119</v>
       </c>
       <c r="D1997" t="n">
-        <v>-4.282547919119455</v>
+        <v>-4.246219978304491</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.520396562584589</v>
+        <v>1.534927738910576</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.1249907020304254</v>
+        <v>0.06383108924230302</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.308766575764374</v>
+        <v>3.272070808091501</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784700379389898</v>
+        <v>3.784700379389896</v>
       </c>
       <c r="C1998" t="n">
         <v>3.224436177043023</v>
       </c>
       <c r="D1998" t="n">
-        <v>-4.259826815436303</v>
+        <v>-4.223498874621338</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.520149026554755</v>
+        <v>1.534680202880741</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.1249907020304254</v>
+        <v>0.06383108924230302</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.299430598261279</v>
+        <v>3.262734830588405</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.444242211450967</v>
+        <v>3.830315646565468</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.025162371844598</v>
+        <v>3.311991367564307</v>
       </c>
       <c r="D1999" t="n">
-        <v>-4.259826815436303</v>
+        <v>-4.223498874621338</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.520149026554755</v>
+        <v>1.534680202880741</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.1249907020304254</v>
+        <v>0.06383108924230302</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.018226168830966</v>
+        <v>3.305055164550675</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240618.xlsx
+++ b/tame_output/ON/bt/strategyON_20240618.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>15.9%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>71.1%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>33.2%</t>
+          <t>37.2%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,22 +844,22 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>9.7%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.0%</t>
+          <t>-76.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.4%</t>
+          <t>109.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.1%</t>
+          <t>124.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.0%</t>
+          <t>93.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.6%</t>
+          <t>-52.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-71.6%</t>
+          <t>-73.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.8%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>454.2%</t>
+          <t>449.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-583.9%</t>
+          <t>-598.6%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.5%</t>
+          <t>99.3%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.2%</t>
+          <t>-38.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-13.5%</t>
+          <t>-14.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>343.5%</t>
+          <t>163.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-222.8%</t>
+          <t>-197.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-21.6%</t>
+          <t>-24.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.4%</t>
+          <t>-32.6%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-14.7%</t>
+          <t>-18.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-179.9%</t>
+          <t>-162.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-217.6%</t>
+          <t>-238.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>95.9%</t>
+          <t>94.3%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-27.9%</t>
+          <t>-25.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-15.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-115.5%</t>
+          <t>-125.4%</t>
         </is>
       </c>
     </row>
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.127581802042781</v>
+        <v>-6.280620118629608</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.665289830798053</v>
+        <v>0.604074504163322</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.094535488072073</v>
+        <v>-1.13958631717643</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.459957683085669</v>
+        <v>2.432927185623055</v>
       </c>
     </row>
     <row r="1864">
@@ -44420,19 +44420,19 @@
         <v>3.300815818330521</v>
       </c>
       <c r="C1864" t="n">
-        <v>3.115440519943672</v>
+        <v>3.429831658529679</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.536170579223459</v>
+        <v>-6.689208895810287</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.5006158639405407</v>
+        <v>0.7537916758918168</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.503124265252752</v>
+        <v>-1.548175094357108</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.213565960792021</v>
+        <v>2.500926601915414</v>
       </c>
     </row>
     <row r="1865">
@@ -44443,19 +44443,19 @@
         <v>3.302618194191735</v>
       </c>
       <c r="C1865" t="n">
-        <v>3.110625952415132</v>
+        <v>3.425017091001139</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.812746679539291</v>
+        <v>-6.96578499612612</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3851708562856686</v>
+        <v>0.6383466682369443</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.503124265252752</v>
+        <v>-1.548175094357108</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.208751393263482</v>
+        <v>2.496112034386875</v>
       </c>
     </row>
     <row r="1866">
@@ -44466,19 +44466,19 @@
         <v>3.305023265108638</v>
       </c>
       <c r="C1866" t="n">
-        <v>3.10862000302401</v>
+        <v>3.423011141610017</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.229138553826289</v>
+        <v>-7.382176870413117</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.2166081571797469</v>
+        <v>0.4697839691310226</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.503124265252752</v>
+        <v>-1.548175094357108</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.206745443872359</v>
+        <v>2.494106084995752</v>
       </c>
     </row>
     <row r="1867">
@@ -44489,19 +44489,19 @@
         <v>3.34137872309782</v>
       </c>
       <c r="C1867" t="n">
-        <v>3.118878693692689</v>
+        <v>3.433269832278696</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.499904642918934</v>
+        <v>-7.652942959505762</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.1185604122113677</v>
+        <v>0.3717362241626434</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.503124265252752</v>
+        <v>-1.548175094357108</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.217004134541038</v>
+        <v>2.504364775664431</v>
       </c>
     </row>
     <row r="1868">
@@ -44512,19 +44512,19 @@
         <v>3.374439043094116</v>
       </c>
       <c r="C1868" t="n">
-        <v>3.114978258838384</v>
+        <v>3.429369397424391</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.845779464903742</v>
+        <v>-7.998817781490571</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.02368995143686048</v>
+        <v>0.2294858605144152</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.503124265252752</v>
+        <v>-1.548175094357108</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.213103699686733</v>
+        <v>2.500464340810126</v>
       </c>
     </row>
     <row r="1869">
@@ -44535,19 +44535,19 @@
         <v>3.405960511199285</v>
       </c>
       <c r="C1869" t="n">
-        <v>3.113383178893385</v>
+        <v>3.427774317479392</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.009359343088127</v>
+        <v>-8.162397659674955</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.09071698265561334</v>
+        <v>0.1624588292956628</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.503124265252752</v>
+        <v>-1.548175094357108</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.211508619741734</v>
+        <v>2.498869260865127</v>
       </c>
     </row>
     <row r="1870">
@@ -44558,19 +44558,19 @@
         <v>3.424633354969592</v>
       </c>
       <c r="C1870" t="n">
-        <v>3.117162154822593</v>
+        <v>3.4315532934086</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.306020684898325</v>
+        <v>-8.459059001485153</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2056025434504845</v>
+        <v>0.04757326850079169</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.57186740098663</v>
+        <v>-1.616918230090987</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.174041714230615</v>
+        <v>2.461402355354008</v>
       </c>
     </row>
     <row r="1871">
@@ -44581,19 +44581,19 @@
         <v>3.419979433923085</v>
       </c>
       <c r="C1871" t="n">
-        <v>3.11313585028819</v>
+        <v>3.427526988874197</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.492740393207628</v>
+        <v>-8.645778709794456</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.2843167313086088</v>
+        <v>-0.03114091935733265</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.57186740098663</v>
+        <v>-1.616918230090987</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.170015409696212</v>
+        <v>2.457376050819605</v>
       </c>
     </row>
     <row r="1872">
@@ -44604,19 +44604,19 @@
         <v>3.458100091297748</v>
       </c>
       <c r="C1872" t="n">
-        <v>3.113033748966606</v>
+        <v>3.427424887552613</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.875741781950259</v>
+        <v>-9.028780098537087</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4376193881272452</v>
+        <v>-0.1844435761759691</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.57186740098663</v>
+        <v>-1.616918230090987</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.169913308374628</v>
+        <v>2.457273949498021</v>
       </c>
     </row>
     <row r="1873">
@@ -44627,19 +44627,19 @@
         <v>3.447750501317615</v>
       </c>
       <c r="C1873" t="n">
-        <v>3.115605264938036</v>
+        <v>3.429996403524043</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.057611572935294</v>
+        <v>-9.210649889522122</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5077957885498288</v>
+        <v>-0.2546199765985531</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.753737191971666</v>
+        <v>-1.798788021076022</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.063362949755037</v>
+        <v>2.35072359087843</v>
       </c>
     </row>
     <row r="1874">
@@ -44650,19 +44650,19 @@
         <v>3.503515506737168</v>
       </c>
       <c r="C1874" t="n">
-        <v>3.120955568236086</v>
+        <v>3.435346706822093</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.417141895439295</v>
+        <v>-9.570180212026123</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6462576142533791</v>
+        <v>-0.3930818023021034</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.753737191971666</v>
+        <v>-1.798788021076022</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.068713253053087</v>
+        <v>2.35607389417648</v>
       </c>
     </row>
     <row r="1875">
@@ -44673,19 +44673,19 @@
         <v>3.503170282341311</v>
       </c>
       <c r="C1875" t="n">
-        <v>3.128871588193264</v>
+        <v>3.443262726779271</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.467490958893517</v>
+        <v>-9.620529275480346</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6584812196778906</v>
+        <v>-0.4053054077266149</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.804086255425888</v>
+        <v>-1.849137084530244</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.046419834937732</v>
+        <v>2.333780476061125</v>
       </c>
     </row>
     <row r="1876">
@@ -44696,19 +44696,19 @@
         <v>3.501052558539461</v>
       </c>
       <c r="C1876" t="n">
-        <v>3.131913338815032</v>
+        <v>3.44630447740104</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.565110236314913</v>
+        <v>-9.718148552901742</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.6944871800246801</v>
+        <v>-0.4413113680734044</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.901705532847284</v>
+        <v>-1.946756361951641</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.990890019106662</v>
+        <v>2.278250660230055</v>
       </c>
     </row>
     <row r="1877">
@@ -44719,19 +44719,19 @@
         <v>3.492448711937497</v>
       </c>
       <c r="C1877" t="n">
-        <v>3.134806895136605</v>
+        <v>3.449198033722612</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.712636324320556</v>
+        <v>-9.865674640907384</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7506040589053651</v>
+        <v>-0.4974282469540894</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.049231620852928</v>
+        <v>-2.094282449957284</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.905267922624848</v>
+        <v>2.192628563748242</v>
       </c>
     </row>
     <row r="1878">
@@ -44742,19 +44742,19 @@
         <v>3.502790399141699</v>
       </c>
       <c r="C1878" t="n">
-        <v>3.140320092255247</v>
+        <v>3.454711230841254</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.91689449965042</v>
+        <v>-10.06993281623725</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.8267941319186685</v>
+        <v>-0.5736183199673928</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.176870565466916</v>
+        <v>-2.221921394571273</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.834197752975097</v>
+        <v>2.121558394098491</v>
       </c>
     </row>
     <row r="1879">
@@ -44765,19 +44765,19 @@
         <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
-        <v>3.144802646739683</v>
+        <v>3.45919378532569</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.991227475910584</v>
+        <v>-10.14426579249741</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8520447679382981</v>
+        <v>-0.5988689559870219</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.321570089401589</v>
+        <v>-2.366620918505946</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.75186059309873</v>
+        <v>2.039221234222123</v>
       </c>
     </row>
     <row r="1880">
@@ -44788,19 +44788,19 @@
         <v>3.499971739440632</v>
       </c>
       <c r="C1880" t="n">
-        <v>3.160174348233104</v>
+        <v>3.474565486819111</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.917757644243135</v>
+        <v>-10.07079596082996</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.8072851337778975</v>
+        <v>-0.5541093218266218</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.248100257734141</v>
+        <v>-2.293151086838497</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.81131419359262</v>
+        <v>2.098674834716014</v>
       </c>
     </row>
     <row r="1881">
@@ -44811,19 +44811,19 @@
         <v>3.490059241608599</v>
       </c>
       <c r="C1881" t="n">
-        <v>3.174729568980621</v>
+        <v>3.489120707566628</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.09288206162968</v>
+        <v>-10.24592037821651</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8627796799849978</v>
+        <v>-0.6096038680337221</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.423224675120685</v>
+        <v>-2.468275504225041</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.720794763908211</v>
+        <v>2.008155405031604</v>
       </c>
     </row>
     <row r="1882">
@@ -44834,19 +44834,19 @@
         <v>3.48587859441027</v>
       </c>
       <c r="C1882" t="n">
-        <v>3.167510404079025</v>
+        <v>3.481901542665032</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.32733415564417</v>
+        <v>-10.480372472231</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9637796824923899</v>
+        <v>-0.7106038705411142</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.423224675120685</v>
+        <v>-2.468275504225041</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.713575599006615</v>
+        <v>2.000936240130008</v>
       </c>
     </row>
     <row r="1883">
@@ -44857,19 +44857,19 @@
         <v>3.480692492764395</v>
       </c>
       <c r="C1883" t="n">
-        <v>3.160838213305049</v>
+        <v>3.475229351891056</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.43170888667061</v>
+        <v>-10.58474720325744</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.012201765676945</v>
+        <v>-0.7590259537256689</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.52759940614713</v>
+        <v>-2.572650235251487</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.644278569616771</v>
+        <v>1.931639210740165</v>
       </c>
     </row>
     <row r="1884">
@@ -44880,19 +44880,19 @@
         <v>3.493716014390584</v>
       </c>
       <c r="C1884" t="n">
-        <v>3.161954003143605</v>
+        <v>3.476345141729612</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.48449504227094</v>
+        <v>-10.63753335885777</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.032200438078519</v>
+        <v>-0.7790246261272431</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.623274892729527</v>
+        <v>-2.668325721833884</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.587989067505889</v>
+        <v>1.875349708629283</v>
       </c>
     </row>
     <row r="1885">
@@ -44903,19 +44903,19 @@
         <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
-        <v>3.16464773177272</v>
+        <v>3.479038870358727</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.61053183563923</v>
+        <v>-10.76357015222606</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.07992142679672</v>
+        <v>-0.8267456148454442</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.598023269919785</v>
+        <v>-2.643074099024141</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.605833769820849</v>
+        <v>1.893194410944242</v>
       </c>
     </row>
     <row r="1886">
@@ -44926,19 +44926,19 @@
         <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
-        <v>3.168638067459121</v>
+        <v>3.483029206045128</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.55851632167042</v>
+        <v>-10.71155463825725</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.055124885522794</v>
+        <v>-0.8019490735715182</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.598023269919785</v>
+        <v>-2.643074099024141</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.60982410550725</v>
+        <v>1.897184746630643</v>
       </c>
     </row>
     <row r="1887">
@@ -44949,19 +44949,19 @@
         <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
-        <v>3.167162840560379</v>
+        <v>3.481553979146386</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.70018816339454</v>
+        <v>-10.85322647998137</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.113268849111184</v>
+        <v>-0.860093037159908</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.598023269919785</v>
+        <v>-2.643074099024141</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.608348878608508</v>
+        <v>1.895709519731902</v>
       </c>
     </row>
     <row r="1888">
@@ -44972,19 +44972,19 @@
         <v>3.691571733940718</v>
       </c>
       <c r="C1888" t="n">
-        <v>3.182216250725251</v>
+        <v>3.496607389311258</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.6505973189697</v>
+        <v>-10.80363563555653</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.078379101176378</v>
+        <v>-0.8252032892251013</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.548432425494951</v>
+        <v>-2.593483254599307</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.653156795428281</v>
+        <v>1.940517436551674</v>
       </c>
     </row>
     <row r="1889">
@@ -44995,19 +44995,19 @@
         <v>3.676841549770579</v>
       </c>
       <c r="C1889" t="n">
-        <v>3.169165117078568</v>
+        <v>3.483556255664575</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.63778992596493</v>
+        <v>-10.79082824255176</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.086307277621151</v>
+        <v>-0.8331314656698754</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.597288200503852</v>
+        <v>-2.642339029608209</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.610792196776257</v>
+        <v>1.898152837899651</v>
       </c>
     </row>
     <row r="1890">
@@ -45018,19 +45018,19 @@
         <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
-        <v>3.178744190114777</v>
+        <v>3.493135328700784</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.41194477324552</v>
+        <v>-10.56498308983235</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.9863901434971782</v>
+        <v>-0.7332143315459017</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.555361524916688</v>
+        <v>-2.600412354021045</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.645527275164764</v>
+        <v>1.932887916288157</v>
       </c>
     </row>
     <row r="1891">
@@ -45041,19 +45041,19 @@
         <v>3.684843823812101</v>
       </c>
       <c r="C1891" t="n">
-        <v>3.179883334670836</v>
+        <v>3.494274473256843</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.28736611690793</v>
+        <v>-10.44040443349475</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9354195364060822</v>
+        <v>-0.6822437244548056</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.555361524916688</v>
+        <v>-2.600412354021045</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.646666419720823</v>
+        <v>1.934027060844216</v>
       </c>
     </row>
     <row r="1892">
@@ -45064,19 +45064,19 @@
         <v>3.710935533646215</v>
       </c>
       <c r="C1892" t="n">
-        <v>3.182517108832943</v>
+        <v>3.496908247418951</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.34026140495221</v>
+        <v>-10.49329972153904</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9539438774616897</v>
+        <v>-0.7007680655104132</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.550406178828242</v>
+        <v>-2.595457007932599</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.652273401535998</v>
+        <v>1.939634042659391</v>
       </c>
     </row>
     <row r="1893">
@@ -45087,19 +45087,19 @@
         <v>3.768951674611567</v>
       </c>
       <c r="C1893" t="n">
-        <v>3.18825081307158</v>
+        <v>3.502641951657587</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.26812822966433</v>
+        <v>-10.42116654625116</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.919356903107901</v>
+        <v>-0.6661810911566244</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.550406178828242</v>
+        <v>-2.595457007932599</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.658007105774635</v>
+        <v>1.945367746898028</v>
       </c>
     </row>
     <row r="1894">
@@ -45110,19 +45110,19 @@
         <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
-        <v>3.178513550677715</v>
+        <v>3.492904689263722</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.19676183705469</v>
+        <v>-10.34980015364151</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9005476084579067</v>
+        <v>-0.6473717965066301</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.479039786218594</v>
+        <v>-2.524090615322951</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.691089678946559</v>
+        <v>1.978450320069952</v>
       </c>
     </row>
     <row r="1895">
@@ -45133,19 +45133,19 @@
         <v>3.747702660232412</v>
       </c>
       <c r="C1895" t="n">
-        <v>3.168630069364807</v>
+        <v>3.483021207950814</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.10330280306946</v>
+        <v>-10.25634111965629</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8730474761767248</v>
+        <v>-0.6198716642254483</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.479039786218594</v>
+        <v>-2.524090615322951</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.681206197633651</v>
+        <v>1.968566838757044</v>
       </c>
     </row>
     <row r="1896">
@@ -45156,19 +45156,19 @@
         <v>3.766317079436228</v>
       </c>
       <c r="C1896" t="n">
-        <v>3.166795508865433</v>
+        <v>3.481186647451441</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.00420955356372</v>
+        <v>-9.98909931878789</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.8352447368738027</v>
+        <v>-0.5148095043774625</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.479039786218594</v>
+        <v>-2.524090615322951</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.679371637134277</v>
+        <v>1.966732278257671</v>
       </c>
     </row>
     <row r="1897">
@@ -45179,19 +45179,19 @@
         <v>3.784684521311949</v>
       </c>
       <c r="C1897" t="n">
-        <v>3.166495193891973</v>
+        <v>3.48088633247798</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.906302514887232</v>
+        <v>-9.891192280111399</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7963822363766675</v>
+        <v>-0.4759470038803273</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.411054036358038</v>
+        <v>-2.456104865462394</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.71986277207715</v>
+        <v>2.007223413200544</v>
       </c>
     </row>
     <row r="1898">
@@ -45202,19 +45202,19 @@
         <v>3.800829354097244</v>
       </c>
       <c r="C1898" t="n">
-        <v>3.167163700037466</v>
+        <v>3.481554838623473</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.882348973911274</v>
+        <v>-9.867238739135441</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7861323138407905</v>
+        <v>-0.4656970813444503</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.38710049538208</v>
+        <v>-2.432151324486437</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.734903402808218</v>
+        <v>2.022264043931612</v>
       </c>
     </row>
     <row r="1899">
@@ -45225,19 +45225,19 @@
         <v>3.789311112017772</v>
       </c>
       <c r="C1899" t="n">
-        <v>3.153903383875714</v>
+        <v>3.468294522461721</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.618289035588477</v>
+        <v>-9.603178800812644</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6937686546734243</v>
+        <v>-0.3733334221770841</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.123040557059284</v>
+        <v>-2.168091386163641</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.880079049640144</v>
+        <v>2.167439690763537</v>
       </c>
     </row>
     <row r="1900">
@@ -45248,19 +45248,19 @@
         <v>3.833252747839724</v>
       </c>
       <c r="C1900" t="n">
-        <v>3.151116350215413</v>
+        <v>3.46550748880142</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.91120941208364</v>
+        <v>-8.896099177307807</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.4137238389317899</v>
+        <v>-0.09328860643544967</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.123040557059284</v>
+        <v>-2.168091386163641</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.877292015979843</v>
+        <v>2.164652657103236</v>
       </c>
     </row>
     <row r="1901">
@@ -45271,19 +45271,19 @@
         <v>3.839374447388726</v>
       </c>
       <c r="C1901" t="n">
-        <v>3.151459974103255</v>
+        <v>3.465851112689262</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.871025113717449</v>
+        <v>-8.855914878941617</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3973064956974723</v>
+        <v>-0.07687126320113213</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.082856258693093</v>
+        <v>-2.12790708779745</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.901746218887399</v>
+        <v>2.189106860010792</v>
       </c>
     </row>
     <row r="1902">
@@ -45294,19 +45294,19 @@
         <v>3.856161751626472</v>
       </c>
       <c r="C1902" t="n">
-        <v>3.150826795324011</v>
+        <v>3.465217933910019</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.707625242778086</v>
+        <v>-8.692515008002253</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.3325797261009704</v>
+        <v>-0.01214449360463021</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.919456387753731</v>
+        <v>-1.964507216858087</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.999152962671773</v>
+        <v>2.286513603795167</v>
       </c>
     </row>
     <row r="1903">
@@ -45317,19 +45317,19 @@
         <v>3.787330429291809</v>
       </c>
       <c r="C1903" t="n">
-        <v>3.158751224161864</v>
+        <v>3.473142362747871</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.474144020548486</v>
+        <v>-8.459033785772654</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.231262808371278</v>
+        <v>0.08917242412506221</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.685975165524132</v>
+        <v>-1.731025994628489</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.147166124847385</v>
+        <v>2.434526765970778</v>
       </c>
     </row>
     <row r="1904">
@@ -45340,19 +45340,19 @@
         <v>3.801637122785786</v>
       </c>
       <c r="C1904" t="n">
-        <v>3.155859013848905</v>
+        <v>3.470250152434912</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.324477629540972</v>
+        <v>-8.30936739476514</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1742884622812317</v>
+        <v>0.1461467702151085</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.593071674281596</v>
+        <v>-1.638122503385953</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.200016009279947</v>
+        <v>2.48737665040334</v>
       </c>
     </row>
     <row r="1905">
@@ -45363,19 +45363,19 @@
         <v>3.763182248390426</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.151226500595932</v>
+        <v>3.465617639181939</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.192202155910085</v>
+        <v>-8.177091921134252</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.1260107860818498</v>
+        <v>0.1944244464144904</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.46079620065071</v>
+        <v>-1.505847029755066</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.274748780205506</v>
+        <v>2.562109421328899</v>
       </c>
     </row>
     <row r="1906">
@@ -45386,19 +45386,19 @@
         <v>3.784718794105951</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.154041561283568</v>
+        <v>3.468432699869576</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.001602481236933</v>
+        <v>-7.9864922464611</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.04695585552495185</v>
+        <v>0.2734793769713884</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.270196525977557</v>
+        <v>-1.315247355081913</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.391923645697035</v>
+        <v>2.679284286820428</v>
       </c>
     </row>
     <row r="1907">
@@ -45409,19 +45409,19 @@
         <v>3.753882571960985</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.166947902507227</v>
+        <v>3.481339041093234</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.752602682553352</v>
+        <v>-7.737492447777519</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.06555040517213939</v>
+        <v>0.3859856376684796</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.270196525977557</v>
+        <v>-1.315247355081913</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.404829986920693</v>
+        <v>2.692190628044087</v>
       </c>
     </row>
     <row r="1908">
@@ -45432,19 +45432,19 @@
         <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
-        <v>3.038971972908008</v>
+        <v>3.353363111494016</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.858192672326457</v>
+        <v>-7.843082437550623</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.1046615203363213</v>
+        <v>0.2157737121600189</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.375786515750661</v>
+        <v>-1.420837344855018</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.213500063457612</v>
+        <v>2.500860704581005</v>
       </c>
     </row>
     <row r="1909">
@@ -45455,19 +45455,19 @@
         <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.087516314785095</v>
+        <v>3.401907453371102</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.876927574445054</v>
+        <v>-7.86181733966922</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.06361113930667361</v>
+        <v>0.2568240931896666</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.381382525410792</v>
+        <v>-1.426433354515149</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.25868679953862</v>
+        <v>2.546047440662013</v>
       </c>
     </row>
     <row r="1910">
@@ -45478,19 +45478,19 @@
         <v>3.76033368671081</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.967637392096927</v>
+        <v>3.282028530682934</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.728987533037454</v>
+        <v>-7.713877298261621</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1243140454318015</v>
+        <v>0.1961211870645387</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.361061609502235</v>
+        <v>-1.406112438606591</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.151000426395587</v>
+        <v>2.43836106751898</v>
       </c>
     </row>
     <row r="1911">
@@ -45501,19 +45501,19 @@
         <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.958923405843449</v>
+        <v>3.273314544429456</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.676018010783466</v>
+        <v>-7.660907776007632</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.1118402227836843</v>
+        <v>0.2085950097126559</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.308092087248246</v>
+        <v>-1.353142916352602</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.174068153494502</v>
+        <v>2.461428794617895</v>
       </c>
     </row>
     <row r="1912">
@@ -45524,19 +45524,19 @@
         <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.951962793748356</v>
+        <v>3.266353932334363</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.632469604012775</v>
+        <v>-7.617359369236942</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.1013814721705013</v>
+        <v>0.2190537603258389</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.308092087248246</v>
+        <v>-1.353142916352602</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.167107541399409</v>
+        <v>2.454468182522802</v>
       </c>
     </row>
     <row r="1913">
@@ -45547,19 +45547,19 @@
         <v>3.782922533493418</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.966425148129499</v>
+        <v>3.280816286715506</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.390321210558917</v>
+        <v>-7.375210975783084</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.009940239592185041</v>
+        <v>0.3303754720885252</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.308092087248246</v>
+        <v>-1.353142916352602</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.181569895780552</v>
+        <v>2.468930536903945</v>
       </c>
     </row>
     <row r="1914">
@@ -45570,19 +45570,19 @@
         <v>3.828551486722815</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.960957268588694</v>
+        <v>3.275348407174701</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.282062073436395</v>
+        <v>-7.266951838660562</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.04777601490038874</v>
+        <v>0.3682112473967289</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.308092087248246</v>
+        <v>-1.353142916352602</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.176102016239747</v>
+        <v>2.46346265736314</v>
       </c>
     </row>
     <row r="1915">
@@ -45593,19 +45593,19 @@
         <v>3.828052928792045</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.958455362599271</v>
+        <v>3.272846501185278</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.158770938619265</v>
+        <v>-7.143660703843431</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.09459056283781786</v>
+        <v>0.4150257953341581</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.184800952431115</v>
+        <v>-1.229851781535472</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.247574791140602</v>
+        <v>2.534935432263995</v>
       </c>
     </row>
     <row r="1916">
@@ -45616,19 +45616,19 @@
         <v>3.812453678919906</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.966156340836596</v>
+        <v>3.280547479422603</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.137621739715821</v>
+        <v>-7.122511504939988</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1107512206365207</v>
+        <v>0.4311864531328609</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.163651753527672</v>
+        <v>-1.208702582632029</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.267965288719993</v>
+        <v>2.555325929843387</v>
       </c>
     </row>
     <row r="1917">
@@ -45639,19 +45639,19 @@
         <v>3.748328408318091</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.961937049183647</v>
+        <v>3.276328187769654</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.893856297732377</v>
+        <v>-6.878746062956544</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2040381057769491</v>
+        <v>0.5244733382732893</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.163651753527672</v>
+        <v>-1.208702582632029</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.263745997067044</v>
+        <v>2.551106638190437</v>
       </c>
     </row>
     <row r="1918">
@@ -45662,19 +45662,19 @@
         <v>3.824311233057524</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.964061363103663</v>
+        <v>3.27845250168967</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.792093477455082</v>
+        <v>-6.776983242679249</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.246867547807883</v>
+        <v>0.5673027803042232</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.150432685135243</v>
+        <v>-1.1954835142396</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.273801752022517</v>
+        <v>2.56116239314591</v>
       </c>
     </row>
     <row r="1919">
@@ -45685,19 +45685,19 @@
         <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.956803438087365</v>
+        <v>3.271194576673372</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.542243083506007</v>
+        <v>-6.527132848730174</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3395497803712151</v>
+        <v>0.6599850128675553</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.150432685135243</v>
+        <v>-1.1954835142396</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.266543827006219</v>
+        <v>2.553904468129613</v>
       </c>
     </row>
     <row r="1920">
@@ -45708,19 +45708,19 @@
         <v>3.835957987011497</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.960402561608014</v>
+        <v>3.274793700194021</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.366350991038575</v>
+        <v>-6.351240756262742</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4135057408788363</v>
+        <v>0.7339409733751765</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.150432685135243</v>
+        <v>-1.1954835142396</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.270142950526868</v>
+        <v>2.557503591650261</v>
       </c>
     </row>
     <row r="1921">
@@ -45731,19 +45731,19 @@
         <v>3.780933911392985</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.973730067662567</v>
+        <v>3.288121206248575</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.194904528016112</v>
+        <v>-6.179794293240279</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4954118321423757</v>
+        <v>0.8158470646387159</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.9789862221127802</v>
+        <v>-1.024037051217137</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.3863383343949</v>
+        <v>2.673698975518293</v>
       </c>
     </row>
     <row r="1922">
@@ -45754,19 +45754,19 @@
         <v>3.77376522263278</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.972750545278864</v>
+        <v>3.287141683864871</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.120614962277773</v>
+        <v>-6.105504727501939</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5241481360540083</v>
+        <v>0.8445833685503485</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.904696656374441</v>
+        <v>-0.9497474854787973</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.4299325514542</v>
+        <v>2.717293192577594</v>
       </c>
     </row>
     <row r="1923">
@@ -45777,19 +45777,19 @@
         <v>3.764617879883072</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.977445346333182</v>
+        <v>3.291836484919189</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.056979220043838</v>
+        <v>-6.041868985268005</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5542972340018992</v>
+        <v>0.8747324664982394</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.8410609141405064</v>
+        <v>-0.8861117432448627</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.472808797848878</v>
+        <v>2.760169438972271</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074782</v>
+        <v>3.798814771074781</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.958639605116977</v>
+        <v>3.273030743702984</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.945552460717918</v>
+        <v>-5.930442225942085</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5800621965160628</v>
+        <v>0.900497429012403</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.8410609141405064</v>
+        <v>-0.8861117432448627</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.454003056632674</v>
+        <v>2.741363697756067</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242294</v>
+        <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.960382681741855</v>
+        <v>3.274773820327862</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.705121963913058</v>
+        <v>-5.851576710101368</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6779774718628846</v>
+        <v>0.9337867119735672</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.6006304173356461</v>
+        <v>-0.8072462274041464</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.600004431340467</v>
+        <v>2.790426083885374</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367685</v>
+        <v>3.821593509367684</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.964311995576675</v>
+        <v>3.278703134162682</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.632879395741863</v>
+        <v>-5.779334141930174</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7108038129661827</v>
+        <v>0.9666130530768653</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.6006304173356461</v>
+        <v>-0.8072462274041464</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.603933745175287</v>
+        <v>2.794355397720194</v>
       </c>
     </row>
     <row r="1927">
@@ -45869,19 +45869,19 @@
         <v>3.822326997879966</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.964990579494015</v>
+        <v>3.279381718080022</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.579881073460475</v>
+        <v>-5.726335819648786</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7326817257960778</v>
+        <v>0.9884909659067604</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.5452941583337073</v>
+        <v>-0.7519099684022076</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.637814084493791</v>
+        <v>2.828235737038698</v>
       </c>
     </row>
     <row r="1928">
@@ -45892,19 +45892,19 @@
         <v>3.848616626502338</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.961988650714008</v>
+        <v>3.276379789300015</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.471076187980748</v>
+        <v>-5.617530934169059</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7732017512079619</v>
+        <v>1.029010991318644</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.5452941583337073</v>
+        <v>-0.7519099684022076</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.634812155713784</v>
+        <v>2.825233808258691</v>
       </c>
     </row>
     <row r="1929">
@@ -45915,19 +45915,19 @@
         <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.963567687724622</v>
+        <v>3.27795882631063</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.251055389943738</v>
+        <v>-5.397510136132048</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8627891074333802</v>
+        <v>1.118598347544063</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4040743132657271</v>
+        <v>-0.6106901233342273</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.721123099765186</v>
+        <v>2.911544752310093</v>
       </c>
     </row>
     <row r="1930">
@@ -45938,19 +45938,19 @@
         <v>3.843274527539948</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.979461870526446</v>
+        <v>3.293853009112453</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.11818770088046</v>
+        <v>-5.264642447068771</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9318303658605149</v>
+        <v>1.187639605971198</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4040743132657271</v>
+        <v>-0.6106901233342273</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.73701728256701</v>
+        <v>2.927438935111917</v>
       </c>
     </row>
     <row r="1931">
@@ -45961,19 +45961,19 @@
         <v>3.845047386496258</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.980607714966748</v>
+        <v>3.294998853552755</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.998014617515961</v>
+        <v>-5.144469363704272</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9810454436466161</v>
+        <v>1.236854683757299</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.2839012299012281</v>
+        <v>-0.4905170399697284</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.810266977026011</v>
+        <v>3.000688629570918</v>
       </c>
     </row>
     <row r="1932">
@@ -45984,19 +45984,19 @@
         <v>3.791273551576994</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.990695817528187</v>
+        <v>3.305086956114195</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.853342472416224</v>
+        <v>-4.999797218604535</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.049002404247951</v>
+        <v>1.304811644358634</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.1392290848014907</v>
+        <v>-0.345844894869991</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.907158366647293</v>
+        <v>3.0975800191922</v>
       </c>
     </row>
     <row r="1933">
@@ -46007,19 +46007,19 @@
         <v>3.7358392229421</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.976733308929613</v>
+        <v>3.29112444751562</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.913217299773916</v>
+        <v>-5.059672045962227</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.0110899647063</v>
+        <v>1.266899204816982</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.1991039121591828</v>
+        <v>-0.4057197222276831</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.857270961634104</v>
+        <v>3.047692614179011</v>
       </c>
     </row>
     <row r="1934">
@@ -46030,19 +46030,19 @@
         <v>3.762647477674512</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.999133802252179</v>
+        <v>3.313524940838187</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.826417801994908</v>
+        <v>-4.972872548183219</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.068210257140469</v>
+        <v>1.324019497251152</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.1991039121591828</v>
+        <v>-0.4057197222276831</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.87967145495667</v>
+        <v>3.070093107501577</v>
       </c>
     </row>
     <row r="1935">
@@ -46053,19 +46053,19 @@
         <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.999206203625592</v>
+        <v>3.313597342211599</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.828887508456714</v>
+        <v>-4.975342254645025</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.067294775929159</v>
+        <v>1.323104016039842</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.201573618620989</v>
+        <v>-0.4081894286894893</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.878262032452998</v>
+        <v>3.068683684997906</v>
       </c>
     </row>
     <row r="1936">
@@ -46076,19 +46076,19 @@
         <v>3.743220196003598</v>
       </c>
       <c r="C1936" t="n">
-        <v>3.010213126100294</v>
+        <v>3.324604264686301</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.897257694780724</v>
+        <v>-5.043712440969035</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.050953623874257</v>
+        <v>1.30676286398494</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.192297919584774</v>
+        <v>-0.3989137296532743</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.89483437434943</v>
+        <v>3.085256026894336</v>
       </c>
     </row>
     <row r="1937">
@@ -46099,19 +46099,19 @@
         <v>3.714179139508366</v>
       </c>
       <c r="C1937" t="n">
-        <v>3.000649834732185</v>
+        <v>3.315040973318192</v>
       </c>
       <c r="D1937" t="n">
-        <v>-5.005795875696858</v>
+        <v>-5.152250621885169</v>
       </c>
       <c r="E1937" t="n">
-        <v>0.9979750601396946</v>
+        <v>1.253784300250377</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.192297919584774</v>
+        <v>-0.3989137296532743</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.885271082981321</v>
+        <v>3.075692735526228</v>
       </c>
     </row>
     <row r="1938">
@@ -46122,19 +46122,19 @@
         <v>3.710906731417701</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.825359399772572</v>
+        <v>3.139750538358579</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.036789035025564</v>
+        <v>-5.183243781213874</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8102873614485993</v>
+        <v>1.066096601559282</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.192297919584774</v>
+        <v>-0.3989137296532743</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.709980648021708</v>
+        <v>2.900402300566614</v>
       </c>
     </row>
     <row r="1939">
@@ -46145,19 +46145,19 @@
         <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.829926631764359</v>
+        <v>3.144317770350367</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.861314775233095</v>
+        <v>-5.007769521421405</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.8850442973573747</v>
+        <v>1.140853537468057</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.192297919584774</v>
+        <v>-0.3989137296532743</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.714547880013495</v>
+        <v>2.904969532558402</v>
       </c>
     </row>
     <row r="1940">
@@ -46168,19 +46168,19 @@
         <v>3.765024323225443</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.805668660525567</v>
+        <v>3.120059799111574</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.972251027874344</v>
+        <v>-5.118705774062654</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8164118250620822</v>
+        <v>1.072221065172765</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.192297919584774</v>
+        <v>-0.3989137296532743</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.690289908774703</v>
+        <v>2.880711561319609</v>
       </c>
     </row>
     <row r="1941">
@@ -46191,19 +46191,19 @@
         <v>3.773210297111291</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.808800045745472</v>
+        <v>3.123191184331479</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.980533102019402</v>
+        <v>-5.126987848207713</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8162303806239644</v>
+        <v>1.072039620734647</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.2005799937298324</v>
+        <v>-0.4071958037983327</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.688452049507573</v>
+        <v>2.87887370205248</v>
       </c>
     </row>
     <row r="1942">
@@ -46214,19 +46214,19 @@
         <v>3.784343952264161</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.818972432177604</v>
+        <v>3.133363570763612</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.920680482815679</v>
+        <v>-5.067135229003989</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8503438147375859</v>
+        <v>1.106153054848269</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.2005799937298324</v>
+        <v>-0.4071958037983327</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.698624435939705</v>
+        <v>2.889046088484612</v>
       </c>
     </row>
     <row r="1943">
@@ -46237,19 +46237,19 @@
         <v>3.786949957742297</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.813918702751465</v>
+        <v>3.128309841337472</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.834437019789301</v>
+        <v>-4.980891765977612</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8797874705219972</v>
+        <v>1.13559671063268</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.2005799937298324</v>
+        <v>-0.4071958037983327</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.693570706513566</v>
+        <v>2.883992359058472</v>
       </c>
     </row>
     <row r="1944">
@@ -46260,19 +46260,19 @@
         <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.80569447819599</v>
+        <v>3.120085616781997</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.879743839188281</v>
+        <v>-5.026198585376592</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8534405182069309</v>
+        <v>1.109249758317614</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.2413901567390632</v>
+        <v>-0.4480059668075635</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.660860384152552</v>
+        <v>2.85128203669746</v>
       </c>
     </row>
     <row r="1945">
@@ -46283,19 +46283,19 @@
         <v>3.753571165803189</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.806246351229092</v>
+        <v>3.120637489815099</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.908776943890582</v>
+        <v>-5.055231690078893</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.842379149359112</v>
+        <v>1.098188389469795</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.2413901567390632</v>
+        <v>-0.4480059668075635</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.661412257185654</v>
+        <v>2.851833909730561</v>
       </c>
     </row>
     <row r="1946">
@@ -46306,19 +46306,19 @@
         <v>3.733390600809496</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.735519043120457</v>
+        <v>3.049910181706465</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.815966462439722</v>
+        <v>-4.962421208628033</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8087760338308216</v>
+        <v>1.064585273941504</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.1485796752882039</v>
+        <v>-0.3551954853567041</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.646371237947535</v>
+        <v>2.836792890492442</v>
       </c>
     </row>
     <row r="1947">
@@ -46329,19 +46329,19 @@
         <v>3.748285816560424</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.737392519045058</v>
+        <v>3.051783657631066</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.86035593176915</v>
+        <v>-5.006810677957461</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.7928937220236514</v>
+        <v>1.048702962134334</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.1929691446176315</v>
+        <v>-0.3995849546861318</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.62161103227448</v>
+        <v>2.812032684819387</v>
       </c>
     </row>
     <row r="1948">
@@ -46352,19 +46352,19 @@
         <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.732468227556781</v>
+        <v>3.046859366142789</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.7476847135329</v>
+        <v>-4.89413945972121</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8330379178298744</v>
+        <v>1.088847157940557</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.08029792638138133</v>
+        <v>-0.2869137364498816</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.684289471727953</v>
+        <v>2.87471112427286</v>
       </c>
     </row>
     <row r="1949">
@@ -46375,19 +46375,19 @@
         <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.737959523387449</v>
+        <v>3.052350661973456</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.635307712350227</v>
+        <v>-4.781762458538537</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.8834800141336108</v>
+        <v>1.139289254244293</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.08029792638138133</v>
+        <v>-0.2869137364498816</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.68978076755862</v>
+        <v>2.880202420103527</v>
       </c>
     </row>
     <row r="1950">
@@ -46398,19 +46398,19 @@
         <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.749456725155988</v>
+        <v>3.063847863741995</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.66308811025158</v>
+        <v>-4.80954285643989</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8838650567416089</v>
+        <v>1.139674296852291</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1080783242827344</v>
+        <v>-0.3146941343512347</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.684609730586347</v>
+        <v>2.875031383131254</v>
       </c>
     </row>
     <row r="1951">
@@ -46421,19 +46421,19 @@
         <v>3.643069621705323</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.587812445156641</v>
+        <v>2.902203583742648</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.746089391276858</v>
+        <v>-4.892544137465169</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6890202643321506</v>
+        <v>0.9448295044428332</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.1266492088099082</v>
+        <v>-0.3332650188784084</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.511822919870696</v>
+        <v>2.702244572415603</v>
       </c>
     </row>
     <row r="1952">
@@ -46444,19 +46444,19 @@
         <v>3.682716310729268</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.707962105875847</v>
+        <v>3.022353244461854</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.85470346972019</v>
+        <v>-5.0011582159085</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7657242936740238</v>
+        <v>1.021533533784706</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.1266492088099082</v>
+        <v>-0.3332650188784084</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.631972580589902</v>
+        <v>2.822394233134809</v>
       </c>
     </row>
     <row r="1953">
@@ -46467,19 +46467,19 @@
         <v>3.733012441190767</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.722475131978169</v>
+        <v>3.036866270564177</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.941302052701293</v>
+        <v>-5.087756798889603</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7455978865839055</v>
+        <v>1.001407126694588</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.1266492088099082</v>
+        <v>-0.3332650188784084</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.646485606692225</v>
+        <v>2.836907259237132</v>
       </c>
     </row>
     <row r="1954">
@@ -46490,19 +46490,19 @@
         <v>3.741174069913424</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.719894573320538</v>
+        <v>3.034285711906545</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.902918390143141</v>
+        <v>-5.049373136331452</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.7583707929495347</v>
+        <v>1.014180033060217</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.08826554625175698</v>
+        <v>-0.2948813563202572</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.666935245569484</v>
+        <v>2.857356898114391</v>
       </c>
     </row>
     <row r="1955">
@@ -46513,19 +46513,19 @@
         <v>3.751147197532485</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.71662360216584</v>
+        <v>3.031014740751847</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.725802060107975</v>
+        <v>-4.872256806296286</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8259463538089031</v>
+        <v>1.081755593919586</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.08826554625175698</v>
+        <v>-0.2948813563202572</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.663664274414786</v>
+        <v>2.854085926959693</v>
       </c>
     </row>
     <row r="1956">
@@ -46536,19 +46536,19 @@
         <v>3.741328448793903</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.717306993927753</v>
+        <v>3.03169813251376</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.770894304941521</v>
+        <v>-4.917349051129832</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8085928476373978</v>
+        <v>1.06440208774808</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.1501615894211468</v>
+        <v>-0.356777399489647</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.627210040275065</v>
+        <v>2.817631692819972</v>
       </c>
     </row>
     <row r="1957">
@@ -46559,19 +46559,19 @@
         <v>3.750729377011236</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.711093969234168</v>
+        <v>3.025485107820175</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.591518883702753</v>
+        <v>-4.737973629891064</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.8741299914393192</v>
+        <v>1.129939231550002</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.006615168749571909</v>
+        <v>-0.2000006413189284</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.715063070483911</v>
+        <v>2.905484723028818</v>
       </c>
     </row>
     <row r="1958">
@@ -46582,19 +46582,19 @@
         <v>3.71699171898223</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.691901424565757</v>
+        <v>3.006292563151765</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.636533097223359</v>
+        <v>-4.78298784341167</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8369317613626668</v>
+        <v>1.092741001473349</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.0237337265650327</v>
+        <v>-0.230349536633533</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.677661188626738</v>
+        <v>2.868082841171645</v>
       </c>
     </row>
     <row r="1959">
@@ -46605,19 +46605,19 @@
         <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.697592986904703</v>
+        <v>3.01198412549071</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.903537607495794</v>
+        <v>-5.049992353684105</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.7358215195926385</v>
+        <v>0.9916307597033209</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2180967646079813</v>
+        <v>-0.4247125746764815</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.566734928139915</v>
+        <v>2.757156580684822</v>
       </c>
     </row>
     <row r="1960">
@@ -46628,19 +46628,19 @@
         <v>3.702309454760808</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.696796908801204</v>
+        <v>3.011188047387212</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.004735388932967</v>
+        <v>-5.151190135121277</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.6945463289142708</v>
+        <v>0.9503555690249534</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.2865055781533005</v>
+        <v>-0.4931213882218007</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.524893561909225</v>
+        <v>2.715315214454132</v>
       </c>
     </row>
     <row r="1961">
@@ -46651,19 +46651,19 @@
         <v>3.705571661815453</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.694396870355521</v>
+        <v>3.008788008941528</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.972259802762195</v>
+        <v>-5.118714548950505</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7051365249368964</v>
+        <v>0.9609457650475792</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.2865055781533005</v>
+        <v>-0.4931213882218007</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.522493523463541</v>
+        <v>2.712915176008448</v>
       </c>
     </row>
     <row r="1962">
@@ -46674,19 +46674,19 @@
         <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.690921589563766</v>
+        <v>3.005312728149773</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.953221675054897</v>
+        <v>-5.099676421243208</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7092764952280604</v>
+        <v>0.965085735338743</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.344689189484495</v>
+        <v>-0.5513049995529953</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.48410807587307</v>
+        <v>2.674529728417976</v>
       </c>
     </row>
     <row r="1963">
@@ -46697,19 +46697,19 @@
         <v>3.731064473131249</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.868503458502447</v>
+        <v>3.182894597088454</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.984348306205516</v>
+        <v>-5.130803052393826</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.8744077117064935</v>
+        <v>1.130216951817176</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.344689189484495</v>
+        <v>-0.5513049995529953</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.66168994481175</v>
+        <v>2.852111597356657</v>
       </c>
     </row>
     <row r="1964">
@@ -46720,19 +46720,19 @@
         <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.86933678748858</v>
+        <v>3.183727926074587</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.998215067539434</v>
+        <v>-5.144669813727744</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.8696943361590599</v>
+        <v>1.125503576269742</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.3825471062183179</v>
+        <v>-0.5891629162868182</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.63980852375759</v>
+        <v>2.830230176302497</v>
       </c>
     </row>
     <row r="1965">
@@ -46743,19 +46743,19 @@
         <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.875345317885506</v>
+        <v>3.189736456471513</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.018472366068392</v>
+        <v>-5.164927112256702</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.8675999471444027</v>
+        <v>1.123409187255085</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.3825471062183179</v>
+        <v>-0.5891629162868182</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.645817054154516</v>
+        <v>2.836238706699423</v>
       </c>
     </row>
     <row r="1966">
@@ -46766,19 +46766,19 @@
         <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.954497965677528</v>
+        <v>3.268889104263535</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.870729395833389</v>
+        <v>-5.0171841420217</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.005849783030426</v>
+        <v>1.261659023141108</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2147397489834348</v>
+        <v>-0.421355559051935</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.825654116287467</v>
+        <v>3.016075768832374</v>
       </c>
     </row>
     <row r="1967">
@@ -46789,19 +46789,19 @@
         <v>3.80224592918117</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.957291587209009</v>
+        <v>3.271682725795016</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.97274407836461</v>
+        <v>-5.119198824552921</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9678375315494181</v>
+        <v>1.223646771660101</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.2147397489834348</v>
+        <v>-0.421355559051935</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.828447737818948</v>
+        <v>3.018869390363855</v>
       </c>
     </row>
     <row r="1968">
@@ -46812,19 +46812,19 @@
         <v>3.805608985394729</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.957953935600667</v>
+        <v>3.272345074186675</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.966591372311826</v>
+        <v>-5.113046118500137</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9709609623621902</v>
+        <v>1.226770202472873</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.2085870429306505</v>
+        <v>-0.4152028529991507</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.832801709842277</v>
+        <v>3.023223362387184</v>
       </c>
     </row>
     <row r="1969">
@@ -46835,19 +46835,19 @@
         <v>3.798239794890609</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.957034412340778</v>
+        <v>3.271425550926785</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.983400670462328</v>
+        <v>-5.129855416650638</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9633177198420997</v>
+        <v>1.219126959952782</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.2253963410811521</v>
+        <v>-0.4320121511496524</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.821796607692087</v>
+        <v>3.012218260236994</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
-        <v>3.023369966137599</v>
+        <v>3.337761104723606</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.921102671686206</v>
+        <v>-5.067557417874516</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.054572473149369</v>
+        <v>1.310381713260052</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.2253963410811521</v>
+        <v>-0.4320121511496524</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.888132161488908</v>
+        <v>3.078553814033814</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.848729139992192</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.731950838526997</v>
+        <v>3.046341977113004</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.719312474021048</v>
+        <v>-4.865767220209358</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8438694246048306</v>
+        <v>1.099678664715513</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.02737814891199775</v>
+        <v>-0.233993958980498</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.715523949179798</v>
+        <v>2.905945601724705</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.802241070849172</v>
+        <v>3.116632209435179</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.659421792378454</v>
+        <v>-4.805876538566765</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9381159295840431</v>
+        <v>1.193925169694726</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.03251253273059573</v>
+        <v>-0.1741032773379045</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.821748590487529</v>
+        <v>3.012170243032437</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.819063300319546</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.816868806965215</v>
+        <v>3.131259945551223</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.757162337003429</v>
+        <v>-4.903617083191739</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9136474478500971</v>
+        <v>1.16945668796078</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.01662325459761554</v>
+        <v>-0.1899925554708847</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.826842759723785</v>
+        <v>3.017264412268692</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.815404787789887</v>
+        <v>3.129795926375894</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.933500097126358</v>
+        <v>-5.079954843314669</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.841648324625597</v>
+        <v>1.097457564736279</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.1597145055253139</v>
+        <v>-0.3663303155938141</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.719576084474699</v>
+        <v>2.909997737019606</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.813896405829816</v>
+        <v>3.128287544415823</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.861953774349481</v>
+        <v>-5.008408520537792</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8687584717762764</v>
+        <v>1.124567711886959</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.1597145055253139</v>
+        <v>-0.3663303155938141</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.718067702514628</v>
+        <v>2.908489355059535</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.836023391024961</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.813759273265252</v>
+        <v>3.128150411851259</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.817580642710912</v>
+        <v>-4.964035388899223</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8863705918671401</v>
+        <v>1.142179831977823</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.1153413738867453</v>
+        <v>-0.3219571839552455</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.744554448933205</v>
+        <v>2.934976101478112</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.821591150863222</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.813759273265252</v>
+        <v>3.128150411851259</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.80962667241614</v>
+        <v>-4.956081418604451</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.8895521799850488</v>
+        <v>1.145361420095731</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.1153413738867453</v>
+        <v>-0.3219571839552455</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.744554448933205</v>
+        <v>2.934976101478112</v>
       </c>
     </row>
     <row r="1978">
@@ -47042,19 +47042,19 @@
         <v>3.833040181947581</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.820141030293057</v>
+        <v>3.134532168879064</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.761970941855084</v>
+        <v>-4.908425688043395</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9149962292372757</v>
+        <v>1.170805469347958</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.0676856433256896</v>
+        <v>-0.2743014533941898</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.779529644297643</v>
+        <v>2.96995129684255</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822707244326874</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.825033403667781</v>
+        <v>3.139424542253789</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.634286632060788</v>
+        <v>-4.780741378249099</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.9709623265297191</v>
+        <v>1.226771566640402</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.05999866646860685</v>
+        <v>-0.1466171435998934</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.861032603548946</v>
+        <v>3.051454256093853</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.828837911314549</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.811788076143654</v>
+        <v>3.126179214729661</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.694953222463178</v>
+        <v>-4.841407968651488</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.9334503628446356</v>
+        <v>1.189259602955318</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.02169965024992682</v>
+        <v>-0.228315460318427</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.798768285993698</v>
+        <v>2.989189938538605</v>
       </c>
     </row>
     <row r="1981">
@@ -47111,19 +47111,19 @@
         <v>3.816866067690025</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.815885778754282</v>
+        <v>3.130276917340289</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.650114820854779</v>
+        <v>-4.79656956704309</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.9554834260986236</v>
+        <v>1.211292666209306</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.01715621730505734</v>
+        <v>-0.2237720273735576</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.805592048371248</v>
+        <v>2.996013700916155</v>
       </c>
     </row>
     <row r="1982">
@@ -47134,19 +47134,19 @@
         <v>3.817961388674309</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.82004671838536</v>
+        <v>3.134437856971367</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.750873456611777</v>
+        <v>-4.897328202800088</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.9193409114269024</v>
+        <v>1.175150151537585</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.1059817860320628</v>
+        <v>-0.312597596100563</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.756457646766123</v>
+        <v>2.94687929931103</v>
       </c>
     </row>
     <row r="1983">
@@ -47157,19 +47157,19 @@
         <v>3.826713779163218</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.825926320913197</v>
+        <v>3.140317459499204</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.706670619525877</v>
+        <v>-4.853125365714187</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.9429016487890998</v>
+        <v>1.198710888899782</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.06177894894616232</v>
+        <v>-0.2683947590146625</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.7888589515455</v>
+        <v>2.979280604090407</v>
       </c>
     </row>
     <row r="1984">
@@ -47180,19 +47180,19 @@
         <v>3.838228663022903</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.824336321382445</v>
+        <v>3.138727459968452</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.743649647189319</v>
+        <v>-4.89010439337763</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.9265200381929701</v>
+        <v>1.182329278303653</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.02480504715483178</v>
+        <v>-0.231420857223332</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.809453293089546</v>
+        <v>2.999874945634453</v>
       </c>
     </row>
     <row r="1985">
@@ -47203,19 +47203,19 @@
         <v>3.863924114042137</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.875584086565484</v>
+        <v>3.189975225151492</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.76370772605416</v>
+        <v>-4.910162472242471</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.9697445718300735</v>
+        <v>1.225553811940756</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.02480504715483178</v>
+        <v>-0.231420857223332</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.860701058272586</v>
+        <v>3.051122710817493</v>
       </c>
     </row>
     <row r="1986">
@@ -47226,19 +47226,19 @@
         <v>3.86536771507828</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.874024791159738</v>
+        <v>3.188415929745745</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.72377705287627</v>
+        <v>-4.87023179906458</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.9841575456954827</v>
+        <v>1.239966785806165</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.01512562602305856</v>
+        <v>-0.1914901840454417</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.883100166773573</v>
+        <v>3.07352181931848</v>
       </c>
     </row>
     <row r="1987">
@@ -47249,19 +47249,19 @@
         <v>3.864518876232397</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.868973019398008</v>
+        <v>3.183364157984015</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.672744960153742</v>
+        <v>-4.819199706342053</v>
       </c>
       <c r="E1987" t="n">
-        <v>0.9995186110227638</v>
+        <v>1.255327851133446</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.06615771874558651</v>
+        <v>-0.1404580913229137</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.90866765064536</v>
+        <v>3.099089303190267</v>
       </c>
     </row>
     <row r="1988">
@@ -47272,19 +47272,19 @@
         <v>3.842576394162113</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.886160423490713</v>
+        <v>3.20055156207672</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.607520779026537</v>
+        <v>-4.753975525214847</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.042795687566351</v>
+        <v>1.298604927677034</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.1313818998727921</v>
+        <v>-0.07523391019570808</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.964989563414388</v>
+        <v>3.155411215959295</v>
       </c>
     </row>
     <row r="1989">
@@ -47295,19 +47295,19 @@
         <v>3.840090220639818</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.882121395789993</v>
+        <v>3.196512534376</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.658015069383593</v>
+        <v>-4.804469815571903</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.018558943722809</v>
+        <v>1.274368183833491</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.0863611627467179</v>
+        <v>-0.1202546473217823</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.933938093438024</v>
+        <v>3.124359745982931</v>
       </c>
     </row>
     <row r="1990">
@@ -47318,19 +47318,19 @@
         <v>3.84519884274992</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.883378188121233</v>
+        <v>3.19776932670724</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.678126725418301</v>
+        <v>-4.824581471606612</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.011771073640166</v>
+        <v>1.267580313750849</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.0973885077441371</v>
+        <v>-0.1092273023243631</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.941811292767716</v>
+        <v>3.132232945312623</v>
       </c>
     </row>
     <row r="1991">
@@ -47341,19 +47341,19 @@
         <v>3.828690479393545</v>
       </c>
       <c r="C1991" t="n">
-        <v>3.043935959142444</v>
+        <v>3.358327097728451</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.775807304690947</v>
+        <v>-4.922262050879258</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.133256612952318</v>
+        <v>1.389065853063001</v>
       </c>
       <c r="F1991" t="n">
-        <v>-0.0133146875960517</v>
+        <v>-0.2199304976645519</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.035947146584813</v>
+        <v>3.226368799129721</v>
       </c>
     </row>
     <row r="1992">
@@ -47364,19 +47364,19 @@
         <v>3.813251854714883</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.164048868360261</v>
+        <v>3.478440006946268</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.752015736084805</v>
+        <v>-4.898470482273115</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.262886149612592</v>
+        <v>1.518695389723275</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.01047688101009059</v>
+        <v>-0.1961389290584096</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.170334996966316</v>
+        <v>3.360756649511223</v>
       </c>
     </row>
     <row r="1993">
@@ -47387,19 +47387,19 @@
         <v>3.81425976175601</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.15575684437412</v>
+        <v>3.470147982960127</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.788770154646527</v>
+        <v>-4.935224900834838</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.239892358201762</v>
+        <v>1.495701598312445</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.01047688101009059</v>
+        <v>-0.1961389290584096</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.162042972980175</v>
+        <v>3.352464625525082</v>
       </c>
     </row>
     <row r="1994">
@@ -47410,19 +47410,19 @@
         <v>3.803426852654185</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.1539500399579</v>
+        <v>3.468341178543907</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.784435851589479</v>
+        <v>-4.93089059777779</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.239819275008361</v>
+        <v>1.495628515119044</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.1621269843292945</v>
+        <v>-0.04448882573920571</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.251226230555477</v>
+        <v>3.441647883100384</v>
       </c>
     </row>
     <row r="1995">
@@ -47433,19 +47433,19 @@
         <v>3.796293177717115</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.171504445684691</v>
+        <v>3.485895584270698</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.775543390196196</v>
+        <v>-4.921998136384507</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.260930665292466</v>
+        <v>1.516739905403148</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.1621269843292945</v>
+        <v>-0.04448882573920571</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.268780636282268</v>
+        <v>3.459202288827175</v>
       </c>
     </row>
     <row r="1996">
@@ -47456,19 +47456,19 @@
         <v>3.794453975702623</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.163359493089275</v>
+        <v>3.477750631675282</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.944019507166074</v>
+        <v>-5.090474253354384</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.185395265909099</v>
+        <v>1.441204506019781</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.1341791486127137</v>
+        <v>-0.07243666145578648</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.243866982256904</v>
+        <v>3.434288634801811</v>
       </c>
     </row>
     <row r="1997">
@@ -47479,19 +47479,19 @@
         <v>3.795603100539966</v>
       </c>
       <c r="C1997" t="n">
-        <v>3.233772154546119</v>
+        <v>3.548163293132126</v>
       </c>
       <c r="D1997" t="n">
-        <v>-4.246219978304491</v>
+        <v>-4.392674724492801</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.534927738910576</v>
+        <v>1.790736979021258</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.06383108924230302</v>
+        <v>-0.1427847208261972</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.272070808091501</v>
+        <v>3.462492460636408</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784700379389896</v>
+        <v>3.784700379389895</v>
       </c>
       <c r="C1998" t="n">
-        <v>3.224436177043023</v>
+        <v>3.53882731562903</v>
       </c>
       <c r="D1998" t="n">
-        <v>-4.223498874621338</v>
+        <v>-4.369953620809649</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.534680202880741</v>
+        <v>1.790489442991424</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.06383108924230302</v>
+        <v>-0.1427847208261972</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.262734830588405</v>
+        <v>3.453156483133312</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.830315646565468</v>
+        <v>3.439368929008216</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.311991367564307</v>
+        <v>3.213559327802014</v>
       </c>
       <c r="D1999" t="n">
-        <v>-4.223498874621338</v>
+        <v>-4.369953620809649</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.534680202880741</v>
+        <v>1.790489442991424</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.06383108924230302</v>
+        <v>-0.1427847208261972</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.305055164550675</v>
+        <v>3.206623124788382</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240618.xlsx
+++ b/tame_output/ON/bt/strategyON_20240618.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>60.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>37.2%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -844,22 +844,22 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-5.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>8.8%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.9%</t>
+          <t>-76.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.2%</t>
+          <t>109.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.4%</t>
+          <t>124.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.2%</t>
+          <t>94.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.3%</t>
+          <t>-72.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>449.4%</t>
+          <t>454.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-11.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-598.6%</t>
+          <t>-586.5%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>49.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.3%</t>
+          <t>99.5%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-38.3%</t>
+          <t>-40.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-14.6%</t>
+          <t>-9.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>163.3%</t>
+          <t>182.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-197.2%</t>
+          <t>-223.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-24.5%</t>
+          <t>-23.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-18.8%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>198.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-162.0%</t>
+          <t>-166.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-238.3%</t>
+          <t>-227.1%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>94.3%</t>
+          <t>96.0%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-25.3%</t>
+          <t>-28.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.1%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-125.4%</t>
+          <t>-126.3%</t>
         </is>
       </c>
     </row>
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330521</v>
+        <v>3.30081581833052</v>
       </c>
       <c r="C1864" t="n">
-        <v>3.429831658529679</v>
+        <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
         <v>-6.689208895810287</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.7537916758918168</v>
+        <v>0.4394005373058096</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.548175094357108</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.500926601915414</v>
+        <v>2.186535463329407</v>
       </c>
     </row>
     <row r="1865">
@@ -44443,19 +44443,19 @@
         <v>3.302618194191735</v>
       </c>
       <c r="C1865" t="n">
-        <v>3.425017091001139</v>
+        <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.96578499612612</v>
+        <v>-6.956010906065385</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.6383466682369443</v>
+        <v>0.3278651656752309</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.548175094357108</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.496112034386875</v>
+        <v>2.181720895800868</v>
       </c>
     </row>
     <row r="1866">
@@ -44466,19 +44466,19 @@
         <v>3.305023265108638</v>
       </c>
       <c r="C1866" t="n">
-        <v>3.423011141610017</v>
+        <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.382176870413117</v>
+        <v>-7.372402780352382</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.4697839691310226</v>
+        <v>0.1593024665693097</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.548175094357108</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.494106084995752</v>
+        <v>2.179714946409745</v>
       </c>
     </row>
     <row r="1867">
@@ -44489,19 +44489,19 @@
         <v>3.34137872309782</v>
       </c>
       <c r="C1867" t="n">
-        <v>3.433269832278696</v>
+        <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.652942959505762</v>
+        <v>-7.643168869445027</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.3717362241626434</v>
+        <v>0.06125472160093048</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.548175094357108</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.504364775664431</v>
+        <v>2.189973637078424</v>
       </c>
     </row>
     <row r="1868">
@@ -44512,19 +44512,19 @@
         <v>3.374439043094116</v>
       </c>
       <c r="C1868" t="n">
-        <v>3.429369397424391</v>
+        <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.998817781490571</v>
+        <v>-7.989043691429837</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.2294858605144152</v>
+        <v>-0.08099564204729814</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.548175094357108</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.500464340810126</v>
+        <v>2.186073202224119</v>
       </c>
     </row>
     <row r="1869">
@@ -44535,19 +44535,19 @@
         <v>3.405960511199285</v>
       </c>
       <c r="C1869" t="n">
-        <v>3.427774317479392</v>
+        <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.162397659674955</v>
+        <v>-8.152623569614221</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.1624588292956628</v>
+        <v>-0.148022673266051</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.548175094357108</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.498869260865127</v>
+        <v>2.18447812227912</v>
       </c>
     </row>
     <row r="1870">
@@ -44558,19 +44558,19 @@
         <v>3.424633354969592</v>
       </c>
       <c r="C1870" t="n">
-        <v>3.4315532934086</v>
+        <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.459059001485153</v>
+        <v>-8.449284911424419</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.04757326850079169</v>
+        <v>-0.2629082340609221</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.616918230090987</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.461402355354008</v>
+        <v>2.147011216768001</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923085</v>
+        <v>3.419979433923086</v>
       </c>
       <c r="C1871" t="n">
-        <v>3.427526988874197</v>
+        <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.645778709794456</v>
+        <v>-8.636004619733722</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.03114091935733265</v>
+        <v>-0.3416224219190465</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.616918230090987</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.457376050819605</v>
+        <v>2.142984912233598</v>
       </c>
     </row>
     <row r="1872">
@@ -44604,19 +44604,19 @@
         <v>3.458100091297748</v>
       </c>
       <c r="C1872" t="n">
-        <v>3.427424887552613</v>
+        <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.028780098537087</v>
+        <v>-9.019006008476353</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.1844435761759691</v>
+        <v>-0.4949250787376829</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.616918230090987</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.457273949498021</v>
+        <v>2.142882810912014</v>
       </c>
     </row>
     <row r="1873">
@@ -44627,19 +44627,19 @@
         <v>3.447750501317615</v>
       </c>
       <c r="C1873" t="n">
-        <v>3.429996403524043</v>
+        <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.210649889522122</v>
+        <v>-9.200875799461388</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.2546199765985531</v>
+        <v>-0.5651014791602664</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.798788021076022</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.35072359087843</v>
+        <v>2.036332452292423</v>
       </c>
     </row>
     <row r="1874">
@@ -44650,19 +44650,19 @@
         <v>3.503515506737168</v>
       </c>
       <c r="C1874" t="n">
-        <v>3.435346706822093</v>
+        <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.570180212026123</v>
+        <v>-9.560406121965389</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.3930818023021034</v>
+        <v>-0.7035633048638168</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.798788021076022</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.35607389417648</v>
+        <v>2.041682755590473</v>
       </c>
     </row>
     <row r="1875">
@@ -44673,19 +44673,19 @@
         <v>3.503170282341311</v>
       </c>
       <c r="C1875" t="n">
-        <v>3.443262726779271</v>
+        <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.620529275480346</v>
+        <v>-9.610755185419611</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.4053054077266149</v>
+        <v>-0.7157869102883283</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.849137084530244</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.333780476061125</v>
+        <v>2.019389337475118</v>
       </c>
     </row>
     <row r="1876">
@@ -44696,19 +44696,19 @@
         <v>3.501052558539461</v>
       </c>
       <c r="C1876" t="n">
-        <v>3.44630447740104</v>
+        <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.718148552901742</v>
+        <v>-9.708374462841007</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.4413113680734044</v>
+        <v>-0.7517928706351178</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.946756361951641</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.278250660230055</v>
+        <v>1.963859521644048</v>
       </c>
     </row>
     <row r="1877">
@@ -44719,19 +44719,19 @@
         <v>3.492448711937497</v>
       </c>
       <c r="C1877" t="n">
-        <v>3.449198033722612</v>
+        <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.865674640907384</v>
+        <v>-9.85590055084665</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.4974282469540894</v>
+        <v>-0.8079097495158027</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.094282449957284</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.192628563748242</v>
+        <v>1.878237425162234</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141699</v>
+        <v>3.5027903991417</v>
       </c>
       <c r="C1878" t="n">
-        <v>3.454711230841254</v>
+        <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.06993281623725</v>
+        <v>-10.06015872617651</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.5736183199673928</v>
+        <v>-0.8840998225291061</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.221921394571273</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.121558394098491</v>
+        <v>1.807167255512484</v>
       </c>
     </row>
     <row r="1879">
@@ -44765,19 +44765,19 @@
         <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
-        <v>3.45919378532569</v>
+        <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.14426579249741</v>
+        <v>-10.13449170243668</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.5988689559870219</v>
+        <v>-0.9093504585487353</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.366620918505946</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.039221234222123</v>
+        <v>1.724830095636116</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440632</v>
+        <v>3.499971739440633</v>
       </c>
       <c r="C1880" t="n">
-        <v>3.474565486819111</v>
+        <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.07079596082996</v>
+        <v>-10.06102187076923</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.5541093218266218</v>
+        <v>-0.8645908243883351</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.293151086838497</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.098674834716014</v>
+        <v>1.784283696130006</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608599</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
-        <v>3.489120707566628</v>
+        <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.24592037821651</v>
+        <v>-10.23614628815577</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.6096038680337221</v>
+        <v>-0.9200853705954355</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.468275504225041</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.008155405031604</v>
+        <v>1.693764266445597</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587859441027</v>
+        <v>3.485878594410271</v>
       </c>
       <c r="C1882" t="n">
-        <v>3.481901542665032</v>
+        <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.480372472231</v>
+        <v>-10.47059838217026</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.7106038705411142</v>
+        <v>-1.021085373102828</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.468275504225041</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.000936240130008</v>
+        <v>1.686545101544001</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764395</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
-        <v>3.475229351891056</v>
+        <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.58474720325744</v>
+        <v>-10.57497311319671</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.7590259537256689</v>
+        <v>-1.069507456287382</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.572650235251487</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.931639210740165</v>
+        <v>1.617248072154157</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390584</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
-        <v>3.476345141729612</v>
+        <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.63753335885777</v>
+        <v>-10.62775926879704</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.7790246261272431</v>
+        <v>-1.089506128688956</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.668325721833884</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.875349708629283</v>
+        <v>1.560958570043275</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297398</v>
       </c>
       <c r="C1885" t="n">
-        <v>3.479038870358727</v>
+        <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.76357015222606</v>
+        <v>-10.75379606216532</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.8267456148454442</v>
+        <v>-1.137227117407158</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.643074099024141</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.893194410944242</v>
+        <v>1.578803272358235</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
-        <v>3.483029206045128</v>
+        <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.71155463825725</v>
+        <v>-10.70178054819651</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.8019490735715182</v>
+        <v>-1.112430576133232</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.643074099024141</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.897184746630643</v>
+        <v>1.582793608044636</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
-        <v>3.481553979146386</v>
+        <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.85322647998137</v>
+        <v>-10.84345238992063</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.860093037159908</v>
+        <v>-1.170574539721621</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.643074099024141</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.895709519731902</v>
+        <v>1.581318381145894</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940718</v>
+        <v>3.691571733940719</v>
       </c>
       <c r="C1888" t="n">
-        <v>3.496607389311258</v>
+        <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.80363563555653</v>
+        <v>-10.7938615454958</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.8252032892251013</v>
+        <v>-1.135684791786816</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.593483254599307</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.940517436551674</v>
+        <v>1.626126297965667</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770579</v>
+        <v>3.67684154977058</v>
       </c>
       <c r="C1889" t="n">
-        <v>3.483556255664575</v>
+        <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.79082824255176</v>
+        <v>-10.78105415249102</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.8331314656698754</v>
+        <v>-1.143612968231589</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.642339029608209</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.898152837899651</v>
+        <v>1.583761699313643</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
-        <v>3.493135328700784</v>
+        <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.56498308983235</v>
+        <v>-10.55520899977161</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.7332143315459017</v>
+        <v>-1.043695834107615</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.600412354021045</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.932887916288157</v>
+        <v>1.61849677770215</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812101</v>
+        <v>3.684843823812102</v>
       </c>
       <c r="C1891" t="n">
-        <v>3.494274473256843</v>
+        <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.44040443349475</v>
+        <v>-10.43063034343402</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.6822437244548056</v>
+        <v>-0.9927252270165199</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.600412354021045</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.934027060844216</v>
+        <v>1.619635922258209</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646215</v>
+        <v>3.710935533646216</v>
       </c>
       <c r="C1892" t="n">
-        <v>3.496908247418951</v>
+        <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.49329972153904</v>
+        <v>-10.48352563147831</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.7007680655104132</v>
+        <v>-1.011249568072127</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.595457007932599</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.939634042659391</v>
+        <v>1.625242904073384</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611567</v>
+        <v>3.768951674611568</v>
       </c>
       <c r="C1893" t="n">
-        <v>3.502641951657587</v>
+        <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.42116654625116</v>
+        <v>-10.41139245619043</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.6661810911566244</v>
+        <v>-0.9766625937183377</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.595457007932599</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.945367746898028</v>
+        <v>1.630976608312021</v>
       </c>
     </row>
     <row r="1894">
@@ -45110,19 +45110,19 @@
         <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
-        <v>3.492904689263722</v>
+        <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.34980015364151</v>
+        <v>-10.34002606358078</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.6473717965066301</v>
+        <v>-0.9578532990683435</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.524090615322951</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.978450320069952</v>
+        <v>1.664059181483945</v>
       </c>
     </row>
     <row r="1895">
@@ -45133,19 +45133,19 @@
         <v>3.747702660232412</v>
       </c>
       <c r="C1895" t="n">
-        <v>3.483021207950814</v>
+        <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.25634111965629</v>
+        <v>-10.24656702959555</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.6198716642254483</v>
+        <v>-0.9303531667871616</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.524090615322951</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.968566838757044</v>
+        <v>1.654175700171037</v>
       </c>
     </row>
     <row r="1896">
@@ -45156,19 +45156,19 @@
         <v>3.766317079436228</v>
       </c>
       <c r="C1896" t="n">
-        <v>3.481186647451441</v>
+        <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.98909931878789</v>
+        <v>-9.979325228727156</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.5148095043774625</v>
+        <v>-0.8252910069391763</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.524090615322951</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.966732278257671</v>
+        <v>1.652341139671663</v>
       </c>
     </row>
     <row r="1897">
@@ -45179,19 +45179,19 @@
         <v>3.784684521311949</v>
       </c>
       <c r="C1897" t="n">
-        <v>3.48088633247798</v>
+        <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.891192280111399</v>
+        <v>-9.881418190050665</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.4759470038803273</v>
+        <v>-0.7864285064420407</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.456104865462394</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.007223413200544</v>
+        <v>1.692832274614536</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097244</v>
+        <v>3.800829354097245</v>
       </c>
       <c r="C1898" t="n">
-        <v>3.481554838623473</v>
+        <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.867238739135441</v>
+        <v>-9.857464649074707</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.4656970813444503</v>
+        <v>-0.7761785839061641</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.432151324486437</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.022264043931612</v>
+        <v>1.707872905345605</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017772</v>
+        <v>3.789311112017773</v>
       </c>
       <c r="C1899" t="n">
-        <v>3.468294522461721</v>
+        <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.603178800812644</v>
+        <v>-9.59340471075191</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.3733334221770841</v>
+        <v>-0.6838149247387975</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.168091386163641</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.167439690763537</v>
+        <v>1.85304855217753</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839724</v>
+        <v>3.833252747839726</v>
       </c>
       <c r="C1900" t="n">
-        <v>3.46550748880142</v>
+        <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.896099177307807</v>
+        <v>-8.886325087247073</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.09328860643544967</v>
+        <v>-0.4037701089971635</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.168091386163641</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.164652657103236</v>
+        <v>1.850261518517229</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388726</v>
+        <v>3.839374447388729</v>
       </c>
       <c r="C1901" t="n">
-        <v>3.465851112689262</v>
+        <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.855914878941617</v>
+        <v>-8.846140788880883</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.07687126320113213</v>
+        <v>-0.3873527657628459</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.12790708779745</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.189106860010792</v>
+        <v>1.874715721424785</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626472</v>
+        <v>3.856161751626475</v>
       </c>
       <c r="C1902" t="n">
-        <v>3.465217933910019</v>
+        <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.692515008002253</v>
+        <v>-8.682740917941519</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.01214449360463021</v>
+        <v>-0.3226259961663436</v>
       </c>
       <c r="F1902" t="n">
         <v>-1.964507216858087</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.286513603795167</v>
+        <v>1.972122465209159</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291809</v>
+        <v>3.787330429291812</v>
       </c>
       <c r="C1903" t="n">
-        <v>3.473142362747871</v>
+        <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.459033785772654</v>
+        <v>-8.44925969571192</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.08917242412506221</v>
+        <v>-0.2213090784366516</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.731025994628489</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.434526765970778</v>
+        <v>2.120135627384771</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785786</v>
+        <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
-        <v>3.470250152434912</v>
+        <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.30936739476514</v>
+        <v>-8.299593304704405</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.1461467702151085</v>
+        <v>-0.1643347323466049</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.638122503385953</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.48737665040334</v>
+        <v>2.172985511817333</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390426</v>
+        <v>3.763182248390428</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.465617639181939</v>
+        <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.177091921134252</v>
+        <v>-8.167317831073518</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.1944244464144904</v>
+        <v>-0.1160570561472229</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.505847029755066</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.562109421328899</v>
+        <v>2.247718282742892</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105951</v>
+        <v>3.784718794105952</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.468432699869576</v>
+        <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.9864922464611</v>
+        <v>-7.976718156400366</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.2734793769713884</v>
+        <v>-0.03700212559032501</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.315247355081913</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.679284286820428</v>
+        <v>2.364893148234421</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960985</v>
+        <v>3.753882571960987</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.481339041093234</v>
+        <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.737492447777519</v>
+        <v>-7.727718357716785</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.3859856376684796</v>
+        <v>0.07550413510676579</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.315247355081913</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.692190628044087</v>
+        <v>2.377799489458079</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607646</v>
       </c>
       <c r="C1908" t="n">
-        <v>3.353363111494016</v>
+        <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.843082437550623</v>
+        <v>-7.833308347489889</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.2157737121600189</v>
+        <v>-0.09470779040169441</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.420837344855018</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.500860704581005</v>
+        <v>2.186469565994998</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.401907453371102</v>
+        <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.86181733966922</v>
+        <v>-7.852043249608486</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.2568240931896666</v>
+        <v>-0.05365740937204677</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.426433354515149</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.546047440662013</v>
+        <v>2.231656302076006</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.76033368671081</v>
+        <v>3.760333686710812</v>
       </c>
       <c r="C1910" t="n">
-        <v>3.282028530682934</v>
+        <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.713877298261621</v>
+        <v>-7.704103208200887</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.1961211870645387</v>
+        <v>-0.1143603154971746</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.406112438606591</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.43836106751898</v>
+        <v>2.123969928932973</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
-        <v>3.273314544429456</v>
+        <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.660907776007632</v>
+        <v>-7.651133685946898</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.2085950097126559</v>
+        <v>-0.1018864928490575</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.353142916352602</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.461428794617895</v>
+        <v>2.147037656031888</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.729969716098109</v>
       </c>
       <c r="C1912" t="n">
-        <v>3.266353932334363</v>
+        <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.617359369236942</v>
+        <v>-7.607585279176208</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.2190537603258389</v>
+        <v>-0.09142774223587447</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.353142916352602</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.454468182522802</v>
+        <v>2.140077043936795</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493418</v>
+        <v>3.78292253349342</v>
       </c>
       <c r="C1913" t="n">
-        <v>3.280816286715506</v>
+        <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.375210975783084</v>
+        <v>-7.36543688572235</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.3303754720885252</v>
+        <v>0.01989396952681188</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.353142916352602</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.468930536903945</v>
+        <v>2.154539398317938</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722815</v>
+        <v>3.828551486722817</v>
       </c>
       <c r="C1914" t="n">
-        <v>3.275348407174701</v>
+        <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.266951838660562</v>
+        <v>-7.257177748599828</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.3682112473967289</v>
+        <v>0.05772974483501558</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.353142916352602</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.46346265736314</v>
+        <v>2.149071518777133</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792045</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
-        <v>3.272846501185278</v>
+        <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.143660703843431</v>
+        <v>-7.133886613782697</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.4150257953341581</v>
+        <v>0.1045442927724447</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.229851781535472</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.534935432263995</v>
+        <v>2.220544293677988</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919906</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
-        <v>3.280547479422603</v>
+        <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.122511504939988</v>
+        <v>-7.112737414879254</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.4311864531328609</v>
+        <v>0.1207049505711471</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.208702582632029</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.555325929843387</v>
+        <v>2.240934791257379</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318091</v>
+        <v>3.748328408318093</v>
       </c>
       <c r="C1917" t="n">
-        <v>3.276328187769654</v>
+        <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.878746062956544</v>
+        <v>-6.868971972895809</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.5244733382732893</v>
+        <v>0.2139918357115755</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.208702582632029</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.551106638190437</v>
+        <v>2.23671549960443</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057524</v>
+        <v>3.824311233057526</v>
       </c>
       <c r="C1918" t="n">
-        <v>3.27845250168967</v>
+        <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.776983242679249</v>
+        <v>-6.767209152618515</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.5673027803042232</v>
+        <v>0.2568212777425094</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.1954835142396</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.56116239314591</v>
+        <v>2.246771254559903</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279184</v>
+        <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
-        <v>3.271194576673372</v>
+        <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.527132848730174</v>
+        <v>-6.51735875866944</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.6599850128675553</v>
+        <v>0.3495035103058415</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.1954835142396</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.553904468129613</v>
+        <v>2.239513329543605</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011497</v>
+        <v>3.835957987011499</v>
       </c>
       <c r="C1920" t="n">
-        <v>3.274793700194021</v>
+        <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.351240756262742</v>
+        <v>-6.341466666202008</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.7339409733751765</v>
+        <v>0.4234594708134631</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.1954835142396</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.557503591650261</v>
+        <v>2.243112453064254</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392985</v>
+        <v>3.780933911392987</v>
       </c>
       <c r="C1921" t="n">
-        <v>3.288121206248575</v>
+        <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.179794293240279</v>
+        <v>-6.170020203179544</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8158470646387159</v>
+        <v>0.5053655620770021</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.024037051217137</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.673698975518293</v>
+        <v>2.359307836932286</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.77376522263278</v>
+        <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
-        <v>3.287141683864871</v>
+        <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.105504727501939</v>
+        <v>-6.095730637441205</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.8445833685503485</v>
+        <v>0.5341018659886347</v>
       </c>
       <c r="F1922" t="n">
         <v>-0.9497474854787973</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.717293192577594</v>
+        <v>2.402902053991586</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883072</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
-        <v>3.291836484919189</v>
+        <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.041868985268005</v>
+        <v>-6.032094895207271</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.8747324664982394</v>
+        <v>0.5642509639365261</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.8861117432448627</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.760169438972271</v>
+        <v>2.445778300386264</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074781</v>
+        <v>3.798814771074783</v>
       </c>
       <c r="C1924" t="n">
-        <v>3.273030743702984</v>
+        <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.930442225942085</v>
+        <v>-5.920668135881351</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.900497429012403</v>
+        <v>0.5900159264506897</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.8861117432448627</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.741363697756067</v>
+        <v>2.42697255917006</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.797694884242294</v>
       </c>
       <c r="C1925" t="n">
-        <v>3.274773820327862</v>
+        <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.851576710101368</v>
+        <v>-5.68023763907649</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9337867119735672</v>
+        <v>0.687931201797511</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.8072462274041464</v>
+        <v>-0.6456812464400025</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.790426083885374</v>
+        <v>2.572973933877853</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367684</v>
+        <v>3.821593509367685</v>
       </c>
       <c r="C1926" t="n">
-        <v>3.278703134162682</v>
+        <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.779334141930174</v>
+        <v>-5.607995070905296</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9666130530768653</v>
+        <v>0.7207575429008091</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.8072462274041464</v>
+        <v>-0.6456812464400025</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.794355397720194</v>
+        <v>2.576903247712674</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879966</v>
+        <v>3.822326997879967</v>
       </c>
       <c r="C1927" t="n">
-        <v>3.279381718080022</v>
+        <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.726335819648786</v>
+        <v>-5.554996748623908</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9884909659067604</v>
+        <v>0.7426354557307042</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.7519099684022076</v>
+        <v>-0.5903449874380636</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.828235737038698</v>
+        <v>2.610783587031177</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502338</v>
+        <v>3.848616626502339</v>
       </c>
       <c r="C1928" t="n">
-        <v>3.276379789300015</v>
+        <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.617530934169059</v>
+        <v>-5.446191863144181</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.029010991318644</v>
+        <v>0.7831554811425887</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.7519099684022076</v>
+        <v>-0.5903449874380636</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.825233808258691</v>
+        <v>2.607781658251171</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675937</v>
+        <v>3.818668951675939</v>
       </c>
       <c r="C1929" t="n">
-        <v>3.27795882631063</v>
+        <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.397510136132048</v>
+        <v>-5.22617106510717</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.118598347544063</v>
+        <v>0.8727428373680071</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.6106901233342273</v>
+        <v>-0.4491251423700834</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.911544752310093</v>
+        <v>2.694092602302573</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539948</v>
+        <v>3.84327452753995</v>
       </c>
       <c r="C1930" t="n">
-        <v>3.293853009112453</v>
+        <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.264642447068771</v>
+        <v>-5.093303376043893</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.187639605971198</v>
+        <v>0.9417840957951413</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.6106901233342273</v>
+        <v>-0.4491251423700834</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.927438935111917</v>
+        <v>2.709986785104396</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496258</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
-        <v>3.294998853552755</v>
+        <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-5.144469363704272</v>
+        <v>-4.973130292679394</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.236854683757299</v>
+        <v>0.9909991735812427</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4905170399697284</v>
+        <v>-0.3289520590055844</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.000688629570918</v>
+        <v>2.783236479563397</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576994</v>
+        <v>3.791273551576996</v>
       </c>
       <c r="C1932" t="n">
-        <v>3.305086956114195</v>
+        <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.999797218604535</v>
+        <v>-4.828458147579656</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.304811644358634</v>
+        <v>1.058956134182578</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.345844894869991</v>
+        <v>-0.184279913905847</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.0975800191922</v>
+        <v>2.88012786918468</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.7358392229421</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
-        <v>3.29112444751562</v>
+        <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-5.059672045962227</v>
+        <v>-4.888332974937349</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.266899204816982</v>
+        <v>1.021043694640926</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.4057197222276831</v>
+        <v>-0.2441547412635391</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.047692614179011</v>
+        <v>2.83024046417149</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674512</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
-        <v>3.313524940838187</v>
+        <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.972872548183219</v>
+        <v>-4.80153347715834</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.324019497251152</v>
+        <v>1.078163987075096</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.4057197222276831</v>
+        <v>-0.2441547412635391</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.070093107501577</v>
+        <v>2.852640957494056</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430691</v>
+        <v>3.729146398430693</v>
       </c>
       <c r="C1935" t="n">
-        <v>3.313597342211599</v>
+        <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.975342254645025</v>
+        <v>-4.804003183620146</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.323104016039842</v>
+        <v>1.077248505863786</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.4081894286894893</v>
+        <v>-0.2466244477253453</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.068683684997906</v>
+        <v>2.851231534990385</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003598</v>
+        <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
-        <v>3.324604264686301</v>
+        <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-5.043712440969035</v>
+        <v>-4.872373369944157</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.30676286398494</v>
+        <v>1.060907353808884</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.3989137296532743</v>
+        <v>-0.2373487486891304</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.085256026894336</v>
+        <v>2.867803876886815</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508366</v>
+        <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
-        <v>3.315040973318192</v>
+        <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-5.152250621885169</v>
+        <v>-4.980911550860291</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.253784300250377</v>
+        <v>1.007928790074321</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.3989137296532743</v>
+        <v>-0.2373487486891304</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.075692735526228</v>
+        <v>2.858240585518707</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417701</v>
+        <v>3.710906731417702</v>
       </c>
       <c r="C1938" t="n">
-        <v>3.139750538358579</v>
+        <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.183243781213874</v>
+        <v>-5.011904710188996</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.066096601559282</v>
+        <v>0.8202410913832261</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.3989137296532743</v>
+        <v>-0.2373487486891304</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.900402300566614</v>
+        <v>2.682950150559094</v>
       </c>
     </row>
     <row r="1939">
@@ -46145,19 +46145,19 @@
         <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
-        <v>3.144317770350367</v>
+        <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-5.007769521421405</v>
+        <v>-4.836430450396527</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.140853537468057</v>
+        <v>0.8949980272920013</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.3989137296532743</v>
+        <v>-0.2373487486891304</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.904969532558402</v>
+        <v>2.687517382550881</v>
       </c>
     </row>
     <row r="1940">
@@ -46168,19 +46168,19 @@
         <v>3.765024323225443</v>
       </c>
       <c r="C1940" t="n">
-        <v>3.120059799111574</v>
+        <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-5.118705774062654</v>
+        <v>-4.947366703037776</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.072221065172765</v>
+        <v>0.8263655549967088</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.3989137296532743</v>
+        <v>-0.2373487486891304</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.880711561319609</v>
+        <v>2.663259411312088</v>
       </c>
     </row>
     <row r="1941">
@@ -46191,19 +46191,19 @@
         <v>3.773210297111291</v>
       </c>
       <c r="C1941" t="n">
-        <v>3.123191184331479</v>
+        <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-5.126987848207713</v>
+        <v>-4.955648777182835</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.072039620734647</v>
+        <v>0.826184110558591</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.4071958037983327</v>
+        <v>-0.2456308228341887</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.87887370205248</v>
+        <v>2.661421552044959</v>
       </c>
     </row>
     <row r="1942">
@@ -46214,19 +46214,19 @@
         <v>3.784343952264161</v>
       </c>
       <c r="C1942" t="n">
-        <v>3.133363570763612</v>
+        <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-5.067135229003989</v>
+        <v>-4.895796157979111</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.106153054848269</v>
+        <v>0.8602975446722125</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.4071958037983327</v>
+        <v>-0.2456308228341887</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.889046088484612</v>
+        <v>2.671593938477091</v>
       </c>
     </row>
     <row r="1943">
@@ -46237,19 +46237,19 @@
         <v>3.786949957742297</v>
       </c>
       <c r="C1943" t="n">
-        <v>3.128309841337472</v>
+        <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.980891765977612</v>
+        <v>-4.809552694952734</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.13559671063268</v>
+        <v>0.8897412004566241</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.4071958037983327</v>
+        <v>-0.2456308228341887</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.883992359058472</v>
+        <v>2.666540209050952</v>
       </c>
     </row>
     <row r="1944">
@@ -46260,19 +46260,19 @@
         <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
-        <v>3.120085616781997</v>
+        <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-5.026198585376592</v>
+        <v>-4.854859514351713</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.109249758317614</v>
+        <v>0.8633942481415575</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.4480059668075635</v>
+        <v>-0.2864409858434195</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.85128203669746</v>
+        <v>2.633829886689939</v>
       </c>
     </row>
     <row r="1945">
@@ -46283,19 +46283,19 @@
         <v>3.753571165803189</v>
       </c>
       <c r="C1945" t="n">
-        <v>3.120637489815099</v>
+        <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-5.055231690078893</v>
+        <v>-4.883892619054015</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.098188389469795</v>
+        <v>0.8523328792937388</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.4480059668075635</v>
+        <v>-0.2864409858434195</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.851833909730561</v>
+        <v>2.63438175972304</v>
       </c>
     </row>
     <row r="1946">
@@ -46306,19 +46306,19 @@
         <v>3.733390600809496</v>
       </c>
       <c r="C1946" t="n">
-        <v>3.049910181706465</v>
+        <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.962421208628033</v>
+        <v>-4.791082137603155</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.064585273941504</v>
+        <v>0.8187297637654483</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.3551954853567041</v>
+        <v>-0.1936305043925602</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.836792890492442</v>
+        <v>2.619340740484922</v>
       </c>
     </row>
     <row r="1947">
@@ -46329,19 +46329,19 @@
         <v>3.748285816560424</v>
       </c>
       <c r="C1947" t="n">
-        <v>3.051783657631066</v>
+        <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-5.006810677957461</v>
+        <v>-4.835471606932582</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.048702962134334</v>
+        <v>0.802847451958278</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.3995849546861318</v>
+        <v>-0.2380199737219879</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.812032684819387</v>
+        <v>2.594580534811866</v>
       </c>
     </row>
     <row r="1948">
@@ -46352,19 +46352,19 @@
         <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
-        <v>3.046859366142789</v>
+        <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.89413945972121</v>
+        <v>-4.722800388696332</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.088847157940557</v>
+        <v>0.8429916477645012</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.2869137364498816</v>
+        <v>-0.1253487554857377</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.87471112427286</v>
+        <v>2.657258974265339</v>
       </c>
     </row>
     <row r="1949">
@@ -46375,19 +46375,19 @@
         <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
-        <v>3.052350661973456</v>
+        <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.781762458538537</v>
+        <v>-4.610423387513659</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.139289254244293</v>
+        <v>0.8934337440682376</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.2869137364498816</v>
+        <v>-0.1253487554857377</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.880202420103527</v>
+        <v>2.662750270096006</v>
       </c>
     </row>
     <row r="1950">
@@ -46398,19 +46398,19 @@
         <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
-        <v>3.063847863741995</v>
+        <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.80954285643989</v>
+        <v>-4.638203785415012</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.139674296852291</v>
+        <v>0.8938187866762355</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.3146941343512347</v>
+        <v>-0.1531291533870907</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.875031383131254</v>
+        <v>2.657579233123733</v>
       </c>
     </row>
     <row r="1951">
@@ -46421,19 +46421,19 @@
         <v>3.643069621705323</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.902203583742648</v>
+        <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.892544137465169</v>
+        <v>-4.721205066440291</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9448295044428332</v>
+        <v>0.6989739942667772</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.3332650188784084</v>
+        <v>-0.1717000379142645</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.702244572415603</v>
+        <v>2.484792422408082</v>
       </c>
     </row>
     <row r="1952">
@@ -46444,19 +46444,19 @@
         <v>3.682716310729268</v>
       </c>
       <c r="C1952" t="n">
-        <v>3.022353244461854</v>
+        <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-5.0011582159085</v>
+        <v>-4.829819144883622</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.021533533784706</v>
+        <v>0.7756780236086505</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.3332650188784084</v>
+        <v>-0.1717000379142645</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.822394233134809</v>
+        <v>2.604942083127288</v>
       </c>
     </row>
     <row r="1953">
@@ -46467,19 +46467,19 @@
         <v>3.733012441190767</v>
       </c>
       <c r="C1953" t="n">
-        <v>3.036866270564177</v>
+        <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-5.087756798889603</v>
+        <v>-4.916417727864725</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.001407126694588</v>
+        <v>0.7555516165185323</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.3332650188784084</v>
+        <v>-0.1717000379142645</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.836907259237132</v>
+        <v>2.619455109229611</v>
       </c>
     </row>
     <row r="1954">
@@ -46490,19 +46490,19 @@
         <v>3.741174069913424</v>
       </c>
       <c r="C1954" t="n">
-        <v>3.034285711906545</v>
+        <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-5.049373136331452</v>
+        <v>-4.878034065306574</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.014180033060217</v>
+        <v>0.7683245228841613</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.2948813563202572</v>
+        <v>-0.1333163753561133</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.857356898114391</v>
+        <v>2.63990474810687</v>
       </c>
     </row>
     <row r="1955">
@@ -46513,19 +46513,19 @@
         <v>3.751147197532485</v>
       </c>
       <c r="C1955" t="n">
-        <v>3.031014740751847</v>
+        <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.872256806296286</v>
+        <v>-4.700917735271408</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.081755593919586</v>
+        <v>0.8359000837435298</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.2948813563202572</v>
+        <v>-0.1333163753561133</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.854085926959693</v>
+        <v>2.636633776952173</v>
       </c>
     </row>
     <row r="1956">
@@ -46536,19 +46536,19 @@
         <v>3.741328448793903</v>
       </c>
       <c r="C1956" t="n">
-        <v>3.03169813251376</v>
+        <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.917349051129832</v>
+        <v>-4.746009980104954</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.06440208774808</v>
+        <v>0.8185465775720244</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.356777399489647</v>
+        <v>-0.1952124185255031</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.817631692819972</v>
+        <v>2.600179542812452</v>
       </c>
     </row>
     <row r="1957">
@@ -46559,19 +46559,19 @@
         <v>3.750729377011236</v>
       </c>
       <c r="C1957" t="n">
-        <v>3.025485107820175</v>
+        <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.737973629891064</v>
+        <v>-4.566634558866186</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.129939231550002</v>
+        <v>0.8840837213739459</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.2000006413189284</v>
+        <v>-0.03843566035478441</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.905484723028818</v>
+        <v>2.688032573021297</v>
       </c>
     </row>
     <row r="1958">
@@ -46582,19 +46582,19 @@
         <v>3.71699171898223</v>
       </c>
       <c r="C1958" t="n">
-        <v>3.006292563151765</v>
+        <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.78298784341167</v>
+        <v>-4.611648772386792</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.092741001473349</v>
+        <v>0.8468854912972934</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.230349536633533</v>
+        <v>-0.06878455566938901</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.868082841171645</v>
+        <v>2.650630691164124</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.737026608509537</v>
       </c>
       <c r="C1959" t="n">
-        <v>3.01198412549071</v>
+        <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-5.049992353684105</v>
+        <v>-4.878653282659227</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9916307597033209</v>
+        <v>0.7457752495272651</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.4247125746764815</v>
+        <v>-0.2631475937123376</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.757156580684822</v>
+        <v>2.539704430677301</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760808</v>
+        <v>3.70230945476081</v>
       </c>
       <c r="C1960" t="n">
-        <v>3.011188047387212</v>
+        <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-5.151190135121277</v>
+        <v>-4.979851064096399</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9503555690249534</v>
+        <v>0.7045000588488974</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.4931213882218007</v>
+        <v>-0.3315564072576568</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.715315214454132</v>
+        <v>2.497863064446611</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815453</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
-        <v>3.008788008941528</v>
+        <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-5.118714548950505</v>
+        <v>-4.947375477925627</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9609457650475792</v>
+        <v>0.715090254871523</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.4931213882218007</v>
+        <v>-0.3315564072576568</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.712915176008448</v>
+        <v>2.495463026000928</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
-        <v>3.005312728149773</v>
+        <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-5.099676421243208</v>
+        <v>-4.92833735021833</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.965085735338743</v>
+        <v>0.719230225162687</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.5513049995529953</v>
+        <v>-0.3897400185888513</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.674529728417976</v>
+        <v>2.457077578410455</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131249</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
-        <v>3.182894597088454</v>
+        <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-5.130803052393826</v>
+        <v>-4.959463981368948</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.130216951817176</v>
+        <v>0.8843614416411201</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.5513049995529953</v>
+        <v>-0.3897400185888513</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.852111597356657</v>
+        <v>2.634659447349136</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
-        <v>3.183727926074587</v>
+        <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-5.144669813727744</v>
+        <v>-4.973330742702866</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.125503576269742</v>
+        <v>0.8796480660936865</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.5891629162868182</v>
+        <v>-0.4275979353226743</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.830230176302497</v>
+        <v>2.612778026294976</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789121</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
-        <v>3.189736456471513</v>
+        <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.164927112256702</v>
+        <v>-4.993588041231824</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.123409187255085</v>
+        <v>0.8775536770790293</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.5891629162868182</v>
+        <v>-0.4275979353226743</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.836238706699423</v>
+        <v>2.618786556691902</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
-        <v>3.268889104263535</v>
+        <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-5.0171841420217</v>
+        <v>-4.845845070996821</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.261659023141108</v>
+        <v>1.015803512965052</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.421355559051935</v>
+        <v>-0.2597905780877911</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.016075768832374</v>
+        <v>2.798623618824854</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918117</v>
+        <v>3.802245929181172</v>
       </c>
       <c r="C1967" t="n">
-        <v>3.271682725795016</v>
+        <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-5.119198824552921</v>
+        <v>-4.947859753528043</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.223646771660101</v>
+        <v>0.9777912614840447</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.421355559051935</v>
+        <v>-0.2597905780877911</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.018869390363855</v>
+        <v>2.801417240356335</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394729</v>
+        <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
-        <v>3.272345074186675</v>
+        <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-5.113046118500137</v>
+        <v>-4.941707047475258</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.226770202472873</v>
+        <v>0.9809146922968168</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.4152028529991507</v>
+        <v>-0.2536378720350068</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.023223362387184</v>
+        <v>2.805771212379664</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890609</v>
+        <v>3.798239794890612</v>
       </c>
       <c r="C1969" t="n">
-        <v>3.271425550926785</v>
+        <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-5.129855416650638</v>
+        <v>-4.95851634562576</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.219126959952782</v>
+        <v>0.9732714497767263</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.4320121511496524</v>
+        <v>-0.2704471701855085</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.012218260236994</v>
+        <v>2.794766110229473</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798424</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
-        <v>3.337761104723606</v>
+        <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-5.067557417874516</v>
+        <v>-4.896218346849638</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.310381713260052</v>
+        <v>1.064526203083996</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.4320121511496524</v>
+        <v>-0.2704471701855085</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.078553814033814</v>
+        <v>2.861101664026294</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992192</v>
+        <v>3.848729139992194</v>
       </c>
       <c r="C1971" t="n">
-        <v>3.046341977113004</v>
+        <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.865767220209358</v>
+        <v>-4.69442814918448</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.099678664715513</v>
+        <v>0.8538231545394572</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.233993958980498</v>
+        <v>-0.07242897801635406</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.905945601724705</v>
+        <v>2.688493451717184</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852421</v>
+        <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
-        <v>3.116632209435179</v>
+        <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.805876538566765</v>
+        <v>-4.634537467541887</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.193925169694726</v>
+        <v>0.9480696595186697</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.1741032773379045</v>
+        <v>-0.01253829637376058</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.012170243032437</v>
+        <v>2.794718093024916</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319546</v>
+        <v>3.819063300319548</v>
       </c>
       <c r="C1973" t="n">
-        <v>3.131259945551223</v>
+        <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.903617083191739</v>
+        <v>-4.732278012166861</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.16945668796078</v>
+        <v>0.9236011777847237</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.1899925554708847</v>
+        <v>-0.02842757450674077</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.017264412268692</v>
+        <v>2.799812262261171</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.831819032489384</v>
       </c>
       <c r="C1974" t="n">
-        <v>3.129795926375894</v>
+        <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-5.079954843314669</v>
+        <v>-4.908615772289791</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.097457564736279</v>
+        <v>0.8516020545602236</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.3663303155938141</v>
+        <v>-0.2047653346296702</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.909997737019606</v>
+        <v>2.692545587012085</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
-        <v>3.128287544415823</v>
+        <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-5.008408520537792</v>
+        <v>-4.837069449512914</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.124567711886959</v>
+        <v>0.878712201710903</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.3663303155938141</v>
+        <v>-0.2047653346296702</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.908489355059535</v>
+        <v>2.691037205052014</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024961</v>
+        <v>3.836023391024962</v>
       </c>
       <c r="C1976" t="n">
-        <v>3.128150411851259</v>
+        <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.964035388899223</v>
+        <v>-4.792696317874345</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.142179831977823</v>
+        <v>0.8963243218017667</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.3219571839552455</v>
+        <v>-0.1603922029911016</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.934976101478112</v>
+        <v>2.717523951470591</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863222</v>
+        <v>3.821591150863224</v>
       </c>
       <c r="C1977" t="n">
-        <v>3.128150411851259</v>
+        <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.956081418604451</v>
+        <v>-4.784742347579573</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.145361420095731</v>
+        <v>0.8995059099196756</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.3219571839552455</v>
+        <v>-0.1603922029911016</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.934976101478112</v>
+        <v>2.717523951470591</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947581</v>
+        <v>3.833040181947583</v>
       </c>
       <c r="C1978" t="n">
-        <v>3.134532168879064</v>
+        <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.908425688043395</v>
+        <v>-4.737086617018517</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.170805469347958</v>
+        <v>0.9249499591719026</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.2743014533941898</v>
+        <v>-0.1127364724300459</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.96995129684255</v>
+        <v>2.752499146835029</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326874</v>
+        <v>3.822707244326875</v>
       </c>
       <c r="C1979" t="n">
-        <v>3.139424542253789</v>
+        <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.780741378249099</v>
+        <v>-4.609402307224221</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.226771566640402</v>
+        <v>0.9809160564643458</v>
       </c>
       <c r="F1979" t="n">
-        <v>-0.1466171435998934</v>
+        <v>0.01494783736425054</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.051454256093853</v>
+        <v>2.834002106086332</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314549</v>
+        <v>3.828837911314551</v>
       </c>
       <c r="C1980" t="n">
-        <v>3.126179214729661</v>
+        <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.841407968651488</v>
+        <v>-4.67006889762661</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.189259602955318</v>
+        <v>0.9434040927792622</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.228315460318427</v>
+        <v>-0.06675047935428313</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.989189938538605</v>
+        <v>2.771737788531084</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690025</v>
+        <v>3.816866067690027</v>
       </c>
       <c r="C1981" t="n">
-        <v>3.130276917340289</v>
+        <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.79656956704309</v>
+        <v>-4.625230496018212</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.211292666209306</v>
+        <v>0.9654371560332502</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.2237720273735576</v>
+        <v>-0.06220704640941366</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.996013700916155</v>
+        <v>2.778561550908634</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674309</v>
+        <v>3.817961388674311</v>
       </c>
       <c r="C1982" t="n">
-        <v>3.134437856971367</v>
+        <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.897328202800088</v>
+        <v>-4.72598913177521</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.175150151537585</v>
+        <v>0.9292946413615291</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.312597596100563</v>
+        <v>-0.1510326151364191</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.94687929931103</v>
+        <v>2.729427149303509</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163218</v>
+        <v>3.82671377916322</v>
       </c>
       <c r="C1983" t="n">
-        <v>3.140317459499204</v>
+        <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.853125365714187</v>
+        <v>-4.681786294689309</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.198710888899782</v>
+        <v>0.9528553787237264</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.2683947590146625</v>
+        <v>-0.1068297780505186</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.979280604090407</v>
+        <v>2.761828454082886</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022903</v>
+        <v>3.838228663022905</v>
       </c>
       <c r="C1984" t="n">
-        <v>3.138727459968452</v>
+        <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.89010439337763</v>
+        <v>-4.718765322352752</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.182329278303653</v>
+        <v>0.9364737681275968</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.231420857223332</v>
+        <v>-0.0698558762591881</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.999874945634453</v>
+        <v>2.782422795626932</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042137</v>
+        <v>3.863924114042139</v>
       </c>
       <c r="C1985" t="n">
-        <v>3.189975225151492</v>
+        <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.910162472242471</v>
+        <v>-4.738823401217592</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.225553811940756</v>
+        <v>0.9796983017647003</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.231420857223332</v>
+        <v>-0.0698558762591881</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.051122710817493</v>
+        <v>2.833670560809972</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86536771507828</v>
+        <v>3.865367715078282</v>
       </c>
       <c r="C1986" t="n">
-        <v>3.188415929745745</v>
+        <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.87023179906458</v>
+        <v>-4.698892728039702</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.239966785806165</v>
+        <v>0.9941112756301096</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.1914901840454417</v>
+        <v>-0.02992520308129776</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.07352181931848</v>
+        <v>2.856069669310959</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232397</v>
+        <v>3.864518876232399</v>
       </c>
       <c r="C1987" t="n">
-        <v>3.183364157984015</v>
+        <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.819199706342053</v>
+        <v>-4.647860635317175</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.255327851133446</v>
+        <v>1.00947234095739</v>
       </c>
       <c r="F1987" t="n">
-        <v>-0.1404580913229137</v>
+        <v>0.0211068896412302</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.099089303190267</v>
+        <v>2.881637153182746</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162113</v>
+        <v>3.842576394162115</v>
       </c>
       <c r="C1988" t="n">
-        <v>3.20055156207672</v>
+        <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.753975525214847</v>
+        <v>-4.632900557375272</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.298604927677034</v>
+        <v>1.032643776226856</v>
       </c>
       <c r="F1988" t="n">
-        <v>-0.07523391019570808</v>
+        <v>0.03606696758313188</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.155411215959295</v>
+        <v>2.907800604040592</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639818</v>
+        <v>3.840090220639819</v>
       </c>
       <c r="C1989" t="n">
-        <v>3.196512534376</v>
+        <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.804469815571903</v>
+        <v>-4.683394847732329</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.274368183833491</v>
+        <v>1.008407032383314</v>
       </c>
       <c r="F1989" t="n">
-        <v>-0.1202546473217823</v>
+        <v>-0.008953769542942358</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.124359745982931</v>
+        <v>2.876749134064228</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.84519884274992</v>
+        <v>3.845198842749921</v>
       </c>
       <c r="C1990" t="n">
-        <v>3.19776932670724</v>
+        <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.824581471606612</v>
+        <v>-4.703506503767037</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.267580313750849</v>
+        <v>1.001619162300671</v>
       </c>
       <c r="F1990" t="n">
-        <v>-0.1092273023243631</v>
+        <v>0.002073575454476839</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.132232945312623</v>
+        <v>2.88462233339392</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828690479393545</v>
+        <v>3.828690479393547</v>
       </c>
       <c r="C1991" t="n">
-        <v>3.358327097728451</v>
+        <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.922262050879258</v>
+        <v>-4.801187083039682</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.389065853063001</v>
+        <v>1.123104701612824</v>
       </c>
       <c r="F1991" t="n">
-        <v>-0.2199304976645519</v>
+        <v>-0.108629619885712</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.226368799129721</v>
+        <v>2.978758187211017</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714883</v>
+        <v>3.813251854714885</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.478440006946268</v>
+        <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.898470482273115</v>
+        <v>-4.77739551443354</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.518695389723275</v>
+        <v>1.252734238273098</v>
       </c>
       <c r="F1992" t="n">
-        <v>-0.1961389290584096</v>
+        <v>-0.08483805127956967</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.360756649511223</v>
+        <v>3.11314603759252</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.81425976175601</v>
+        <v>3.814259761756013</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.470147982960127</v>
+        <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.935224900834838</v>
+        <v>-4.814149932995262</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.495701598312445</v>
+        <v>1.229740446862268</v>
       </c>
       <c r="F1993" t="n">
-        <v>-0.1961389290584096</v>
+        <v>-0.08483805127956967</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.352464625525082</v>
+        <v>3.104854013606379</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803426852654185</v>
+        <v>3.803426852654187</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.468341178543907</v>
+        <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.93089059777779</v>
+        <v>-4.809815629938214</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.495628515119044</v>
+        <v>1.229667363668867</v>
       </c>
       <c r="F1994" t="n">
-        <v>-0.04448882573920571</v>
+        <v>0.06681205203963425</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.441647883100384</v>
+        <v>3.19403727118168</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796293177717115</v>
+        <v>3.796293177717118</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.485895584270698</v>
+        <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.921998136384507</v>
+        <v>-4.800923168544931</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.516739905403148</v>
+        <v>1.250778753952971</v>
       </c>
       <c r="F1995" t="n">
-        <v>-0.04448882573920571</v>
+        <v>0.06681205203963425</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.459202288827175</v>
+        <v>3.211591676908472</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794453975702623</v>
+        <v>3.794453975702626</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.477750631675282</v>
+        <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-5.090474253354384</v>
+        <v>-4.969399285514808</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.441204506019781</v>
+        <v>1.175243354569604</v>
       </c>
       <c r="F1996" t="n">
-        <v>-0.07243666145578648</v>
+        <v>0.03886421632305348</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.434288634801811</v>
+        <v>3.186678022883108</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795603100539966</v>
+        <v>3.795603100539969</v>
       </c>
       <c r="C1997" t="n">
-        <v>3.548163293132126</v>
+        <v>3.233772154546119</v>
       </c>
       <c r="D1997" t="n">
-        <v>-4.392674724492801</v>
+        <v>-4.271599756653226</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.790736979021258</v>
+        <v>1.524775827571081</v>
       </c>
       <c r="F1997" t="n">
-        <v>-0.1427847208261972</v>
+        <v>-0.03148384304735724</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.462492460636408</v>
+        <v>3.214881848717705</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784700379389895</v>
+        <v>3.784700379389899</v>
       </c>
       <c r="C1998" t="n">
-        <v>3.53882731562903</v>
+        <v>3.224436177043023</v>
       </c>
       <c r="D1998" t="n">
-        <v>-4.369953620809649</v>
+        <v>-4.248878652970073</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.790489442991424</v>
+        <v>1.524528291541247</v>
       </c>
       <c r="F1998" t="n">
-        <v>-0.1427847208261972</v>
+        <v>-0.03148384304735724</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.453156483133312</v>
+        <v>3.205545871214609</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.439368929008216</v>
+        <v>3.780657783970052</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.213559327802014</v>
+        <v>3.204252428470376</v>
       </c>
       <c r="D1999" t="n">
-        <v>-4.369953620809649</v>
+        <v>-4.248878652970073</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.790489442991424</v>
+        <v>1.524528291541247</v>
       </c>
       <c r="F1999" t="n">
-        <v>-0.1427847208261972</v>
+        <v>-0.03148384304735724</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.206623124788382</v>
+        <v>3.197316225456743</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240618.xlsx
+++ b/tame_output/ON/bt/strategyON_20240618.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.4%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>52.4%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>69.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.5%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>12.9%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.5%</t>
+          <t>-76.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.5%</t>
+          <t>109.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.3%</t>
+          <t>124.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.1%</t>
+          <t>94.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.2%</t>
+          <t>-72.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>454.1%</t>
+          <t>454.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-586.5%</t>
+          <t>-590.3%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-9.4%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>182.4%</t>
+          <t>242.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-223.8%</t>
+          <t>-223.2%</t>
         </is>
       </c>
     </row>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>198.4%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-166.8%</t>
+          <t>-189.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-227.1%</t>
+          <t>-226.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-126.3%</t>
+          <t>-123.2%</t>
         </is>
       </c>
     </row>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330521</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.956010906065385</v>
+        <v>-6.969762319567352</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3278651656752309</v>
+        <v>0.3223646002744438</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.548175094357108</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.372402780352382</v>
+        <v>-7.38615419385435</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1593024665693097</v>
+        <v>0.1538019011685225</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.548175094357108</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.643168869445027</v>
+        <v>-7.656920282946995</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.06125472160093048</v>
+        <v>0.05575415620014335</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.548175094357108</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.989043691429837</v>
+        <v>-8.002795104931804</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.08099564204729814</v>
+        <v>-0.08649620744808528</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.548175094357108</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.152623569614221</v>
+        <v>-8.166374983116189</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.148022673266051</v>
+        <v>-0.1535232386668381</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.548175094357108</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.449284911424419</v>
+        <v>-8.463036324926387</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2629082340609221</v>
+        <v>-0.2684087994617093</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.616918230090987</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.636004619733722</v>
+        <v>-8.64975603323569</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3416224219190465</v>
+        <v>-0.3471229873198336</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.616918230090987</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.019006008476353</v>
+        <v>-9.032757421978321</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4949250787376829</v>
+        <v>-0.50042564413847</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.616918230090987</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.200875799461388</v>
+        <v>-9.214627212963356</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5651014791602664</v>
+        <v>-0.5706020445610536</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.798788021076022</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.560406121965389</v>
+        <v>-9.574157535467357</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.7035633048638168</v>
+        <v>-0.7090638702646039</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.798788021076022</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.610755185419611</v>
+        <v>-9.624506598921579</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.7157869102883283</v>
+        <v>-0.7212874756891154</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.849137084530244</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.708374462841007</v>
+        <v>-9.722125876342975</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7517928706351178</v>
+        <v>-0.7572934360359049</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.946756361951641</v>
@@ -44722,10 +44722,10 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.85590055084665</v>
+        <v>-9.869651964348618</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8079097495158027</v>
+        <v>-0.8134103149165899</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.094282449957284</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.5027903991417</v>
+        <v>3.502790399141699</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.06015872617651</v>
+        <v>-10.07391013967848</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.8840998225291061</v>
+        <v>-0.8896003879298933</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.221921394571273</v>
@@ -44768,10 +44768,10 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.13449170243668</v>
+        <v>-10.14824311593865</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.9093504585487353</v>
+        <v>-0.9148510239495224</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.366620918505946</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440633</v>
+        <v>3.499971739440632</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.06102187076923</v>
+        <v>-10.0747732842712</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.8645908243883351</v>
+        <v>-0.8700913897891223</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.293151086838497</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.23614628815577</v>
+        <v>-10.24989770165774</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9200853705954355</v>
+        <v>-0.9255859359962226</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.468275504225041</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410271</v>
+        <v>3.48587859441027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.47059838217026</v>
+        <v>-10.48434979567223</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.021085373102828</v>
+        <v>-1.026585938503615</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.468275504225041</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.57497311319671</v>
+        <v>-10.58872452669868</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.069507456287382</v>
+        <v>-1.075008021688169</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.572650235251487</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.62775926879704</v>
+        <v>-10.641510682299</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.089506128688956</v>
+        <v>-1.095006694089744</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.668325721833884</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297398</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.75379606216532</v>
+        <v>-10.76754747566729</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.137227117407158</v>
+        <v>-1.142727682807945</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.643074099024141</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.70178054819651</v>
+        <v>-10.71553196169848</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.112430576133232</v>
+        <v>-1.117931141534019</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.643074099024141</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.84345238992063</v>
+        <v>-10.8572038034226</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.170574539721621</v>
+        <v>-1.176075105122409</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.643074099024141</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940719</v>
+        <v>3.691571733940718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.7938615454958</v>
+        <v>-10.80761295899777</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.135684791786816</v>
+        <v>-1.141185357187603</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.593483254599307</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.67684154977058</v>
+        <v>3.676841549770579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.78105415249102</v>
+        <v>-10.79480556599299</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.143612968231589</v>
+        <v>-1.149113533632376</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.642339029608209</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.55520899977161</v>
+        <v>-10.56896041327358</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.043695834107615</v>
+        <v>-1.049196399508402</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.600412354021045</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812102</v>
+        <v>3.684843823812101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.43063034343402</v>
+        <v>-10.44438175693599</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9927252270165199</v>
+        <v>-0.998225792417307</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.600412354021045</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646216</v>
+        <v>3.710935533646215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.48352563147831</v>
+        <v>-10.49727704498027</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.011249568072127</v>
+        <v>-1.016750133472914</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.595457007932599</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611568</v>
+        <v>3.768951674611567</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.41139245619043</v>
+        <v>-10.42514386969239</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9766625937183377</v>
+        <v>-0.9821631591191249</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.595457007932599</v>
@@ -45113,10 +45113,10 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.34002606358078</v>
+        <v>-10.35377747708275</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9578532990683435</v>
+        <v>-0.9633538644691306</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.524090615322951</v>
@@ -45136,10 +45136,10 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.24656702959555</v>
+        <v>-10.26031844309752</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.9303531667871616</v>
+        <v>-0.9358537321879488</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.524090615322951</v>
@@ -45159,10 +45159,10 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.979325228727156</v>
+        <v>-9.993076642229124</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.8252910069391763</v>
+        <v>-0.8307915723399635</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.524090615322951</v>
@@ -45182,10 +45182,10 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.881418190050665</v>
+        <v>-9.895169603552633</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7864285064420407</v>
+        <v>-0.7919290718428278</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.456104865462394</v>
@@ -45199,16 +45199,16 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097245</v>
+        <v>3.800829354097244</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.857464649074707</v>
+        <v>-9.871216062576675</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7761785839061641</v>
+        <v>-0.7816791493069513</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.432151324486437</v>
@@ -45222,16 +45222,16 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017773</v>
+        <v>3.789311112017772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.59340471075191</v>
+        <v>-9.607156124253878</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6838149247387975</v>
+        <v>-0.6893154901395846</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.168091386163641</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839726</v>
+        <v>3.833252747839724</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.886325087247073</v>
+        <v>-8.900076500749041</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.4037701089971635</v>
+        <v>-0.4092706743979506</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.168091386163641</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388729</v>
+        <v>3.839374447388727</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.846140788880883</v>
+        <v>-8.85989220238285</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3873527657628459</v>
+        <v>-0.3928533311636331</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.12790708779745</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626475</v>
+        <v>3.856161751626473</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.682740917941519</v>
+        <v>-8.696492331443487</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.3226259961663436</v>
+        <v>-0.3281265615671307</v>
       </c>
       <c r="F1902" t="n">
         <v>-1.964507216858087</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291812</v>
+        <v>3.78733042929181</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.44925969571192</v>
+        <v>-8.463011109213888</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.2213090784366516</v>
+        <v>-0.2268096438374387</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.731025994628489</v>
@@ -45337,16 +45337,16 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785788</v>
+        <v>3.801637122785786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.299593304704405</v>
+        <v>-8.313344718206373</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.1643347323466049</v>
+        <v>-0.169835297747392</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.638122503385953</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390428</v>
+        <v>3.763182248390426</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.167317831073518</v>
+        <v>-8.181069244575486</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.1160570561472229</v>
+        <v>-0.1215576215480101</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.505847029755066</v>
@@ -45383,16 +45383,16 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105952</v>
+        <v>3.784718794105951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.976718156400366</v>
+        <v>-7.990469569902333</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.03700212559032501</v>
+        <v>-0.04250269099111215</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.315247355081913</v>
@@ -45406,16 +45406,16 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960987</v>
+        <v>3.753882571960985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.727718357716785</v>
+        <v>-7.741469771218752</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.07550413510676579</v>
+        <v>0.07000356970597865</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.315247355081913</v>
@@ -45429,16 +45429,16 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607646</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.833308347489889</v>
+        <v>-7.847059760991857</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.09470779040169441</v>
+        <v>-0.1002083558024816</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.420837344855018</v>
@@ -45452,16 +45452,16 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987903</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.852043249608486</v>
+        <v>-7.865794663110454</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.05365740937204677</v>
+        <v>-0.05915797477283391</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.426433354515149</v>
@@ -45475,16 +45475,16 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710812</v>
+        <v>3.76033368671081</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.704103208200887</v>
+        <v>-7.717854621702855</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1143603154971746</v>
+        <v>-0.1198608808979618</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.406112438606591</v>
@@ -45498,16 +45498,16 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409205</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.651133685946898</v>
+        <v>-7.664885099448866</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.1018864928490575</v>
+        <v>-0.1073870582498446</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.353142916352602</v>
@@ -45521,16 +45521,16 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098109</v>
+        <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.607585279176208</v>
+        <v>-7.621336692678176</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.09142774223587447</v>
+        <v>-0.0969283076366616</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.353142916352602</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.78292253349342</v>
+        <v>3.782922533493418</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.36543688572235</v>
+        <v>-7.379188299224317</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.01989396952681188</v>
+        <v>0.01439340412602474</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.353142916352602</v>
@@ -45567,16 +45567,16 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722817</v>
+        <v>3.828551486722815</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.257177748599828</v>
+        <v>-7.270929162101796</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.05772974483501558</v>
+        <v>0.05222917943422845</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.353142916352602</v>
@@ -45590,16 +45590,16 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792045</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.133886613782697</v>
+        <v>-7.147638027284665</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1045442927724447</v>
+        <v>0.09904372737165756</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.229851781535472</v>
@@ -45613,16 +45613,16 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919906</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.112737414879254</v>
+        <v>-7.126488828381222</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1207049505711471</v>
+        <v>0.1152043851703599</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.208702582632029</v>
@@ -45636,16 +45636,16 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318093</v>
+        <v>3.748328408318091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.868971972895809</v>
+        <v>-6.882723386397777</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2139918357115755</v>
+        <v>0.2084912703107884</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.208702582632029</v>
@@ -45659,16 +45659,16 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057526</v>
+        <v>3.824311233057524</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.767209152618515</v>
+        <v>-6.780960566120482</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2568212777425094</v>
+        <v>0.2513207123417223</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.1954835142396</v>
@@ -45682,16 +45682,16 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279186</v>
+        <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.51735875866944</v>
+        <v>-6.531110172171408</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3495035103058415</v>
+        <v>0.3440029449050543</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.1954835142396</v>
@@ -45705,16 +45705,16 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011499</v>
+        <v>3.835957987011497</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.341466666202008</v>
+        <v>-6.355218079703976</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4234594708134631</v>
+        <v>0.417958905412676</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.1954835142396</v>
@@ -45728,16 +45728,16 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392987</v>
+        <v>3.780933911392985</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.170020203179544</v>
+        <v>-6.183771616681512</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5053655620770021</v>
+        <v>0.499864996676215</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.024037051217137</v>
@@ -45751,16 +45751,16 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632782</v>
+        <v>3.77376522263278</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.095730637441205</v>
+        <v>-6.109482050943173</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5341018659886347</v>
+        <v>0.5286013005878476</v>
       </c>
       <c r="F1922" t="n">
         <v>-0.9497474854787973</v>
@@ -45774,16 +45774,16 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883072</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.032094895207271</v>
+        <v>-6.045846308709239</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5642509639365261</v>
+        <v>0.5587503985357389</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.8861117432448627</v>
@@ -45797,16 +45797,16 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074783</v>
+        <v>3.798814771074781</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.920668135881351</v>
+        <v>-5.934419549383319</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5900159264506897</v>
+        <v>0.5845153610499025</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.8861117432448627</v>
@@ -45820,16 +45820,16 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242294</v>
+        <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.68023763907649</v>
+        <v>-5.693989052578458</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.687931201797511</v>
+        <v>0.6824306363967239</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.6456812464400025</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367685</v>
+        <v>3.821593509367684</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.607995070905296</v>
+        <v>-5.621746484407264</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7207575429008091</v>
+        <v>0.7152569775000219</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.6456812464400025</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879967</v>
+        <v>3.822326997879966</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.554996748623908</v>
+        <v>-5.568748162125876</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7426354557307042</v>
+        <v>0.7371348903299171</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.5903449874380636</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502339</v>
+        <v>3.848616626502338</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.446191863144181</v>
+        <v>-5.459943276646149</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7831554811425887</v>
+        <v>0.7776549157418016</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.5903449874380636</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675939</v>
+        <v>3.818668951675938</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.22617106510717</v>
+        <v>-5.239922478609138</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8727428373680071</v>
+        <v>0.8672422719672199</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.4491251423700834</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.84327452753995</v>
+        <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.093303376043893</v>
+        <v>-5.10705478954586</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9417840957951413</v>
+        <v>0.9362835303943542</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.4491251423700834</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496259</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.973130292679394</v>
+        <v>-4.986881706181362</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9909991735812427</v>
+        <v>0.9854986081804555</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.3289520590055844</v>
@@ -45987,10 +45987,10 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.828458147579656</v>
+        <v>-4.842209561081624</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.058956134182578</v>
+        <v>1.053455568781791</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.184279913905847</v>
@@ -46010,10 +46010,10 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.888332974937349</v>
+        <v>-4.902084388439317</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.021043694640926</v>
+        <v>1.015543129240139</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.2441547412635391</v>
@@ -46033,10 +46033,10 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.80153347715834</v>
+        <v>-4.815284890660308</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.078163987075096</v>
+        <v>1.072663421674309</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.2441547412635391</v>
@@ -46056,10 +46056,10 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.804003183620146</v>
+        <v>-4.817754597122114</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.077248505863786</v>
+        <v>1.071747940462999</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.2466244477253453</v>
@@ -46079,10 +46079,10 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.872373369944157</v>
+        <v>-4.886124783446125</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.060907353808884</v>
+        <v>1.055406788408096</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.2373487486891304</v>
@@ -46102,10 +46102,10 @@
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.980911550860291</v>
+        <v>-4.994662964362258</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.007928790074321</v>
+        <v>1.002428224673534</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.2373487486891304</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417702</v>
+        <v>3.710906731417703</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.011904710188996</v>
+        <v>-5.025656123690964</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8202410913832261</v>
+        <v>0.814740525982439</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.2373487486891304</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205899</v>
+        <v>3.746042526205901</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.836430450396527</v>
+        <v>-4.850181863898495</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.8949980272920013</v>
+        <v>0.8894974618912141</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.2373487486891304</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225443</v>
+        <v>3.765024323225445</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.947366703037776</v>
+        <v>-4.961118116539744</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8263655549967088</v>
+        <v>0.8208649895959217</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.2373487486891304</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111291</v>
+        <v>3.773210297111293</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.955648777182835</v>
+        <v>-4.969400190684802</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.826184110558591</v>
+        <v>0.8206835451578038</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.2456308228341887</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264161</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.895796157979111</v>
+        <v>-4.909547571481079</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8602975446722125</v>
+        <v>0.8547969792714254</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.2456308228341887</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742297</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.809552694952734</v>
+        <v>-4.823304108454701</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8897412004566241</v>
+        <v>0.8842406350558369</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.2456308228341887</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.854859514351713</v>
+        <v>-4.868610927853681</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8633942481415575</v>
+        <v>0.8578936827407704</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.2864409858434195</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803189</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.883892619054015</v>
+        <v>-4.897644032555982</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8523328792937388</v>
+        <v>0.8468323138929517</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.2864409858434195</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809496</v>
+        <v>3.733390600809498</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.791082137603155</v>
+        <v>-4.804833551105123</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8187297637654483</v>
+        <v>0.8132291983646611</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.1936305043925602</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560424</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.835471606932582</v>
+        <v>-4.84922302043455</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.802847451958278</v>
+        <v>0.7973468865574909</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.2380199737219879</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472736</v>
+        <v>3.721077195472738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.722800388696332</v>
+        <v>-4.7365518021983</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8429916477645012</v>
+        <v>0.8374910823637141</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.1253487554857377</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.610423387513659</v>
+        <v>-4.624174801015627</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.8934337440682376</v>
+        <v>0.8879331786674505</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.1253487554857377</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.638203785415012</v>
+        <v>-4.65195519891698</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8938187866762355</v>
+        <v>0.8883182212754483</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.1531291533870907</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705323</v>
+        <v>3.643069621705325</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.721205066440291</v>
+        <v>-4.734956479942259</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6989739942667772</v>
+        <v>0.6934734288659901</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.1717000379142645</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729268</v>
+        <v>3.68271631072927</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.829819144883622</v>
+        <v>-4.84357055838559</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7756780236086505</v>
+        <v>0.7701774582078633</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.1717000379142645</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190767</v>
+        <v>3.733012441190769</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.916417727864725</v>
+        <v>-4.930169141366693</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7555516165185323</v>
+        <v>0.7500510511177452</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.1717000379142645</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913424</v>
+        <v>3.741174069913426</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.878034065306574</v>
+        <v>-4.891785478808542</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.7683245228841613</v>
+        <v>0.7628239574833742</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.1333163753561133</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532485</v>
+        <v>3.751147197532487</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.700917735271408</v>
+        <v>-4.714669148773376</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8359000837435298</v>
+        <v>0.8303995183427426</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.1333163753561133</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793903</v>
+        <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.746009980104954</v>
+        <v>-4.759761393606921</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8185465775720244</v>
+        <v>0.8130460121712373</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.1952124185255031</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011236</v>
+        <v>3.750729377011238</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.566634558866186</v>
+        <v>-4.580385972368154</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.8840837213739459</v>
+        <v>0.8785831559731587</v>
       </c>
       <c r="F1957" t="n">
         <v>-0.03843566035478441</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71699171898223</v>
+        <v>3.716991718982232</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.611648772386792</v>
+        <v>-4.625400185888759</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8468854912972934</v>
+        <v>0.8413849258965063</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.06878455566938901</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509537</v>
+        <v>3.737026608509539</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.878653282659227</v>
+        <v>-4.892404696161194</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.7457752495272651</v>
+        <v>0.740274684126478</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.2631475937123376</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476081</v>
+        <v>3.702309454760811</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.979851064096399</v>
+        <v>-4.993602477598367</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7045000588488974</v>
+        <v>0.6989994934481103</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.3315564072576568</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815456</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.947375477925627</v>
+        <v>-4.961126891427595</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.715090254871523</v>
+        <v>0.7095896894707359</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.3315564072576568</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378101</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.92833735021833</v>
+        <v>-4.942088763720298</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.719230225162687</v>
+        <v>0.7137296597618998</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.3897400185888513</v>
@@ -46700,10 +46700,10 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.959463981368948</v>
+        <v>-4.973215394870916</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.8843614416411201</v>
+        <v>0.8788608762403329</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.3897400185888513</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067866</v>
+        <v>3.722447362067867</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.973330742702866</v>
+        <v>-4.987082156204834</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.8796480660936865</v>
+        <v>0.8741475006928994</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.4275979353226743</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789124</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.993588041231824</v>
+        <v>-5.007339454733792</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.8775536770790293</v>
+        <v>0.8720531116782422</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.4275979353226743</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519909</v>
+        <v>3.781501250519911</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.845845070996821</v>
+        <v>-4.859596484498789</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.015803512965052</v>
+        <v>1.010302947564265</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.2597905780877911</v>
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181172</v>
+        <v>3.802245929181174</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.957291587209009</v>
+        <v>2.964823815241827</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.947859753528043</v>
+        <v>-4.961611167030011</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9777912614840447</v>
+        <v>0.9798229241160754</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.2597905780877911</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.801417240356335</v>
+        <v>2.808949468389152</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394731</v>
+        <v>3.805608985394732</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.957953935600667</v>
+        <v>2.965486163633485</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.941707047475258</v>
+        <v>-4.955458460977226</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9809146922968168</v>
+        <v>0.9829463549288475</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.2536378720350068</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.805771212379664</v>
+        <v>2.813303440412481</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890612</v>
+        <v>3.798239794890613</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.957034412340778</v>
+        <v>2.964566640373596</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.95851634562576</v>
+        <v>-4.972267759127728</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9732714497767263</v>
+        <v>0.975303112408757</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.2704471701855085</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.794766110229473</v>
+        <v>2.802298338262291</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
-        <v>3.023369966137599</v>
+        <v>3.030902194170416</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.896218346849638</v>
+        <v>-4.909969760351606</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.064526203083996</v>
+        <v>1.066557865716027</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.2704471701855085</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.861101664026294</v>
+        <v>2.868633892059111</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.848729139992194</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.731950838526997</v>
+        <v>2.739483066559814</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.69442814918448</v>
+        <v>-4.708179562686448</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8538231545394572</v>
+        <v>0.8558548171714879</v>
       </c>
       <c r="F1971" t="n">
         <v>-0.07242897801635406</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.688493451717184</v>
+        <v>2.696025679750002</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.802241070849172</v>
+        <v>2.80977329888199</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.634537467541887</v>
+        <v>-4.648288881043855</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9480696595186697</v>
+        <v>0.9501013221507004</v>
       </c>
       <c r="F1972" t="n">
         <v>-0.01253829637376058</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.794718093024916</v>
+        <v>2.802250321057734</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319548</v>
+        <v>3.819063300319549</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.816868806965215</v>
+        <v>2.824401034998033</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.732278012166861</v>
+        <v>-4.746029425668829</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9236011777847237</v>
+        <v>0.9256328404167544</v>
       </c>
       <c r="F1973" t="n">
         <v>-0.02842757450674077</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.799812262261171</v>
+        <v>2.807344490293989</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489384</v>
+        <v>3.831819032489386</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.815404787789887</v>
+        <v>2.822937015822705</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.908615772289791</v>
+        <v>-4.922367185791758</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8516020545602236</v>
+        <v>0.8536337171922543</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.2047653346296702</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.692545587012085</v>
+        <v>2.700077815044903</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397795</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.813896405829816</v>
+        <v>2.821428633862634</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.837069449512914</v>
+        <v>-4.850820863014881</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.878712201710903</v>
+        <v>0.8807438643429337</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.2047653346296702</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.691037205052014</v>
+        <v>2.698569433084832</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024962</v>
+        <v>3.836023391024963</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.813759273265252</v>
+        <v>2.82129150129807</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.792696317874345</v>
+        <v>-4.806447731376313</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8963243218017667</v>
+        <v>0.8983559844337974</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.1603922029911016</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.717523951470591</v>
+        <v>2.725056179503409</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863224</v>
+        <v>3.821591150863225</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.813759273265252</v>
+        <v>2.82129150129807</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.784742347579573</v>
+        <v>-4.798493761081541</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.8995059099196756</v>
+        <v>0.9015375725517063</v>
       </c>
       <c r="F1977" t="n">
         <v>-0.1603922029911016</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.717523951470591</v>
+        <v>2.725056179503409</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947583</v>
+        <v>3.833040181947584</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.820141030293057</v>
+        <v>2.827673258325874</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.737086617018517</v>
+        <v>-4.750838030520485</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9249499591719026</v>
+        <v>0.9269816218039333</v>
       </c>
       <c r="F1978" t="n">
         <v>-0.1127364724300459</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.752499146835029</v>
+        <v>2.760031374867847</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326875</v>
+        <v>3.822707244326876</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.825033403667781</v>
+        <v>2.832565631700599</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.609402307224221</v>
+        <v>-4.623153720726188</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.9809160564643458</v>
+        <v>0.9829477190963765</v>
       </c>
       <c r="F1979" t="n">
         <v>0.01494783736425054</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.834002106086332</v>
+        <v>2.84153433411915</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314551</v>
+        <v>3.828837911314552</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.811788076143654</v>
+        <v>2.819320304176471</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.67006889762661</v>
+        <v>-4.683820311128578</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.9434040927792622</v>
+        <v>0.9454357554112929</v>
       </c>
       <c r="F1980" t="n">
         <v>-0.06675047935428313</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.771737788531084</v>
+        <v>2.779270016563902</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690027</v>
+        <v>3.816866067690028</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.815885778754282</v>
+        <v>2.8234180067871</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.625230496018212</v>
+        <v>-4.638981909520179</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.9654371560332502</v>
+        <v>0.9674688186652809</v>
       </c>
       <c r="F1981" t="n">
         <v>-0.06220704640941366</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.778561550908634</v>
+        <v>2.786093778941452</v>
       </c>
     </row>
     <row r="1982">
@@ -47134,19 +47134,19 @@
         <v>3.817961388674311</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.82004671838536</v>
+        <v>2.827578946418178</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.72598913177521</v>
+        <v>-4.739740545277177</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.9292946413615291</v>
+        <v>0.9313263039935598</v>
       </c>
       <c r="F1982" t="n">
         <v>-0.1510326151364191</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.729427149303509</v>
+        <v>2.736959377336327</v>
       </c>
     </row>
     <row r="1983">
@@ -47157,19 +47157,19 @@
         <v>3.82671377916322</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.825926320913197</v>
+        <v>2.833458548946015</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.681786294689309</v>
+        <v>-4.695537708191277</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.9528553787237264</v>
+        <v>0.9548870413557571</v>
       </c>
       <c r="F1983" t="n">
         <v>-0.1068297780505186</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.761828454082886</v>
+        <v>2.769360682115704</v>
       </c>
     </row>
     <row r="1984">
@@ -47180,19 +47180,19 @@
         <v>3.838228663022905</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.824336321382445</v>
+        <v>2.831868549415263</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.718765322352752</v>
+        <v>-4.73251673585472</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.9364737681275968</v>
+        <v>0.9385054307596274</v>
       </c>
       <c r="F1984" t="n">
         <v>-0.0698558762591881</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.782422795626932</v>
+        <v>2.78995502365975</v>
       </c>
     </row>
     <row r="1985">
@@ -47203,19 +47203,19 @@
         <v>3.863924114042139</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.875584086565484</v>
+        <v>2.883116314598302</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.738823401217592</v>
+        <v>-4.75257481471956</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.9796983017647003</v>
+        <v>0.981729964396731</v>
       </c>
       <c r="F1985" t="n">
         <v>-0.0698558762591881</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.833670560809972</v>
+        <v>2.84120278884279</v>
       </c>
     </row>
     <row r="1986">
@@ -47226,19 +47226,19 @@
         <v>3.865367715078282</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.874024791159738</v>
+        <v>2.881557019192555</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.698892728039702</v>
+        <v>-4.71264414154167</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.9941112756301096</v>
+        <v>0.9961429382621403</v>
       </c>
       <c r="F1986" t="n">
         <v>-0.02992520308129776</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.856069669310959</v>
+        <v>2.863601897343777</v>
       </c>
     </row>
     <row r="1987">
@@ -47249,19 +47249,19 @@
         <v>3.864518876232399</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.868973019398008</v>
+        <v>2.876505247430825</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.647860635317175</v>
+        <v>-4.661612048819142</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.00947234095739</v>
+        <v>1.011504003589421</v>
       </c>
       <c r="F1987" t="n">
         <v>0.0211068896412302</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.881637153182746</v>
+        <v>2.889169381215564</v>
       </c>
     </row>
     <row r="1988">
@@ -47272,19 +47272,19 @@
         <v>3.842576394162115</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.886160423490713</v>
+        <v>2.89369265152353</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.632900557375272</v>
+        <v>-4.596387867691937</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.032643776226856</v>
+        <v>1.054781080133008</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.03606696758313188</v>
+        <v>0.08633107076843582</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.907800604040592</v>
+        <v>2.945491293984592</v>
       </c>
     </row>
     <row r="1989">
@@ -47295,19 +47295,19 @@
         <v>3.840090220639819</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.882121395789993</v>
+        <v>2.889653623822811</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.683394847732329</v>
+        <v>-4.646882158048993</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.008407032383314</v>
+        <v>1.030544336289466</v>
       </c>
       <c r="F1989" t="n">
-        <v>-0.008953769542942358</v>
+        <v>0.04131033364236159</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.876749134064228</v>
+        <v>2.914439824008228</v>
       </c>
     </row>
     <row r="1990">
@@ -47318,19 +47318,19 @@
         <v>3.845198842749921</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.883378188121233</v>
+        <v>2.890910416154051</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.703506503767037</v>
+        <v>-4.666993814083702</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.001619162300671</v>
+        <v>1.023756466206823</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.002073575454476839</v>
+        <v>0.05233767863978078</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.88462233339392</v>
+        <v>2.92231302333792</v>
       </c>
     </row>
     <row r="1991">
@@ -47341,19 +47341,19 @@
         <v>3.828690479393547</v>
       </c>
       <c r="C1991" t="n">
-        <v>3.043935959142444</v>
+        <v>3.051468187175262</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.801187083039682</v>
+        <v>-4.764674393356348</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.123104701612824</v>
+        <v>1.145242005518975</v>
       </c>
       <c r="F1991" t="n">
-        <v>-0.108629619885712</v>
+        <v>-0.05836551670040802</v>
       </c>
       <c r="G1991" t="n">
-        <v>2.978758187211017</v>
+        <v>3.016448877155017</v>
       </c>
     </row>
     <row r="1992">
@@ -47364,19 +47364,19 @@
         <v>3.813251854714885</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.164048868360261</v>
+        <v>3.171581096393079</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.77739551443354</v>
+        <v>-4.740882824750205</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.252734238273098</v>
+        <v>1.27487154217925</v>
       </c>
       <c r="F1992" t="n">
-        <v>-0.08483805127956967</v>
+        <v>-0.03457394809426573</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.11314603759252</v>
+        <v>3.15083672753652</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814259761756013</v>
+        <v>3.814259761756012</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.15575684437412</v>
+        <v>3.163289072406938</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.814149932995262</v>
+        <v>-4.777637243311927</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.229740446862268</v>
+        <v>1.25187775076842</v>
       </c>
       <c r="F1993" t="n">
-        <v>-0.08483805127956967</v>
+        <v>-0.03457394809426573</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.104854013606379</v>
+        <v>3.142544703550379</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803426852654187</v>
+        <v>3.803426852654186</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.1539500399579</v>
+        <v>3.161482267990718</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.809815629938214</v>
+        <v>-4.773302940254879</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.229667363668867</v>
+        <v>1.251804667575019</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.06681205203963425</v>
+        <v>0.1170761552249382</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.19403727118168</v>
+        <v>3.231727961125681</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796293177717118</v>
+        <v>3.796293177717117</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.171504445684691</v>
+        <v>3.179036673717509</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.800923168544931</v>
+        <v>-4.764410478861596</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.250778753952971</v>
+        <v>1.272916057859123</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.06681205203963425</v>
+        <v>0.1170761552249382</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.211591676908472</v>
+        <v>3.249282366852472</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794453975702626</v>
+        <v>3.794453975702625</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.163359493089275</v>
+        <v>3.170891721122093</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.969399285514808</v>
+        <v>-4.932886595831474</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.175243354569604</v>
+        <v>1.197380658475756</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.03886421632305348</v>
+        <v>0.08912831950835742</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.186678022883108</v>
+        <v>3.224368712827108</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795603100539969</v>
+        <v>3.795603100539967</v>
       </c>
       <c r="C1997" t="n">
-        <v>3.233772154546119</v>
+        <v>3.241304382578936</v>
       </c>
       <c r="D1997" t="n">
-        <v>-4.271599756653226</v>
+        <v>-4.235087066969891</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.524775827571081</v>
+        <v>1.546913131477233</v>
       </c>
       <c r="F1997" t="n">
-        <v>-0.03148384304735724</v>
+        <v>0.0187802601379467</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.214881848717705</v>
+        <v>3.252572538661705</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784700379389899</v>
+        <v>3.784700379389897</v>
       </c>
       <c r="C1998" t="n">
-        <v>3.224436177043023</v>
+        <v>3.231968405075841</v>
       </c>
       <c r="D1998" t="n">
-        <v>-4.248878652970073</v>
+        <v>-4.240163141033999</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.524528291541247</v>
+        <v>1.535546724348494</v>
       </c>
       <c r="F1998" t="n">
-        <v>-0.03148384304735724</v>
+        <v>0.0187802601379467</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.205545871214609</v>
+        <v>3.243236561158609</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.780657783970052</v>
+        <v>3.804710150382263</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.204252428470376</v>
+        <v>3.245201676119179</v>
       </c>
       <c r="D1999" t="n">
-        <v>-4.248878652970073</v>
+        <v>-4.286853414680699</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.524528291541247</v>
+        <v>1.530103885933152</v>
       </c>
       <c r="F1999" t="n">
-        <v>-0.03148384304735724</v>
+        <v>-0.02791001350875416</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.197316225456743</v>
+        <v>3.228455668013927</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240618.xlsx
+++ b/tame_output/ON/bt/strategyON_20240618.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>48.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-12.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>16.2%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>69.1%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>12.1%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.7%</t>
+          <t>-76.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.6%</t>
+          <t>109.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.4%</t>
+          <t>124.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>94.2%</t>
+          <t>94.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,22 +982,22 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-52.2%</t>
+          <t>-50.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.4%</t>
+          <t>-72.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>90.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>454.2%</t>
+          <t>449.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-590.3%</t>
+          <t>-581.6%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>49.6%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-11.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>242.0%</t>
+          <t>220.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-223.2%</t>
+          <t>-220.5%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-23.2%</t>
+          <t>-22.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.6%</t>
+          <t>-31.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-15.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-189.5%</t>
+          <t>-161.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-226.8%</t>
+          <t>-222.5%</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1476,22 +1476,22 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-123.2%</t>
+          <t>-121.4%</t>
         </is>
       </c>
     </row>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.969762319567352</v>
+        <v>-6.96578499612612</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3223646002744438</v>
+        <v>0.3239555296509371</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.548175094357108</v>
@@ -44463,16 +44463,16 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108638</v>
+        <v>3.305023265108637</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.38615419385435</v>
+        <v>-7.382176870413117</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1538019011685225</v>
+        <v>0.1553928305450154</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.548175094357108</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.656920282946995</v>
+        <v>-7.652942959505762</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.05575415620014335</v>
+        <v>0.0573450855766362</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.548175094357108</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094116</v>
+        <v>3.374439043094115</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.002795104931804</v>
+        <v>-7.998817781490571</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.08649620744808528</v>
+        <v>-0.08490527807159198</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.548175094357108</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199285</v>
+        <v>3.405960511199284</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.166374983116189</v>
+        <v>-8.162397659674955</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1535232386668381</v>
+        <v>-0.1519323092903444</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.548175094357108</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.463036324926387</v>
+        <v>-8.459059001485153</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2684087994617093</v>
+        <v>-0.2668178700852155</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.616918230090987</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923086</v>
+        <v>3.419979433923085</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.64975603323569</v>
+        <v>-8.645778709794456</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3471229873198336</v>
+        <v>-0.3455320579433399</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.616918230090987</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297748</v>
+        <v>3.458100091297747</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.032757421978321</v>
+        <v>-9.028780098537087</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.50042564413847</v>
+        <v>-0.4988347147619763</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.616918230090987</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317615</v>
+        <v>3.447750501317614</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.214627212963356</v>
+        <v>-9.210649889522122</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5706020445610536</v>
+        <v>-0.5690111151845603</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.798788021076022</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737168</v>
+        <v>3.503515506737167</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.574157535467357</v>
+        <v>-9.570180212026123</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.7090638702646039</v>
+        <v>-0.7074729408881106</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.798788021076022</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341311</v>
+        <v>3.50317028234131</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.624506598921579</v>
+        <v>-9.620529275480346</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.7212874756891154</v>
+        <v>-0.7196965463126221</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.849137084530244</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539461</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.722125876342975</v>
+        <v>-9.718148552901742</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7572934360359049</v>
+        <v>-0.7557025066594116</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.946756361951641</v>
@@ -44722,10 +44722,10 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.869651964348618</v>
+        <v>-9.865674640907384</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8134103149165899</v>
+        <v>-0.8118193855400966</v>
       </c>
       <c r="F1877" t="n">
         <v>-2.094282449957284</v>
@@ -44745,10 +44745,10 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.07391013967848</v>
+        <v>-10.06993281623725</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.8896003879298933</v>
+        <v>-0.8880094585534</v>
       </c>
       <c r="F1878" t="n">
         <v>-2.221921394571273</v>
@@ -44768,10 +44768,10 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.14824311593865</v>
+        <v>-10.14426579249741</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.9148510239495224</v>
+        <v>-0.9132600945730291</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.366620918505946</v>
@@ -44791,10 +44791,10 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.0747732842712</v>
+        <v>-10.07079596082996</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.8700913897891223</v>
+        <v>-0.868500460412629</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.293151086838497</v>
@@ -44814,10 +44814,10 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.24989770165774</v>
+        <v>-10.24592037821651</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9255859359962226</v>
+        <v>-0.9239950066197293</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.468275504225041</v>
@@ -44837,10 +44837,10 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.48434979567223</v>
+        <v>-10.480372472231</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.026585938503615</v>
+        <v>-1.024995009127121</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.468275504225041</v>
@@ -44860,10 +44860,10 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.58872452669868</v>
+        <v>-10.58474720325744</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.075008021688169</v>
+        <v>-1.073417092311676</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.572650235251487</v>
@@ -44883,10 +44883,10 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.641510682299</v>
+        <v>-10.63753335885777</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.095006694089744</v>
+        <v>-1.09341576471325</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.668325721833884</v>
@@ -44906,10 +44906,10 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.76754747566729</v>
+        <v>-10.76357015222606</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.142727682807945</v>
+        <v>-1.141136753431451</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.643074099024141</v>
@@ -44929,10 +44929,10 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.71553196169848</v>
+        <v>-10.71155463825725</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.117931141534019</v>
+        <v>-1.116340212157525</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.643074099024141</v>
@@ -44952,10 +44952,10 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.8572038034226</v>
+        <v>-10.85322647998137</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.176075105122409</v>
+        <v>-1.174484175745915</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.643074099024141</v>
@@ -44975,10 +44975,10 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.80761295899777</v>
+        <v>-10.80363563555653</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.141185357187603</v>
+        <v>-1.139594427811109</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.593483254599307</v>
@@ -44998,10 +44998,10 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.79480556599299</v>
+        <v>-10.79082824255176</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.149113533632376</v>
+        <v>-1.147522604255883</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.642339029608209</v>
@@ -45021,10 +45021,10 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.56896041327358</v>
+        <v>-10.56498308983235</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.049196399508402</v>
+        <v>-1.047605470131909</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.600412354021045</v>
@@ -45044,10 +45044,10 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.44438175693599</v>
+        <v>-10.44040443349475</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.998225792417307</v>
+        <v>-0.9966348630408128</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.600412354021045</v>
@@ -45067,10 +45067,10 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.49727704498027</v>
+        <v>-10.49329972153904</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.016750133472914</v>
+        <v>-1.01515920409642</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.595457007932599</v>
@@ -45090,10 +45090,10 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.42514386969239</v>
+        <v>-10.42116654625116</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9821631591191249</v>
+        <v>-0.9805722297426316</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.595457007932599</v>
@@ -45113,10 +45113,10 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.35377747708275</v>
+        <v>-10.34980015364151</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9633538644691306</v>
+        <v>-0.9617629350926373</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.524090615322951</v>
@@ -45136,10 +45136,10 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.26031844309752</v>
+        <v>-10.25634111965629</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.9358537321879488</v>
+        <v>-0.9342628028114555</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.524090615322951</v>
@@ -45159,10 +45159,10 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.993076642229124</v>
+        <v>-9.98909931878789</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.8307915723399635</v>
+        <v>-0.8292006429634697</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.524090615322951</v>
@@ -45182,10 +45182,10 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.895169603552633</v>
+        <v>-9.891192280111399</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7919290718428278</v>
+        <v>-0.7903381424663345</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.456104865462394</v>
@@ -45205,10 +45205,10 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.871216062576675</v>
+        <v>-9.867238739135441</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7816791493069513</v>
+        <v>-0.7800882199304575</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.432151324486437</v>
@@ -45228,10 +45228,10 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.607156124253878</v>
+        <v>-9.603178800812644</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6893154901395846</v>
+        <v>-0.6877245607630913</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.168091386163641</v>
@@ -45251,10 +45251,10 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.900076500749041</v>
+        <v>-8.896099177307807</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.4092706743979506</v>
+        <v>-0.4076797450214569</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.168091386163641</v>
@@ -45274,10 +45274,10 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.85989220238285</v>
+        <v>-8.855914878941617</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3928533311636331</v>
+        <v>-0.3912624017871393</v>
       </c>
       <c r="F1901" t="n">
         <v>-2.12790708779745</v>
@@ -45297,10 +45297,10 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.696492331443487</v>
+        <v>-8.692515008002253</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.3281265615671307</v>
+        <v>-0.3265356321906374</v>
       </c>
       <c r="F1902" t="n">
         <v>-1.964507216858087</v>
@@ -45320,10 +45320,10 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.463011109213888</v>
+        <v>-8.459033785772654</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.2268096438374387</v>
+        <v>-0.225218714460945</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.731025994628489</v>
@@ -45343,10 +45343,10 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.313344718206373</v>
+        <v>-8.30936739476514</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.169835297747392</v>
+        <v>-0.1682443683708987</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.638122503385953</v>
@@ -45366,10 +45366,10 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.181069244575486</v>
+        <v>-8.177091921134252</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.1215576215480101</v>
+        <v>-0.1199666921715168</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.505847029755066</v>
@@ -45389,10 +45389,10 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.990469569902333</v>
+        <v>-7.9864922464611</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.04250269099111215</v>
+        <v>-0.04091176161461885</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.315247355081913</v>
@@ -45412,10 +45412,10 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.741469771218752</v>
+        <v>-7.737492447777519</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.07000356970597865</v>
+        <v>0.0715944990824724</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.315247355081913</v>
@@ -45435,10 +45435,10 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.847059760991857</v>
+        <v>-7.843082437550623</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.1002083558024816</v>
+        <v>-0.09861742642598825</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.420837344855018</v>
@@ -45458,10 +45458,10 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.865794663110454</v>
+        <v>-7.86181733966922</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.05915797477283391</v>
+        <v>-0.05756704539634061</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.426433354515149</v>
@@ -45481,10 +45481,10 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.717854621702855</v>
+        <v>-7.713877298261621</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1198608808979618</v>
+        <v>-0.1182699515214685</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.406112438606591</v>
@@ -45504,10 +45504,10 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.664885099448866</v>
+        <v>-7.660907776007632</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.1073870582498446</v>
+        <v>-0.1057961288733513</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.353142916352602</v>
@@ -45527,10 +45527,10 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.621336692678176</v>
+        <v>-7.617359369236942</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.0969283076366616</v>
+        <v>-0.0953373782601683</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.353142916352602</v>
@@ -45550,10 +45550,10 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.379188299224317</v>
+        <v>-7.375210975783084</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.01439340412602474</v>
+        <v>0.01598433350251804</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.353142916352602</v>
@@ -45573,10 +45573,10 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.270929162101796</v>
+        <v>-7.266951838660562</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.05222917943422845</v>
+        <v>0.05382010881072175</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.353142916352602</v>
@@ -45596,10 +45596,10 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.147638027284665</v>
+        <v>-7.143660703843431</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.09904372737165756</v>
+        <v>0.1006346567481509</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.229851781535472</v>
@@ -45619,10 +45619,10 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.126488828381222</v>
+        <v>-7.122511504939988</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1152043851703599</v>
+        <v>0.1167953145468537</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.208702582632029</v>
@@ -45642,10 +45642,10 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.882723386397777</v>
+        <v>-6.878746062956544</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2084912703107884</v>
+        <v>0.2100821996872821</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.208702582632029</v>
@@ -45665,10 +45665,10 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.780960566120482</v>
+        <v>-6.776983242679249</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2513207123417223</v>
+        <v>0.252911641718216</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.1954835142396</v>
@@ -45688,10 +45688,10 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.531110172171408</v>
+        <v>-6.527132848730174</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3440029449050543</v>
+        <v>0.3455938742815481</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.1954835142396</v>
@@ -45711,10 +45711,10 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.355218079703976</v>
+        <v>-6.351240756262742</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.417958905412676</v>
+        <v>0.4195498347891693</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.1954835142396</v>
@@ -45734,10 +45734,10 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.183771616681512</v>
+        <v>-6.179794293240279</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.499864996676215</v>
+        <v>0.5014559260527087</v>
       </c>
       <c r="F1921" t="n">
         <v>-1.024037051217137</v>
@@ -45757,10 +45757,10 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.109482050943173</v>
+        <v>-6.105504727501939</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5286013005878476</v>
+        <v>0.5301922299643413</v>
       </c>
       <c r="F1922" t="n">
         <v>-0.9497474854787973</v>
@@ -45780,10 +45780,10 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.045846308709239</v>
+        <v>-6.041868985268005</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5587503985357389</v>
+        <v>0.5603413279122322</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.8861117432448627</v>
@@ -45803,10 +45803,10 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.934419549383319</v>
+        <v>-5.930442225942085</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5845153610499025</v>
+        <v>0.5861062904263958</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.8861117432448627</v>
@@ -45826,10 +45826,10 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.693989052578458</v>
+        <v>-5.690011729137225</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6824306363967239</v>
+        <v>0.6840215657732176</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.6456812464400025</v>
@@ -45849,10 +45849,10 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.621746484407264</v>
+        <v>-5.612030109080175</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7152569775000219</v>
+        <v>0.7191435276308575</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.6456812464400025</v>
@@ -45872,10 +45872,10 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.568748162125876</v>
+        <v>-5.559031786798787</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7371348903299171</v>
+        <v>0.7410214404607527</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.5903449874380636</v>
@@ -45895,10 +45895,10 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.459943276646149</v>
+        <v>-5.45022690131906</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7776549157418016</v>
+        <v>0.7815414658726372</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.5903449874380636</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675938</v>
+        <v>3.818668951675937</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.239922478609138</v>
+        <v>-5.230206103282049</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8672422719672199</v>
+        <v>0.8711288220980555</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.4491251423700834</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539949</v>
+        <v>3.843274527539948</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.10705478954586</v>
+        <v>-5.097338414218772</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9362835303943542</v>
+        <v>0.9401700805251898</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.4491251423700834</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496259</v>
+        <v>3.845047386496258</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.986881706181362</v>
+        <v>-4.977165330854273</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9854986081804555</v>
+        <v>0.9893851583112911</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.3289520590055844</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576996</v>
+        <v>3.791273551576994</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.842209561081624</v>
+        <v>-4.832493185754536</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.053455568781791</v>
+        <v>1.057342118912626</v>
       </c>
       <c r="F1932" t="n">
         <v>-0.184279913905847</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.7358392229421</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.902084388439317</v>
+        <v>-4.892368013112228</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.015543129240139</v>
+        <v>1.019429679370975</v>
       </c>
       <c r="F1933" t="n">
         <v>-0.2441547412635391</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674512</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.815284890660308</v>
+        <v>-4.805568515333219</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.072663421674309</v>
+        <v>1.076549971805145</v>
       </c>
       <c r="F1934" t="n">
         <v>-0.2441547412635391</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430693</v>
+        <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.817754597122114</v>
+        <v>-4.808038221795025</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.071747940462999</v>
+        <v>1.075634490593834</v>
       </c>
       <c r="F1935" t="n">
         <v>-0.2466244477253453</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432201960036</v>
+        <v>3.743220196003598</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.886124783446125</v>
+        <v>-4.876408408119035</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.055406788408096</v>
+        <v>1.059293338538932</v>
       </c>
       <c r="F1936" t="n">
         <v>-0.2373487486891304</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508368</v>
+        <v>3.714179139508366</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.994662964362258</v>
+        <v>-4.984946589035169</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.002428224673534</v>
+        <v>1.00631477480437</v>
       </c>
       <c r="F1937" t="n">
         <v>-0.2373487486891304</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417703</v>
+        <v>3.710906731417701</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-5.025656123690964</v>
+        <v>-5.015939748363874</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.814740525982439</v>
+        <v>0.8186270761132746</v>
       </c>
       <c r="F1938" t="n">
         <v>-0.2373487486891304</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205901</v>
+        <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.850181863898495</v>
+        <v>-4.840465488571406</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.8894974618912141</v>
+        <v>0.89338401202205</v>
       </c>
       <c r="F1939" t="n">
         <v>-0.2373487486891304</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225445</v>
+        <v>3.765024323225442</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.961118116539744</v>
+        <v>-4.951401741212655</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8208649895959217</v>
+        <v>0.8247515397267575</v>
       </c>
       <c r="F1940" t="n">
         <v>-0.2373487486891304</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111293</v>
+        <v>3.77321029711129</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.969400190684802</v>
+        <v>-4.959683815357713</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8206835451578038</v>
+        <v>0.8245700952886397</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.2456308228341887</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264159</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.909547571481079</v>
+        <v>-4.89983119615399</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8547969792714254</v>
+        <v>0.8586835294022612</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.2456308228341887</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.786949957742295</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.823304108454701</v>
+        <v>-4.813587733127612</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8842406350558369</v>
+        <v>0.8881271851866726</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.2456308228341887</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.752027499316043</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.868610927853681</v>
+        <v>-4.858894552526592</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8578936827407704</v>
+        <v>0.8617802328716062</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.2864409858434195</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803187</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.897644032555982</v>
+        <v>-4.887927657228893</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8468323138929517</v>
+        <v>0.8507188640237873</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.2864409858434195</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809498</v>
+        <v>3.733390600809495</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.804833551105123</v>
+        <v>-4.795117175778033</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8132291983646611</v>
+        <v>0.817115748495497</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.1936305043925602</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560422</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.84922302043455</v>
+        <v>-4.839506645107461</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.7973468865574909</v>
+        <v>0.8012334366883267</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.2380199737219879</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472738</v>
+        <v>3.721077195472734</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.7365518021983</v>
+        <v>-4.726835426871211</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8374910823637141</v>
+        <v>0.8413776324945497</v>
       </c>
       <c r="F1948" t="n">
         <v>-0.1253487554857377</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798534</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.624174801015627</v>
+        <v>-4.614458425688538</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.8879331786674505</v>
+        <v>0.8918197287982861</v>
       </c>
       <c r="F1949" t="n">
         <v>-0.1253487554857377</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498861</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.65195519891698</v>
+        <v>-4.64223882358989</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8883182212754483</v>
+        <v>0.8922047714062842</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.1531291533870907</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705325</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.734956479942259</v>
+        <v>-4.725240104615169</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6934734288659901</v>
+        <v>0.6973599789968259</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.1717000379142645</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.68271631072927</v>
+        <v>3.682716310729266</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.84357055838559</v>
+        <v>-4.8338541830585</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.7701774582078633</v>
+        <v>0.7740640083386991</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.1717000379142645</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190769</v>
+        <v>3.733012441190765</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.930169141366693</v>
+        <v>-4.920452766039603</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7500510511177452</v>
+        <v>0.7539376012485808</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.1717000379142645</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913426</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.891785478808542</v>
+        <v>-4.882069103481452</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.7628239574833742</v>
+        <v>0.76671050761421</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.1333163753561133</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532487</v>
+        <v>3.751147197532483</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.714669148773376</v>
+        <v>-4.704952773446286</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8303995183427426</v>
+        <v>0.8342860684735784</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.1333163753561133</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793904</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.759761393606921</v>
+        <v>-4.750045018279832</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8130460121712373</v>
+        <v>0.8169325623020731</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.1952124185255031</v>
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011238</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.580385972368154</v>
+        <v>-4.721756326676037</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.8785831559731587</v>
+        <v>0.8220350142500057</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.03843566035478441</v>
+        <v>-0.2118178827870694</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.688032573021297</v>
+        <v>2.584003239561926</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982232</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.625400185888759</v>
+        <v>-4.766770540196642</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8413849258965063</v>
+        <v>0.7848367841733532</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.06878455566938901</v>
+        <v>-0.242166778101674</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.650630691164124</v>
+        <v>2.546601357704753</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509539</v>
+        <v>3.737026608509535</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.892404696161194</v>
+        <v>-5.033775050469077</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.740274684126478</v>
+        <v>0.683726542403325</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2631475937123376</v>
+        <v>-0.4365298161446226</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.539704430677301</v>
+        <v>2.43567509721793</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760811</v>
+        <v>3.702309454760808</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.993602477598367</v>
+        <v>-5.13497283190625</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.6989994934481103</v>
+        <v>0.642451351724957</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.3315564072576568</v>
+        <v>-0.5049386296899419</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.497863064446611</v>
+        <v>2.39383373098724</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815456</v>
+        <v>3.705571661815453</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.961126891427595</v>
+        <v>-5.102497245735478</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7095896894707359</v>
+        <v>0.6530415477475828</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.3315564072576568</v>
+        <v>-0.5049386296899419</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.495463026000928</v>
+        <v>2.391433692541556</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378101</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.942088763720298</v>
+        <v>-5.083459118028181</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7137296597618998</v>
+        <v>0.6571815180387466</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3897400185888513</v>
+        <v>-0.5631222410211363</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.457077578410455</v>
+        <v>2.353048244951085</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.731064473131249</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.973215394870916</v>
+        <v>-5.114585749178799</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.8788608762403329</v>
+        <v>0.8223127345171797</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3897400185888513</v>
+        <v>-0.5631222410211363</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.634659447349136</v>
+        <v>2.530630113889765</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067867</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.987082156204834</v>
+        <v>-5.128452510512717</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.8741475006928994</v>
+        <v>0.8175993589697463</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.4275979353226743</v>
+        <v>-0.6009801577549592</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.612778026294976</v>
+        <v>2.508748692835605</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789124</v>
+        <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-5.007339454733792</v>
+        <v>-5.148709809041675</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.8720531116782422</v>
+        <v>0.8155049699550889</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.4275979353226743</v>
+        <v>-0.6009801577549592</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.618786556691902</v>
+        <v>2.514757223232531</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519911</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.859596484498789</v>
+        <v>-5.000966838806672</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.010302947564265</v>
+        <v>0.9537548058411121</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2597905780877911</v>
+        <v>-0.433172800520076</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.798623618824854</v>
+        <v>2.694594285365483</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181174</v>
+        <v>3.80224592918117</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.964823815241827</v>
+        <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.961611167030011</v>
+        <v>-5.102981521337894</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9798229241160754</v>
+        <v>0.9157425543601043</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.2597905780877911</v>
+        <v>-0.433172800520076</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.808949468389152</v>
+        <v>2.697387906896964</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394732</v>
+        <v>3.805608985394729</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.965486163633485</v>
+        <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.955458460977226</v>
+        <v>-5.096828815285109</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9829463549288475</v>
+        <v>0.9188659851728764</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.2536378720350068</v>
+        <v>-0.4270200944672917</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.813303440412481</v>
+        <v>2.701741878920293</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890613</v>
+        <v>3.79823979489061</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.964566640373596</v>
+        <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.972267759127728</v>
+        <v>-5.113638113435611</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.975303112408757</v>
+        <v>0.9112227426527859</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.2704471701855085</v>
+        <v>-0.4438293926177934</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.802298338262291</v>
+        <v>2.690736776770102</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
-        <v>3.030902194170416</v>
+        <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.909969760351606</v>
+        <v>-5.051340114659489</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.066557865716027</v>
+        <v>1.002477495960056</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.2704471701855085</v>
+        <v>-0.4438293926177934</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.868633892059111</v>
+        <v>2.757072330566923</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992194</v>
+        <v>3.848729139992193</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.739483066559814</v>
+        <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.708179562686448</v>
+        <v>-4.849549916994331</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8558548171714879</v>
+        <v>0.7917744474155171</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.07242897801635406</v>
+        <v>-0.245811200448639</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.696025679750002</v>
+        <v>2.584464118257813</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852423</v>
+        <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.80977329888199</v>
+        <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.648288881043855</v>
+        <v>-4.789659235351738</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9501013221507004</v>
+        <v>0.8860209523947296</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.01253829637376058</v>
+        <v>-0.1859205188060455</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.802250321057734</v>
+        <v>2.690688759565545</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319549</v>
+        <v>3.819063300319546</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.824401034998033</v>
+        <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.746029425668829</v>
+        <v>-4.887399779976712</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9256328404167544</v>
+        <v>0.8615524706607833</v>
       </c>
       <c r="F1973" t="n">
-        <v>-0.02842757450674077</v>
+        <v>-0.2018097969390257</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.807344490293989</v>
+        <v>2.6957829288018</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489386</v>
+        <v>3.831819032489382</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.822937015822705</v>
+        <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.922367185791758</v>
+        <v>-5.063737540099641</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8536337171922543</v>
+        <v>0.7895533474362835</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.2047653346296702</v>
+        <v>-0.3781475570619551</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.700077815044903</v>
+        <v>2.588516253552714</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397795</v>
+        <v>3.836411672397792</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.821428633862634</v>
+        <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.850820863014881</v>
+        <v>-4.992191217322764</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8807438643429337</v>
+        <v>0.8166634945869626</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.2047653346296702</v>
+        <v>-0.3781475570619551</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.698569433084832</v>
+        <v>2.587007871592643</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024963</v>
+        <v>3.83602339102496</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.82129150129807</v>
+        <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.806447731376313</v>
+        <v>-4.947818085684196</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.8983559844337974</v>
+        <v>0.8342756146778263</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.1603922029911016</v>
+        <v>-0.3337744254233865</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.725056179503409</v>
+        <v>2.61349461801122</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863225</v>
+        <v>3.821591150863222</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.82129150129807</v>
+        <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.798493761081541</v>
+        <v>-4.939864115389423</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9015375725517063</v>
+        <v>0.8374572027957352</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.1603922029911016</v>
+        <v>-0.3337744254233865</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.725056179503409</v>
+        <v>2.61349461801122</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947584</v>
+        <v>3.833040181947581</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.827673258325874</v>
+        <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.750838030520485</v>
+        <v>-4.892208384828368</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9269816218039333</v>
+        <v>0.8629012520479622</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.1127364724300459</v>
+        <v>-0.2861186948623308</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.760031374867847</v>
+        <v>2.648469813375658</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326876</v>
+        <v>3.822707244326874</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.832565631700599</v>
+        <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.623153720726188</v>
+        <v>-4.764524075034071</v>
       </c>
       <c r="E1979" t="n">
-        <v>0.9829477190963765</v>
+        <v>0.9188673493404056</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.01494783736425054</v>
+        <v>-0.1584343850680344</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.84153433411915</v>
+        <v>2.729972772626961</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314552</v>
+        <v>3.828837911314549</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.819320304176471</v>
+        <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.683820311128578</v>
+        <v>-4.825190665436461</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.9454357554112929</v>
+        <v>0.881355385655322</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.06675047935428313</v>
+        <v>-0.240132701786568</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.779270016563902</v>
+        <v>2.667708455071713</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690028</v>
+        <v>3.816866067690025</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.8234180067871</v>
+        <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.638981909520179</v>
+        <v>-4.780352263828062</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.9674688186652809</v>
+        <v>0.90338844890931</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.06220704640941366</v>
+        <v>-0.2355892688416986</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.786093778941452</v>
+        <v>2.674532217449263</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674311</v>
+        <v>3.817961388674309</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.827578946418178</v>
+        <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.739740545277177</v>
+        <v>-4.88111089958506</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.9313263039935598</v>
+        <v>0.8672459342375887</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.1510326151364191</v>
+        <v>-0.324414837568704</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.736959377336327</v>
+        <v>2.625397815844138</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.82671377916322</v>
+        <v>3.826713779163218</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.833458548946015</v>
+        <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.695537708191277</v>
+        <v>-4.83690806249916</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.9548870413557571</v>
+        <v>0.890806671599786</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.1068297780505186</v>
+        <v>-0.2802120004828035</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.769360682115704</v>
+        <v>2.657799120623515</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022905</v>
+        <v>3.838228663022903</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.831868549415263</v>
+        <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.73251673585472</v>
+        <v>-4.873887090162603</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.9385054307596274</v>
+        <v>0.8744250610036566</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.0698558762591881</v>
+        <v>-0.243238098691473</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.78995502365975</v>
+        <v>2.678393462167561</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042139</v>
+        <v>3.863924114042137</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.883116314598302</v>
+        <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.75257481471956</v>
+        <v>-4.893945169027443</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.981729964396731</v>
+        <v>0.9176495946407599</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.0698558762591881</v>
+        <v>-0.243238098691473</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.84120278884279</v>
+        <v>2.729641227350601</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078282</v>
+        <v>3.86536771507828</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.881557019192555</v>
+        <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.71264414154167</v>
+        <v>-4.854014495849553</v>
       </c>
       <c r="E1986" t="n">
-        <v>0.9961429382621403</v>
+        <v>0.9320625685061692</v>
       </c>
       <c r="F1986" t="n">
-        <v>-0.02992520308129776</v>
+        <v>-0.2033074255135827</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.863601897343777</v>
+        <v>2.752040335851588</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232399</v>
+        <v>3.864518876232397</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.876505247430825</v>
+        <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.661612048819142</v>
+        <v>-4.802982403127025</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.011504003589421</v>
+        <v>0.9474236338334503</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.0211068896412302</v>
+        <v>-0.1522753327910547</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.889169381215564</v>
+        <v>2.777607819723375</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162115</v>
+        <v>3.842576394162113</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.89369265152353</v>
+        <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.596387867691937</v>
+        <v>-4.73775822199982</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.054781080133008</v>
+        <v>0.9907007103770373</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.08633107076843582</v>
+        <v>-0.08705115166384908</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.945491293984592</v>
+        <v>2.833929732492404</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639819</v>
+        <v>3.840090220639818</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.889653623822811</v>
+        <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.646882158048993</v>
+        <v>-4.788252512356876</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.030544336289466</v>
+        <v>0.9664639665334953</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.04131033364236159</v>
+        <v>-0.1320718887899233</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.914439824008228</v>
+        <v>2.802878262516039</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845198842749921</v>
+        <v>3.84519884274992</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.890910416154051</v>
+        <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.666993814083702</v>
+        <v>-4.808364168391584</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.023756466206823</v>
+        <v>0.9596760964508522</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.05233767863978078</v>
+        <v>-0.1210445437925041</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.92231302333792</v>
+        <v>2.810751461845731</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828690479393547</v>
+        <v>3.828690479393545</v>
       </c>
       <c r="C1991" t="n">
-        <v>3.051468187175262</v>
+        <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.764674393356348</v>
+        <v>-4.906044747664231</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.145242005518975</v>
+        <v>1.081161635763005</v>
       </c>
       <c r="F1991" t="n">
-        <v>-0.05836551670040802</v>
+        <v>-0.2317477391326929</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.016448877155017</v>
+        <v>2.904887315662828</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714885</v>
+        <v>3.813251854714883</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.171581096393079</v>
+        <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.740882824750205</v>
+        <v>-4.882253179058088</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.27487154217925</v>
+        <v>1.210791172423279</v>
       </c>
       <c r="F1992" t="n">
-        <v>-0.03457394809426573</v>
+        <v>-0.2079561705265506</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.15083672753652</v>
+        <v>3.039275166044331</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814259761756012</v>
+        <v>3.814259761756011</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.163289072406938</v>
+        <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.777637243311927</v>
+        <v>-4.91900759761981</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.25187775076842</v>
+        <v>1.187797381012449</v>
       </c>
       <c r="F1993" t="n">
-        <v>-0.03457394809426573</v>
+        <v>-0.2079561705265506</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.142544703550379</v>
+        <v>3.03098314205819</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803426852654186</v>
+        <v>3.803426852654185</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.161482267990718</v>
+        <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.773302940254879</v>
+        <v>-4.914673294562762</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.251804667575019</v>
+        <v>1.187724297819047</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.1170761552249382</v>
+        <v>-0.05630606720734671</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.231727961125681</v>
+        <v>3.120166399633492</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796293177717117</v>
+        <v>3.796293177717116</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.179036673717509</v>
+        <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.764410478861596</v>
+        <v>-4.905780833169479</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.272916057859123</v>
+        <v>1.208835688103152</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.1170761552249382</v>
+        <v>-0.05630606720734671</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.249282366852472</v>
+        <v>3.137720805360283</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794453975702625</v>
+        <v>3.794453975702624</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.170891721122093</v>
+        <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.932886595831474</v>
+        <v>-5.074256950139357</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.197380658475756</v>
+        <v>1.133300288719785</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.08912831950835742</v>
+        <v>-0.08425390292392748</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.224368712827108</v>
+        <v>3.112807151334919</v>
       </c>
     </row>
     <row r="1997">
@@ -47479,19 +47479,19 @@
         <v>3.795603100539967</v>
       </c>
       <c r="C1997" t="n">
-        <v>3.241304382578936</v>
+        <v>3.233772154546119</v>
       </c>
       <c r="D1997" t="n">
-        <v>-4.235087066969891</v>
+        <v>-4.376457421277774</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.546913131477233</v>
+        <v>1.482832761721262</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.0187802601379467</v>
+        <v>-0.1546019622943382</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.252572538661705</v>
+        <v>3.141010977169516</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784700379389897</v>
+        <v>3.784700379389896</v>
       </c>
       <c r="C1998" t="n">
-        <v>3.231968405075841</v>
+        <v>3.224436177043023</v>
       </c>
       <c r="D1998" t="n">
-        <v>-4.240163141033999</v>
+        <v>-4.353736317594621</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.535546724348494</v>
+        <v>1.482585225691427</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.0187802601379467</v>
+        <v>-0.1546019622943382</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.243236561158609</v>
+        <v>3.131674999666421</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.804710150382263</v>
+        <v>3.442699768702873</v>
       </c>
       <c r="C1999" t="n">
-        <v>3.245201676119179</v>
+        <v>3.237669448086361</v>
       </c>
       <c r="D1999" t="n">
-        <v>-4.286853414680699</v>
+        <v>-4.20015741407338</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.530103885933152</v>
+        <v>1.557250058143262</v>
       </c>
       <c r="F1999" t="n">
-        <v>-0.02791001350875416</v>
+        <v>0.0145121285678792</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.228455668013927</v>
+        <v>3.246376725227089</v>
       </c>
     </row>
   </sheetData>
